--- a/data/animal-sounds-data.xlsx
+++ b/data/animal-sounds-data.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="メインデータ" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="名称マッピング" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分類マッピング" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="オノマトペマッピング" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="凡例・定義" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="地域マスター" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="地域マッピング" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="メインデータ" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="名称マッピング" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="分類マッピング" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="オノマトペマッピング" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="凡例・定義" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="地域マスター" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="地域マッピング" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'メインデータ'!$A$1:$M$248</definedName>
@@ -516,7 +516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N259"/>
+  <dimension ref="A1:O259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -605,6 +605,11 @@
           <t>音声参照</t>
         </is>
       </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>taxonCode</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -673,6 +678,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Macaca%20fuscata</t>
         </is>
       </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>t-12077600</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -741,6 +751,11 @@
           <t>https://xeno-canto.org/species/Corvus-macrorhynchos</t>
         </is>
       </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>labcro1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -809,6 +824,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Dryophytes%20japonicus</t>
         </is>
       </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>t-11039482</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -875,6 +895,11 @@
       <c r="N5" t="inlineStr">
         <is>
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Teleogryllus%20emma</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>t-12137860</t>
         </is>
       </c>
     </row>
@@ -941,6 +966,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Caretta%20caretta</t>
         </is>
       </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>t-12104433</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1009,6 +1039,11 @@
           <t>https://xeno-canto.org/species/Passer-montanus</t>
         </is>
       </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>eutspa</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1081,6 +1116,11 @@
           <t>https://xeno-canto.org/species/Corvus-corone</t>
         </is>
       </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>carcro1</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1153,6 +1193,11 @@
           <t>https://xeno-canto.org/species/Horornis-diphone</t>
         </is>
       </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>jabwar</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1221,6 +1266,11 @@
           <t>https://xeno-canto.org/species/Zosterops-japonicus</t>
         </is>
       </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>warwhe1</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1293,6 +1343,11 @@
           <t>https://xeno-canto.org/species/Parus-minor</t>
         </is>
       </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>japtit4</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1361,6 +1416,11 @@
           <t>https://xeno-canto.org/species/Sittiparus-varius</t>
         </is>
       </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>vartit1</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1433,6 +1493,11 @@
           <t>https://xeno-canto.org/species/Alauda-arvensis</t>
         </is>
       </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>skylar</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1501,6 +1566,11 @@
           <t>https://xeno-canto.org/species/Hirundo-rustica</t>
         </is>
       </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>barswa</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1573,6 +1643,11 @@
           <t>https://xeno-canto.org/species/Cyanoptila-cyanomelana</t>
         </is>
       </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>bawfly2</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1645,6 +1720,11 @@
           <t>https://xeno-canto.org/species/Larvivora-akahige</t>
         </is>
       </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>japrob2</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1717,6 +1797,11 @@
           <t>https://xeno-canto.org/species/Phoenicurus-auroreus</t>
         </is>
       </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>daured1</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1789,6 +1874,11 @@
           <t>https://xeno-canto.org/species/Lanius-bucephalus</t>
         </is>
       </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>buhshr1</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1857,6 +1947,11 @@
           <t>https://xeno-canto.org/species/Motacilla-alba</t>
         </is>
       </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>whiwag</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1925,6 +2020,11 @@
           <t>https://xeno-canto.org/species/Chloris-sinica</t>
         </is>
       </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>origre</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1997,6 +2097,11 @@
           <t>https://xeno-canto.org/species/Emberiza-cioides</t>
         </is>
       </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>meabun1</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -2069,6 +2174,11 @@
           <t>https://xeno-canto.org/species/Garrulus-glandarius</t>
         </is>
       </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>eurjay1</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -2137,6 +2247,11 @@
           <t>https://xeno-canto.org/species/Cyanopica-cyanus</t>
         </is>
       </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>azwmag2</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -2205,6 +2320,11 @@
           <t>https://xeno-canto.org/species/Hypsipetes-amaurotis</t>
         </is>
       </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>brebul1</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -2273,6 +2393,11 @@
           <t>https://xeno-canto.org/species/Spodiopsar-cineraceus</t>
         </is>
       </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>whcsta1</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2341,6 +2466,11 @@
           <t>https://xeno-canto.org/species/Aegithalos-caudatus</t>
         </is>
       </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>lottit1</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2413,6 +2543,11 @@
           <t>https://xeno-canto.org/species/Alcedo-atthis</t>
         </is>
       </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>comkin1</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2485,6 +2620,11 @@
           <t>https://xeno-canto.org/species/Terpsiphone-atrocaudata</t>
         </is>
       </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>japfly1</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2557,6 +2697,11 @@
           <t>https://xeno-canto.org/species/Monticola-solitarius</t>
         </is>
       </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>burthr</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2629,6 +2774,11 @@
           <t>https://xeno-canto.org/species/Troglodytes-troglodytes</t>
         </is>
       </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>winwre4</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2701,6 +2851,11 @@
           <t>https://xeno-canto.org/species/Phasianus-versicolor</t>
         </is>
       </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>rinphe2</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2773,6 +2928,11 @@
           <t>https://xeno-canto.org/species/Syrmaticus-soemmerringii</t>
         </is>
       </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>copphe1</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2845,6 +3005,11 @@
           <t>https://xeno-canto.org/species/Lagopus-muta</t>
         </is>
       </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>rocpta1</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2917,6 +3082,11 @@
           <t>https://xeno-canto.org/species/Bambusicola-thoracicus</t>
         </is>
       </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>chbpar3</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2985,6 +3155,11 @@
           <t>https://xeno-canto.org/species/Coturnix-japonica</t>
         </is>
       </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>japqua</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -3053,6 +3228,11 @@
           <t>https://xeno-canto.org/species/Anas-platyrhynchos</t>
         </is>
       </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>mallar3</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -3121,6 +3301,11 @@
           <t>https://xeno-canto.org/species/Aix-galericulata</t>
         </is>
       </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>manduc</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -3193,6 +3378,11 @@
           <t>https://xeno-canto.org/species/Cygnus-cygnus</t>
         </is>
       </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>whoswa</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -3261,6 +3451,11 @@
           <t>https://xeno-canto.org/species/Anas-zonorhyncha</t>
         </is>
       </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>spbduc</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -3333,6 +3528,11 @@
           <t>https://xeno-canto.org/species/Anas-crecca</t>
         </is>
       </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>gnwtea</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -3401,6 +3601,11 @@
           <t>https://xeno-canto.org/species/Streptopelia-orientalis</t>
         </is>
       </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>ortdov</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -3473,6 +3678,11 @@
           <t>https://xeno-canto.org/species/Columba-livia</t>
         </is>
       </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>rocpig</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -3541,6 +3751,11 @@
           <t>https://xeno-canto.org/species/Treron-sieboldii</t>
         </is>
       </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>whbpig1</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -3609,6 +3824,11 @@
           <t>https://xeno-canto.org/species/Accipiter-gentilis</t>
         </is>
       </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>y00392</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -3677,6 +3897,11 @@
           <t>https://xeno-canto.org/species/Milvus-migrans</t>
         </is>
       </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>blakit1</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -3745,6 +3970,11 @@
           <t>https://xeno-canto.org/species/Buteo-japonicus</t>
         </is>
       </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>combuz6</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -3817,6 +4047,11 @@
           <t>https://xeno-canto.org/species/Haliaeetus-albicilla</t>
         </is>
       </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>whteag</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -3889,6 +4124,11 @@
           <t>https://xeno-canto.org/species/Nisaetus-nipalensis</t>
         </is>
       </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>mouhae1</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -3961,6 +4201,11 @@
           <t>https://xeno-canto.org/species/Strix-uralensis</t>
         </is>
       </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>uraowl1</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -4029,6 +4274,11 @@
           <t>https://xeno-canto.org/species/Ninox-scutulata</t>
         </is>
       </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>brnhao1</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -4101,6 +4351,11 @@
           <t>https://xeno-canto.org/species/Otus-scops</t>
         </is>
       </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>eursco1</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -4173,6 +4428,11 @@
           <t>https://xeno-canto.org/species/Ketupa-blakistoni</t>
         </is>
       </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>blfowl1</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -4245,6 +4505,11 @@
           <t>https://xeno-canto.org/species/Cuculus-canorus</t>
         </is>
       </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>comcuc</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -4317,6 +4582,11 @@
           <t>https://xeno-canto.org/species/Cuculus-poliocephalus</t>
         </is>
       </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>lescuc1</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -4389,6 +4659,11 @@
           <t>https://xeno-canto.org/species/Cuculus-optatus</t>
         </is>
       </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>oricuc2</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -4461,6 +4736,11 @@
           <t>https://xeno-canto.org/species/Picus-awokera</t>
         </is>
       </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>japwoo1</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -4529,6 +4809,11 @@
           <t>https://xeno-canto.org/species/Dendrocopos-major</t>
         </is>
       </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>grswoo</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -4601,6 +4886,11 @@
           <t>https://xeno-canto.org/species/Yungipicus-kizuki</t>
         </is>
       </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>pygwoo1</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -4669,6 +4959,11 @@
           <t>https://xeno-canto.org/species/Ardea-cinerea</t>
         </is>
       </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>graher1</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -4737,6 +5032,11 @@
           <t>https://xeno-canto.org/species/Ardea-alba</t>
         </is>
       </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>greegr</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -4809,6 +5109,11 @@
           <t>https://xeno-canto.org/species/Nycticorax-nycticorax</t>
         </is>
       </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>bcnher</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -4881,6 +5186,11 @@
           <t>https://xeno-canto.org/species/Grus-japonensis</t>
         </is>
       </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>reccra1</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -4953,6 +5263,11 @@
           <t>https://xeno-canto.org/species/Grus-monacha</t>
         </is>
       </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>hoocra1</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -5021,6 +5336,11 @@
           <t>https://xeno-canto.org/species/Gallinula-chloropus</t>
         </is>
       </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>commoo3</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -5093,6 +5413,11 @@
           <t>https://xeno-canto.org/species/Hypotaenidia-okinawae</t>
         </is>
       </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>okirai1</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -5161,6 +5486,11 @@
           <t>https://xeno-canto.org/species/Chroicocephalus-ridibundus</t>
         </is>
       </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>bkhgul</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -5233,6 +5563,11 @@
           <t>https://xeno-canto.org/species/Larus-crassirostris</t>
         </is>
       </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>bktgul</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -5301,6 +5636,11 @@
           <t>https://xeno-canto.org/species/Charadrius-dubius</t>
         </is>
       </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>y00379</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -5373,6 +5713,11 @@
           <t>https://xeno-canto.org/species/Gallinago-gallinago</t>
         </is>
       </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>comsni</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -5445,6 +5790,11 @@
           <t>https://xeno-canto.org/species/Eurystomus-orientalis</t>
         </is>
       </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>dollar1</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -5513,6 +5863,11 @@
           <t>https://xeno-canto.org/species/Megaceryle-lugubris</t>
         </is>
       </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>crekin1</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -5585,6 +5940,11 @@
           <t>https://xeno-canto.org/species/Ciconia-boyciana</t>
         </is>
       </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>oristo1</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -5653,6 +6013,11 @@
           <t>https://xeno-canto.org/species/Tachybaptus-ruficollis</t>
         </is>
       </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>litgre1</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -5725,6 +6090,11 @@
           <t>https://xeno-canto.org/species/Calonectris-leucomelas</t>
         </is>
       </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>strshe</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -5797,6 +6167,11 @@
           <t>https://xeno-canto.org/species/Aptenodytes-forsteri</t>
         </is>
       </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>emppen1</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -5869,6 +6244,11 @@
           <t>https://xeno-canto.org/species/Upupa-epops</t>
         </is>
       </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>hoopoe</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -5937,6 +6317,11 @@
           <t>https://xeno-canto.org/species/Apus-pacificus</t>
         </is>
       </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>fotswi</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -6005,6 +6390,11 @@
           <t>https://xeno-canto.org/species/Gallus-gallus-domesticus</t>
         </is>
       </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>redjun1</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -6073,6 +6463,11 @@
           <t>https://xeno-canto.org/species/Pavo-cristatus</t>
         </is>
       </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>compea</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -6145,6 +6540,11 @@
           <t>https://xeno-canto.org/species/Haliaeetus-leucocephalus</t>
         </is>
       </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>baleag</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -6217,6 +6617,11 @@
           <t>https://xeno-canto.org/species/Menura-novaehollandiae</t>
         </is>
       </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>suplyr1</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -6289,6 +6694,11 @@
           <t>https://xeno-canto.org/species/Luscinia-megarhynchos</t>
         </is>
       </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>comnig1</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -6361,6 +6771,11 @@
           <t>https://xeno-canto.org/species/Apteryx-mantelli</t>
         </is>
       </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>nibkiw1</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -6433,6 +6848,11 @@
           <t>https://xeno-canto.org/species/Dacelo-novaeguineae</t>
         </is>
       </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>laukoo1</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -6505,6 +6925,11 @@
           <t>https://xeno-canto.org/species/Vultur-gryphus</t>
         </is>
       </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>andcon1</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -6577,6 +7002,11 @@
           <t>https://xeno-canto.org/species/Phalacrocorax-capillatus</t>
         </is>
       </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>japcor1</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -6649,6 +7079,11 @@
           <t>https://xeno-canto.org/species/Cinclus-pallasii</t>
         </is>
       </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>brodip1</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -6717,6 +7152,11 @@
           <t>https://xeno-canto.org/species/Ficedula-narcissina</t>
         </is>
       </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>narfly2</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -6789,6 +7229,11 @@
           <t>https://xeno-canto.org/species/Pericrocotus-divaricatus</t>
         </is>
       </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>ashmin1</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -6861,6 +7306,11 @@
           <t>https://xeno-canto.org/species/Phylloscopus-xanthodryas</t>
         </is>
       </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>arcwar3</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -6933,6 +7383,11 @@
           <t>https://xeno-canto.org/species/Phylloscopus-coronatus</t>
         </is>
       </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>eacwar1</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -7005,6 +7460,11 @@
           <t>https://xeno-canto.org/species/Acrocephalus-orientalis</t>
         </is>
       </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>orrwar1</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -7077,6 +7537,11 @@
           <t>https://xeno-canto.org/species/Nipponia-nippon</t>
         </is>
       </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>creibi1</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -7149,6 +7614,11 @@
           <t>https://xeno-canto.org/species/Anser-fabalis</t>
         </is>
       </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>taibeg1</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -7221,6 +7691,11 @@
           <t>https://xeno-canto.org/species/Gavia-stellata</t>
         </is>
       </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>retloo</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -7293,6 +7768,11 @@
           <t>https://xeno-canto.org/species/Struthio-camelus</t>
         </is>
       </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>ostric2</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -7361,6 +7841,11 @@
           <t>https://xeno-canto.org/species/Melopsittacus-undulatus</t>
         </is>
       </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>budger</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -7429,6 +7914,11 @@
           <t>https://xeno-canto.org/species/Nymphicus-hollandicus</t>
         </is>
       </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>cockat</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -7497,6 +7987,11 @@
           <t>https://xeno-canto.org/species/Phoenicopterus-roseus</t>
         </is>
       </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>grefla3</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -7637,6 +8132,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Felis%20catus</t>
         </is>
       </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>t-11031969</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -7705,6 +8205,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Panthera%20leo</t>
         </is>
       </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>t-11031947</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -7773,6 +8278,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Panthera%20tigris</t>
         </is>
       </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>t-11036143</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -7841,6 +8351,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Canis%20lupus</t>
         </is>
       </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>t-11032766</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -7909,6 +8424,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Vulpes%20vulpes%20japonica</t>
         </is>
       </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>t-12082798</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -7981,6 +8501,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Nyctereutes%20procyonoides</t>
         </is>
       </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>t-12084019</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -8049,6 +8574,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Ursus%20thibetanus</t>
         </is>
       </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>t-12076666</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -8121,6 +8651,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Ursus%20arctos</t>
         </is>
       </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>t-11038647</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -8189,6 +8724,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Ursus%20maritimus</t>
         </is>
       </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>t-11030301</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -8257,6 +8797,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Ailuropoda%20melanoleuca</t>
         </is>
       </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>t-12076675</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -8329,6 +8874,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Lutra%20nippon</t>
         </is>
       </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>t-12084968</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -8397,6 +8947,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Enhydra%20lutris</t>
         </is>
       </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>t-11036138</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -8465,6 +9020,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Phoca%20largha</t>
         </is>
       </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>t-11032768</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -8533,6 +9093,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Zalophus%20japonicus</t>
         </is>
       </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>t-12076704</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -8601,6 +9166,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Odobenus%20rosmarus</t>
         </is>
       </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>t-11030303</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -8669,6 +9239,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Crocuta%20crocuta</t>
         </is>
       </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>t-11074122</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -8741,6 +9316,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Acinonyx%20jubatus</t>
         </is>
       </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>t-11026957</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -8809,6 +9389,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Procyon%20lotor</t>
         </is>
       </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>t-11037790</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -8877,6 +9462,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Martes%20melampus</t>
         </is>
       </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>t-12076724</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -8945,6 +9535,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Bos%20taurus</t>
         </is>
       </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>t-11072529</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -9013,6 +9608,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Ovis%20aries</t>
         </is>
       </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>t-11067775</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -9081,6 +9681,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Capra%20aegagrus%20hircus</t>
         </is>
       </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>t-11076487</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -9149,6 +9754,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Sus%20scrofa%20domesticus</t>
         </is>
       </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>t-12041182</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -9217,6 +9827,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Sus%20scrofa</t>
         </is>
       </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>t-11074908</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -9289,6 +9904,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Cervus%20nippon</t>
         </is>
       </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>t-11078085</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -9357,6 +9977,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Rangifer%20tarandus</t>
         </is>
       </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>t-11070148</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -9429,6 +10054,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Capricornis%20crispus</t>
         </is>
       </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>t-12080269</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -9501,6 +10131,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Giraffa%20camelopardalis</t>
         </is>
       </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>t-11070143</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -9569,6 +10204,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Hippopotamus%20amphibius</t>
         </is>
       </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>t-11066977</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -9641,6 +10281,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Megaptera%20novaeangliae</t>
         </is>
       </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>t-11028617</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -9709,6 +10354,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Physeter%20macrocephalus</t>
         </is>
       </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>t-1474677</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -9777,6 +10427,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Orcinus%20orca</t>
         </is>
       </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>t-11038646</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -9845,6 +10500,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Tursiops%20truncatus</t>
         </is>
       </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>t-11033635</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -9913,6 +10573,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Camelus%20dromedarius</t>
         </is>
       </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>t-11066978</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -9981,6 +10646,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Vicugna%20pacos</t>
         </is>
       </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>t-12081106</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -10049,6 +10719,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Equus%20caballus</t>
         </is>
       </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>t-12030474</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -10117,6 +10792,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Equus%20asinus</t>
         </is>
       </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>t-12030473</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -10189,6 +10869,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Equus%20quagga</t>
         </is>
       </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>t-11069346</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -10257,6 +10942,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Ceratotherium%20simum</t>
         </is>
       </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>t-12077570</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -10325,6 +11015,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Loxodonta%20africana</t>
         </is>
       </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>t-11075812</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -10393,6 +11088,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Elephas%20maximus</t>
         </is>
       </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>t-11075768</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -10461,6 +11161,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Pan%20troglodytes</t>
         </is>
       </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>t-11062382</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -10529,6 +11234,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Gorilla%20gorilla</t>
         </is>
       </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>t-11064823</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -10597,6 +11307,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Hylobates%20lar</t>
         </is>
       </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>t-11053497</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -10665,6 +11380,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Alouatta%20seniculus</t>
         </is>
       </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>t-11057514</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -10733,6 +11453,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Lemur%20catta</t>
         </is>
       </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>t-11056709</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -10801,6 +11526,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Mus%20musculus</t>
         </is>
       </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>t-12078329</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -10869,6 +11599,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Rattus%20norvegicus</t>
         </is>
       </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>t-12078236</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -10937,6 +11672,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Sciurus%20lis</t>
         </is>
       </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>t-12079377</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -11009,6 +11749,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Petaurista%20leucogenys</t>
         </is>
       </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>t-12079370</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -11081,6 +11826,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Hydrochoerus%20hydrochaeris</t>
         </is>
       </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>t-11072558</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -11149,6 +11899,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Cavia%20porcellus</t>
         </is>
       </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>t-11076522</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -11217,6 +11972,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Mesocricetus%20auratus</t>
         </is>
       </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>t-12078507</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -11289,6 +12049,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Castor%20canadensis</t>
         </is>
       </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>t-11036119</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -11361,6 +12126,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Lepus%20brachyurus</t>
         </is>
       </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>t-12077436</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -11433,6 +12203,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Pentalagus%20furnessi</t>
         </is>
       </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>t-12077455</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -11505,6 +12280,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Ochotona%20hyperborea</t>
         </is>
       </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>t-12083931</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -11577,6 +12357,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Pteropus%20pselaphon</t>
         </is>
       </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>t-12076148</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -11649,6 +12434,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Pipistrellus%20abramus</t>
         </is>
       </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>t-12080850</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -11717,6 +12507,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Mogera%20imaizumii</t>
         </is>
       </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>t-12079953</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -11789,6 +12584,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Phascolarctos%20cinereus</t>
         </is>
       </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>t-11055109</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -11857,6 +12657,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Osphranter%20rufus</t>
         </is>
       </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>t-11063203</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -11925,6 +12730,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Sarcophilus%20harrisii</t>
         </is>
       </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>t-11046931</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -11993,6 +12803,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Orycteropus%20afer</t>
         </is>
       </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>t-12079982</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
@@ -12061,6 +12876,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Dasypus%20novemcinctus</t>
         </is>
       </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>t-11037804</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -12133,6 +12953,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Manis%20javanica</t>
         </is>
       </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>t-12077578</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -12205,6 +13030,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Meloimorpha%20japonica</t>
         </is>
       </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>t-12142599</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -12277,6 +13107,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Xenogryllus%20marmoratus</t>
         </is>
       </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>t-12141332</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
@@ -12349,6 +13184,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Velarifictorus%20micado</t>
         </is>
       </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>t-11870891</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -12417,6 +13257,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Loxoblemmus%20doenitzi</t>
         </is>
       </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>t-12156928</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
@@ -12489,6 +13334,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Oecanthus%20longicauda</t>
         </is>
       </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>t-12140054</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -12561,6 +13411,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Truljalia%20hibinonis</t>
         </is>
       </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>t-12134465</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
@@ -12633,6 +13488,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Ornebius%20kanetataki</t>
         </is>
       </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>t-12162519</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -12701,6 +13561,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Svistella%20bifasciata</t>
         </is>
       </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>t-12161659</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -12773,6 +13638,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Gampsocleis%20buergeri</t>
         </is>
       </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>t-12180976</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -12917,6 +13787,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Hexacentrus%20japonicus</t>
         </is>
       </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>t-12148298</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -13057,6 +13932,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Locusta%20migratoria</t>
         </is>
       </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>t-12119273</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
@@ -13129,6 +14009,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Acrida%20cinerea</t>
         </is>
       </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>t-12134456</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
@@ -13201,6 +14086,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Graptopsaltria%20nigrofuscata</t>
         </is>
       </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>t-12130907</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
@@ -13269,6 +14159,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Hyalessa%20maculaticollis</t>
         </is>
       </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>t-12134926</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
@@ -13341,6 +14236,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Cryptotympana%20facialis</t>
         </is>
       </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>t-12106542</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
@@ -13413,6 +14313,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Meimuna%20opalifera</t>
         </is>
       </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>t-12130764</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
@@ -13485,6 +14390,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Tanna%20japonensis</t>
         </is>
       </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>t-12134174</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
@@ -13773,6 +14683,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Apis%20mellifera</t>
         </is>
       </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>t-11139707</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
@@ -13841,6 +14756,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Apis%20cerana%20japonica</t>
         </is>
       </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>t-12931908</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
@@ -13913,6 +14833,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Vespa%20mandarinia</t>
         </is>
       </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>t-12918886</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
@@ -13985,6 +14910,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Aedes%20albopictus</t>
         </is>
       </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>t-12897703</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
@@ -14053,6 +14983,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Musca%20domestica</t>
         </is>
       </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>t-12906097</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
@@ -14125,6 +15060,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Trypoxylus%20dichotomus</t>
         </is>
       </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>t-12919021</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
@@ -14269,6 +15209,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Cephonodes%20hylas</t>
         </is>
       </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>t-12112331</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
@@ -14341,6 +15286,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Gromphadorhina%20portentosa</t>
         </is>
       </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>t-12918910</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
@@ -14413,6 +15363,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Anotogaster%20sieboldii</t>
         </is>
       </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>t-12105523</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
@@ -14481,6 +15436,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Pelophylax%20nigromaculatus</t>
         </is>
       </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>t-11102654</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
@@ -14553,6 +15513,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Lithobates%20catesbeianus</t>
         </is>
       </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>t-11113588</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
@@ -14697,6 +15662,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Zhangixalus%20arboreus</t>
         </is>
       </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>t-12094585</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
@@ -14769,6 +15739,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Zhangixalus%20schlegelii</t>
         </is>
       </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>t-12094587</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
@@ -14841,6 +15816,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Buergeria%20buergeri</t>
         </is>
       </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>t-12089661</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
@@ -14913,6 +15893,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Rana%20tagoi</t>
         </is>
       </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>t-12089325</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
@@ -14985,6 +15970,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Rana%20ornativentris</t>
         </is>
       </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>t-12089343</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
@@ -15053,6 +16043,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Rana%20japonica</t>
         </is>
       </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>t-12089322</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
@@ -15125,6 +16120,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Pelophylax%20porosus</t>
         </is>
       </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>t-12091381</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
@@ -15197,6 +16197,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Kurixalus%20eiffingeri</t>
         </is>
       </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>t-12089672</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
@@ -15269,6 +16274,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Odorrana%20ishikawae</t>
         </is>
       </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>t-12091322</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
@@ -15341,6 +16351,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Andrias%20japonicus</t>
         </is>
       </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>t-12089731</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
@@ -15409,6 +16424,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Cynops%20pyrrhogaster</t>
         </is>
       </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>t-12090190</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
@@ -15481,6 +16501,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Dendrobates%20tinctorius</t>
         </is>
       </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>t-12087506</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
@@ -15553,6 +16578,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Eleutherodactylus%20coqui</t>
         </is>
       </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>t-11130532</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
@@ -15625,6 +16655,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Xenopus%20laevis</t>
         </is>
       </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>t-12089309</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
@@ -15693,6 +16728,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Gekko%20japonicus</t>
         </is>
       </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>t-12108757</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
@@ -15765,6 +16805,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Gekko%20gecko</t>
         </is>
       </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>t-11774257</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
@@ -15837,6 +16882,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Elaphe%20climacophora</t>
         </is>
       </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>t-12105705</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
@@ -15909,6 +16959,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Gloydius%20blomhoffii</t>
         </is>
       </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>t-12098591</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
@@ -15981,6 +17036,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Crotalus%20atrox</t>
         </is>
       </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>t-11756105</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
@@ -16053,6 +17113,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Ophiophagus%20hannah</t>
         </is>
       </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>t-11770590</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
@@ -16125,6 +17190,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Crocodylus%20porosus</t>
         </is>
       </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>t-12096150</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
@@ -16193,6 +17263,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Alligator%20mississippiensis</t>
         </is>
       </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>t-11746735</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
@@ -16265,6 +17340,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Aldabrachelys%20gigantea</t>
         </is>
       </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>t-12030471</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
@@ -16337,6 +17417,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Pelodiscus%20sinensis</t>
         </is>
       </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>t-12105702</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
@@ -16407,6 +17492,11 @@
       <c r="N226" t="inlineStr">
         <is>
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Sphenodon%20punctatus</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>t-12119171</t>
         </is>
       </c>
     </row>
@@ -16473,6 +17563,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Plestiodon%20japonicus</t>
         </is>
       </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>t-12110377</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
@@ -16545,6 +17640,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Varanus%20komodoensis</t>
         </is>
       </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>t-12104272</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
@@ -16617,6 +17717,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Furcifer%20pardalis</t>
         </is>
       </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>t-12099735</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
@@ -16689,6 +17794,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Chelidonichthys%20spinosus</t>
         </is>
       </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>t-12921190</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
@@ -16761,6 +17871,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Oplegnathus%20fasciatus</t>
         </is>
       </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>t-12922796</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
@@ -16833,6 +17948,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Takifugu%20rubripes</t>
         </is>
       </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>t-12906043</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
@@ -16905,6 +18025,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Stephanolepis%20cirrhifer</t>
         </is>
       </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>t-12923047</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
@@ -16977,6 +18102,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Amphiprion%20ocellaris</t>
         </is>
       </c>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>t-12907675</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
@@ -17049,6 +18179,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Porichthys%20notatus</t>
         </is>
       </c>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>t-10857897</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
@@ -17121,6 +18256,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Nibea%20mitsukurii</t>
         </is>
       </c>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>t-12936257</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
@@ -17193,6 +18333,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Pygocentrus%20nattereri</t>
         </is>
       </c>
+      <c r="O237" t="inlineStr">
+        <is>
+          <t>pygnat1</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
@@ -17265,6 +18410,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Opsanus%20tau</t>
         </is>
       </c>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>t-10869486</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
@@ -17337,6 +18487,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Haemulon%20sciurus</t>
         </is>
       </c>
+      <c r="O239" t="inlineStr">
+        <is>
+          <t>t-10948810</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
@@ -17409,6 +18564,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Pagrus%20major</t>
         </is>
       </c>
+      <c r="O240" t="inlineStr">
+        <is>
+          <t>t-12907662</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
@@ -17477,6 +18637,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Sebastiscus%20marmoratus</t>
         </is>
       </c>
+      <c r="O241" t="inlineStr">
+        <is>
+          <t>t-12921074</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
@@ -17549,6 +18714,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Alpheus%20bellulus</t>
         </is>
       </c>
+      <c r="O242" t="inlineStr">
+        <is>
+          <t>t-12939602</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
@@ -17621,6 +18791,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Panulirus%20japonicus</t>
         </is>
       </c>
+      <c r="O243" t="inlineStr">
+        <is>
+          <t>t-12903755</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
@@ -17693,6 +18868,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Odontodactylus%20scyllarus</t>
         </is>
       </c>
+      <c r="O244" t="inlineStr">
+        <is>
+          <t>t-12906041</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
@@ -17765,6 +18945,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Ocypode%20stimpsoni</t>
         </is>
       </c>
+      <c r="O245" t="inlineStr">
+        <is>
+          <t>t-12461434</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
@@ -17837,6 +19022,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Homarus%20americanus</t>
         </is>
       </c>
+      <c r="O246" t="inlineStr">
+        <is>
+          <t>t-12897498</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
@@ -17909,6 +19099,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Mizuhopecten%20yessoensis</t>
         </is>
       </c>
+      <c r="O247" t="inlineStr">
+        <is>
+          <t>t-12919007</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -17976,6 +19171,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Buergeria%20buergeri</t>
         </is>
       </c>
+      <c r="O248" t="inlineStr">
+        <is>
+          <t>t-12089661</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -18043,6 +19243,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Hyla%20arborea</t>
         </is>
       </c>
+      <c r="O249" t="inlineStr">
+        <is>
+          <t>t-11156829</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -18110,6 +19315,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Hyla%20meridionalis</t>
         </is>
       </c>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>t-12088534</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -18177,6 +19387,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Dyscophus%20guineti</t>
         </is>
       </c>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>t-12089102</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -18244,6 +19459,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Cynops%20pyrrhogaster</t>
         </is>
       </c>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>t-12090190</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -18311,6 +19531,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Fejervarya%20kawamurai</t>
         </is>
       </c>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>t-12092612</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -18378,6 +19603,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Phyllobates%20aurotaenia</t>
         </is>
       </c>
+      <c r="O254" t="inlineStr">
+        <is>
+          <t>t-11145721</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -18445,6 +19675,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Rhinella%20marina</t>
         </is>
       </c>
+      <c r="O255" t="inlineStr">
+        <is>
+          <t>t-11147981</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -18574,6 +19809,11 @@
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Andrias%20davidianus</t>
         </is>
       </c>
+      <c r="O257" t="inlineStr">
+        <is>
+          <t>t-12089732</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -18701,6 +19941,11 @@
       <c r="N259" t="inlineStr">
         <is>
           <t>https://search.macaulaylibrary.org/catalog?taxonCode=&amp;mediaType=audio&amp;q=Microhyla%20ornata</t>
+        </is>
+      </c>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>t-11047001</t>
         </is>
       </c>
     </row>

--- a/data/animal-sounds-data.xlsx
+++ b/data/animal-sounds-data.xlsx
@@ -516,7 +516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O259"/>
+  <dimension ref="A1:O306"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -19946,6 +19946,2900 @@
       <c r="O259" t="inlineStr">
         <is>
           <t>t-11047001</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>B096</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>ツグミ</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>脊索動物門</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>鳥綱</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>スズメ目</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>ヒタキ科</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>クィクィ</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>鳴管</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/Category:Turdus_naumanni</t>
+        </is>
+      </c>
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>dusthr1</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>B097</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>シロハラ</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>脊索動物門</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>鳥綱</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>スズメ目</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>ヒタキ科</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>ツィー</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>鳴管</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/Category:Turdus_pallidus</t>
+        </is>
+      </c>
+      <c r="O261" t="inlineStr">
+        <is>
+          <t>palthr1</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>B098</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>キクイタダキ</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>脊索動物門</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>鳥綱</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>スズメ目</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>キクイタダキ科</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>ツィツィツィ</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>鳴管</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/Category:Regulus_regulus</t>
+        </is>
+      </c>
+      <c r="O262" t="inlineStr">
+        <is>
+          <t>goldcr1</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>B099</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>キレンジャク</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>脊索動物門</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>鳥綱</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>スズメ目</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>レンジャク科</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>チリリリリ</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>鳴管</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/Category:Bombycilla_japonica</t>
+        </is>
+      </c>
+      <c r="O263" t="inlineStr">
+        <is>
+          <t>japwax1</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>B108</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>イカル</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>脊索動物門</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>鳥綱</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>スズメ目</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>アトリ科</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>キーコーキー</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>鳴管</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/Category:Eophona_personata</t>
+        </is>
+      </c>
+      <c r="O264" t="inlineStr">
+        <is>
+          <t>japgro1</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>B111</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>セグロセキレイ</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>脊索動物門</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>鳥綱</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>スズメ目</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>セキレイ科</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>ジジッ ジジッ</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>鳴管</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/Category:Motacilla_grandis</t>
+        </is>
+      </c>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>japwag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>B112</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>キセキレイ</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>脊索動物門</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>鳥綱</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>スズメ目</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>セキレイ科</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>チチン チチン</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>鳴管</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/Category:Motacilla_cinerea</t>
+        </is>
+      </c>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>grywag</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>B113</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>トラツグミ</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>脊索動物門</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>鳥綱</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>スズメ目</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>ヒタキ科</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>ヒー ヒョー</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>鳴管</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/Category:Zoothera_dauma</t>
+        </is>
+      </c>
+      <c r="O267" t="inlineStr">
+        <is>
+          <t>scathr8</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>B115</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>コサメビタキ</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>脊索動物門</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>鳥綱</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>スズメ目</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>ヒタキ科</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>チチチチチ</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>鳴管</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/Category:Muscicapa_dauurica</t>
+        </is>
+      </c>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>asbfly</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>B116</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>カナリア</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>脊索動物門</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>鳥綱</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>スズメ目</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>アトリ科</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>ピロロロロ</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>鳴管</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/Category:Serinus_canaria</t>
+        </is>
+      </c>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>comcan</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>B117</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>オニオオハシ</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>脊索動物門</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>鳥綱</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>キツツキ目</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>オオハシ科</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>グワッグワッ</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>鳴管</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/Category:Ramphastos_toco</t>
+        </is>
+      </c>
+      <c r="O270" t="inlineStr">
+        <is>
+          <t>toctou1</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>B118</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>ノドアカハチドリ</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>脊索動物門</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>鳥綱</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>アマツバメ目</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>ハチドリ科</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>チッチッチッ</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>鳴管</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/Category:Archilochus_colubris</t>
+        </is>
+      </c>
+      <c r="O271" t="inlineStr">
+        <is>
+          <t>rthhum</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>B119</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>キバタン</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>脊索動物門</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>鳥綱</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>オウム目</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>オウム科</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>ギャーギャー</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>鳴管</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/Category:Cacatua_galerita</t>
+        </is>
+      </c>
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>succoc</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>B120</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>ヨウム</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>脊索動物門</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>鳥綱</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>オウム目</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>インコ科</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>ピーヨ</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>鳴管</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/Category:Psittacus_erithacus</t>
+        </is>
+      </c>
+      <c r="O273" t="inlineStr">
+        <is>
+          <t>grepar</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>B121</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>ハクチョウ（コハクチョウ）</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>脊索動物門</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>鳥綱</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>カモ目</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>カモ科</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>コォー コォー</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>鳴管</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/Category:Cygnus_columbianus</t>
+        </is>
+      </c>
+      <c r="O274" t="inlineStr">
+        <is>
+          <t>tunswa</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>B122</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>アカショウビン</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>脊索動物門</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>鳥綱</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>ブッポウソウ目</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>カワセミ科</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>キョロロロロ</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>鳴管</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/Category:Halcyon_coromanda</t>
+        </is>
+      </c>
+      <c r="O275" t="inlineStr">
+        <is>
+          <t>rudkin1</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>M069</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>ジャガー</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>脊索動物門</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>哺乳綱</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>ネコ目</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>ネコ科</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>ガウッ ガウッ</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>喉</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/Category:Panthera_onca</t>
+        </is>
+      </c>
+      <c r="O276" t="inlineStr">
+        <is>
+          <t>t-11032765</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>M070</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>ヒョウ</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>脊索動物門</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>哺乳綱</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>ネコ目</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>ネコ科</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>ゴロゴロ ガウ</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>喉</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/Category:Panthera_pardus</t>
+        </is>
+      </c>
+      <c r="O277" t="inlineStr">
+        <is>
+          <t>t-11034447</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>M071</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>シマリス</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>脊索動物門</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>哺乳綱</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>ネズミ目</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>リス科</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>チチチチ</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>喉</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/Category:Tamias_sibiricus</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>M073</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>ミーアキャット</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>脊索動物門</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>哺乳綱</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>ネコ目</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>マングース科</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>ワッワッワッ</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>喉</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/Category:Suricata_suricatta</t>
+        </is>
+      </c>
+      <c r="O279" t="inlineStr">
+        <is>
+          <t>t-12076818</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>M074</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>ナマケモノ（フタユビナマケモノ）</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>脊索動物門</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>哺乳綱</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>有毛目</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>フタユビナマケモノ科</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>アーアー</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>喉</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/Category:Choloepus_didactylus</t>
+        </is>
+      </c>
+      <c r="O280" t="inlineStr">
+        <is>
+          <t>t-12080011</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>M075</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>フェネック</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>脊索動物門</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>哺乳綱</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>ネコ目</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>イヌ科</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>キャンキャン</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>喉</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/Category:Vulpes_zerda</t>
+        </is>
+      </c>
+      <c r="O281" t="inlineStr">
+        <is>
+          <t>t-12076852</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>M076</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>スカンク（シマスカンク）</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>脊索動物門</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>哺乳綱</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>ネコ目</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>スカンク科</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>シャーッ</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>喉</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/Category:Mephitis_mephitis</t>
+        </is>
+      </c>
+      <c r="O282" t="inlineStr">
+        <is>
+          <t>t-11033627</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>M077</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>マナティー</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>脊索動物門</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>哺乳綱</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>海牛目</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>マナティー科</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>キュー</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>喉</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/Category:Trichechus_manatus</t>
+        </is>
+      </c>
+      <c r="O283" t="inlineStr">
+        <is>
+          <t>t-11027779</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>M079</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>コヨーテ</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>脊索動物門</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>哺乳綱</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>ネコ目</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>イヌ科</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>ワォーン キャンキャン</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>喉</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/Category:Canis_latrans</t>
+        </is>
+      </c>
+      <c r="O284" t="inlineStr">
+        <is>
+          <t>t-11031961</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>M080</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>カワウソ（ユーラシアカワウソ）</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>脊索動物門</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>哺乳綱</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>ネコ目</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>イタチ科</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>キュッキュッ</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>喉</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/Category:Lutra_lutra</t>
+        </is>
+      </c>
+      <c r="O285" t="inlineStr">
+        <is>
+          <t>t-12076765</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>M081</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>オランウータン</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>脊索動物門</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>哺乳綱</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>サル目</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>ヒト科</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>ウォォォーン</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>喉（喉袋共鳴）</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/Category:Pongo_pygmaeus</t>
+        </is>
+      </c>
+      <c r="O286" t="inlineStr">
+        <is>
+          <t>t-11062383</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>I043</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>カマキリ（オオカマキリ）</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>節足動物門</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>昆虫綱</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>カマキリ目</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>カマキリ科</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>シュー</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>翅摩擦</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/Category:Tenodera_sinensis</t>
+        </is>
+      </c>
+      <c r="O287" t="inlineStr">
+        <is>
+          <t>t-12898292</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>I044</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>ケラ（オケラ）</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>節足動物門</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>昆虫綱</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>バッタ目</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>ケラ科</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>ジーーー</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>翅摩擦</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/Category:Gryllotalpa_orientalis</t>
+        </is>
+      </c>
+      <c r="O288" t="inlineStr">
+        <is>
+          <t>t-12112003</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>F030</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>アフリカウシガエル</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>脊索動物門</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>両生綱</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>カエル目</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>アカガエル科</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>ウォーウォー</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>鳴嚢共鳴</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/Category:Pyxicephalus_adspersus</t>
+        </is>
+      </c>
+      <c r="O289" t="inlineStr">
+        <is>
+          <t>t-11119234</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>F033</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>ナガレタゴガエル</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>脊索動物門</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>両生綱</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>カエル目</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>アカガエル科</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>グッグッグッ</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>鳴嚢共鳴</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/Category:Rana_sakuraii</t>
+        </is>
+      </c>
+      <c r="O290" t="inlineStr">
+        <is>
+          <t>t-12089324</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>R015</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>グリーンイグアナ</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>脊索動物門</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>爬虫綱</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>有鱗目</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>イグアナ科</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>シュー フッ</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>喉・鼻</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/Category:Iguana_iguana</t>
+        </is>
+      </c>
+      <c r="O291" t="inlineStr">
+        <is>
+          <t>t-11768396</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>R016</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>ガラガラヘビ（ヒガシダイヤガラガラヘビ）</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>脊索動物門</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>爬虫綱</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>有鱗目</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>クサリヘビ科</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>シャカシャカ</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>尾の発音器</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/Category:Crotalus_adamanteus</t>
+        </is>
+      </c>
+      <c r="O292" t="inlineStr">
+        <is>
+          <t>t-11774507</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>R017</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>ミシシッピアカミミガメ</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>脊索動物門</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>爬虫綱</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>カメ目</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>ヌマガメ科</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>シュー</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>喉・鼻</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/Category:Trachemys_scripta_elegans</t>
+        </is>
+      </c>
+      <c r="O293" t="inlineStr">
+        <is>
+          <t>t-12104897</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>R018</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>ヒョウモントカゲモドキ</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>脊索動物門</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>爬虫綱</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>有鱗目</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>トカゲモドキ科</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>キュッ</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>喉</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/Category:Eublepharis_macularius</t>
+        </is>
+      </c>
+      <c r="O294" t="inlineStr">
+        <is>
+          <t>t-12101026</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>R019</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>ガビアル（インドガビアル）</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>脊索動物門</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>爬虫綱</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>ワニ目</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>ガビアル科</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>ブーーン</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>喉</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/Category:Gavialis_gangeticus</t>
+        </is>
+      </c>
+      <c r="O295" t="inlineStr">
+        <is>
+          <t>t-12111825</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>R020</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>エリマキトカゲ</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>脊索動物門</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>爬虫綱</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>有鱗目</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>アガマ科</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>シャーッ</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>喉・鼻</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/Category:Chlamydosaurus_kingii</t>
+        </is>
+      </c>
+      <c r="O296" t="inlineStr">
+        <is>
+          <t>t-12098690</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>S013</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>ナマズ（マナマズ）</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>脊索動物門</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>条鰭綱</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>ナマズ目</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>ナマズ科</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>グーグー</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>浮袋振動</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/Category:Silurus_asotus</t>
+        </is>
+      </c>
+      <c r="O297" t="inlineStr">
+        <is>
+          <t>t-12909923</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>S014</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>シログチ</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>脊索動物門</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>条鰭綱</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>スズキ目</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>ニベ科</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>グーグー</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>浮袋振動</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/Category:Pennahia_argentata</t>
+        </is>
+      </c>
+      <c r="O298" t="inlineStr">
+        <is>
+          <t>t-12910911</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>S016</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>コイ</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>脊索動物門</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>条鰭綱</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>コイ目</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>コイ科</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>パクパク</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>咽頭歯</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/Category:Cyprinus_carpio</t>
+        </is>
+      </c>
+      <c r="O299" t="inlineStr">
+        <is>
+          <t>t-10944174</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>S017</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>ハコフグ</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>脊索動物門</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>条鰭綱</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>フグ目</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>ハコフグ科</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>ブッブッ</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>浮袋振動</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/Category:Ostracion_cubicus</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>S018</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>タチウオ</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>脊索動物門</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>条鰭綱</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>スズキ目</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>タチウオ科</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>ギリギリ</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>歯ぎしり</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/Category:Trichiurus_lepturus</t>
+        </is>
+      </c>
+      <c r="O301" t="inlineStr">
+        <is>
+          <t>t-12896576</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>V008</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>ヤドカリ（オカヤドカリ）</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>節足動物門</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>軟甲綱</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>エビ目</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>オカヤドカリ科</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>ギチギチ</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>殻摩擦</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/Category:Coenobita_rugosus</t>
+        </is>
+      </c>
+      <c r="O302" t="inlineStr">
+        <is>
+          <t>t-12906573</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>V009</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>カタツムリ（ミスジマイマイ）</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>軟体動物門</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>腹足綱</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>柄眼目</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>オナジマイマイ科</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>ネチネチ</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>摂食音</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/Category:Euhadra_peliomphala</t>
+        </is>
+      </c>
+      <c r="O303" t="inlineStr">
+        <is>
+          <t>t-12476790</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>V010</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>ザリガニ（アメリカザリガニ）</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>節足動物門</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>軟甲綱</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>エビ目</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>アメリカザリガニ科</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>キチキチ</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>鋏摩擦</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/Category:Procambarus_clarkii</t>
+        </is>
+      </c>
+      <c r="O304" t="inlineStr">
+        <is>
+          <t>t-12896537</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>V011</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>ダンゴムシ</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>節足動物門</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>軟甲綱</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>ワラジムシ目</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>オカダンゴムシ科</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/Category:Armadillidium_vulgare</t>
+        </is>
+      </c>
+      <c r="O305" t="inlineStr">
+        <is>
+          <t>t-12897119</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>V012</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>セミクジラ（イワシクジラ）</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>脊索動物門</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>哺乳綱</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>鯨偶蹄目</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>ナガスクジラ科</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>ウォーーン</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>喉</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/Category:Balaenoptera_borealis</t>
+        </is>
+      </c>
+      <c r="O306" t="inlineStr">
+        <is>
+          <t>t-11032802</t>
         </is>
       </c>
     </row>
@@ -19973,7 +22867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F259"/>
+  <dimension ref="A1:F306"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -20649,7 +23543,11 @@
           <t>Long-tailed tit</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr"/>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>シマエナガ</t>
+        </is>
+      </c>
       <c r="F26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
@@ -26737,6 +29635,1125 @@
       <c r="D259" t="inlineStr">
         <is>
           <t>Ornate Narrow-mouth Frog</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>B096</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>ツグミ</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Turdus naumanni</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Naumann's thrush</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>B097</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>シロハラ</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Turdus pallidus</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Pale thrush</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>B098</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>キクイタダキ</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Goldcrest</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>B099</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>キレンジャク</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Bombycilla japonica</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Japanese waxwing</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>B108</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>イカル</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Eophona personata</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Japanese grosbeak</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>B111</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>セグロセキレイ</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Motacilla grandis</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Japanese wagtail</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>B112</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>キセキレイ</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Motacilla cinerea</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Grey wagtail</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>B113</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>トラツグミ</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Zoothera dauma</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Scaly thrush</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>鵺（ぬえ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>B115</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>コサメビタキ</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Muscicapa dauurica</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Asian brown flycatcher</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>B116</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>カナリア</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Serinus canaria</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Atlantic canary</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>B117</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>オニオオハシ</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Ramphastos toco</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Toco toucan</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>B118</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>ノドアカハチドリ</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Archilochus colubris</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Ruby-throated hummingbird</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>B119</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>キバタン</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Cacatua galerita</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Sulphur-crested cockatoo</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>B120</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>ヨウム</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Psittacus erithacus</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Grey parrot</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>B121</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>ハクチョウ（コハクチョウ）</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Cygnus columbianus</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Tundra swan</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>コハクチョウ</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>B122</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>アカショウビン</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Halcyon coromanda</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Ruddy kingfisher</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>M069</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>ジャガー</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Panthera onca</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Jaguar</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>M070</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>ヒョウ</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Panthera pardus</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Leopard</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>M071</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>シマリス</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Tamias sibiricus</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Siberian chipmunk</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>M073</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>ミーアキャット</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Suricata suricatta</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Meerkat</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>M074</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>ナマケモノ（フタユビナマケモノ）</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Choloepus didactylus</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Linnaeus's two-toed sloth</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>フタユビナマケモノ</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>M075</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>フェネック</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Vulpes zerda</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Fennec fox</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>M076</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>スカンク（シマスカンク）</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Mephitis mephitis</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Striped skunk</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>シマスカンク</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>M077</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>マナティー</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Trichechus manatus</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>West Indian manatee</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>M079</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>コヨーテ</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Canis latrans</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Coyote</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>M080</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>カワウソ（ユーラシアカワウソ）</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Lutra lutra</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Eurasian otter</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>ユーラシアカワウソ</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>M081</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>オランウータン</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Pongo pygmaeus</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Bornean orangutan</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>I043</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>カマキリ（オオカマキリ）</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Tenodera sinensis</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Chinese mantis</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>オオカマキリ</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>I044</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>ケラ（オケラ）</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Gryllotalpa orientalis</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Oriental mole cricket</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>オケラ</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>F030</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>アフリカウシガエル</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Pyxicephalus adspersus</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>African bullfrog</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>F033</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>ナガレタゴガエル</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Rana sakuraii</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Sakurai's brown frog</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>R015</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>グリーンイグアナ</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Iguana iguana</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Green iguana</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>R016</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>ガラガラヘビ（ヒガシダイヤガラガラヘビ）</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Crotalus adamanteus</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Eastern diamondback rattlesnake</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>ヒガシダイヤガラガラヘビ</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>R017</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>ミシシッピアカミミガメ</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Trachemys scripta elegans</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>Red-eared slider</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>ミドリガメ</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>R018</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>ヒョウモントカゲモドキ</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Eublepharis macularius</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>Leopard gecko</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>レオパ</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>R019</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>ガビアル（インドガビアル）</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Gavialis gangeticus</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>Gharial</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>インドガビアル</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>R020</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>エリマキトカゲ</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Chlamydosaurus kingii</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>Frilled-neck lizard</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>S013</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>ナマズ（マナマズ）</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Silurus asotus</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>Amur catfish</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>マナマズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>S014</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>シログチ</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Pennahia argentata</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>Silver croaker</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>イシモチ</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>S016</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>コイ</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Cyprinus carpio</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>Common carp</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>S017</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>ハコフグ</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Ostracion cubicus</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>Yellow boxfish</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>S018</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>タチウオ</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Trichiurus lepturus</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>Largehead hairtail</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>V008</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>ヤドカリ（オカヤドカリ）</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Coenobita rugosus</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>Rugose land hermit crab</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>オカヤドカリ</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>V009</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>カタツムリ（ミスジマイマイ）</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Euhadra peliomphala</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>Misuji-maimai snail</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>ミスジマイマイ</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>V010</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>ザリガニ（アメリカザリガニ）</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Procambarus clarkii</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>Red swamp crayfish</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>アメリカザリガニ</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>V011</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>ダンゴムシ</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Armadillidium vulgare</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>Common pill-bug</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>V012</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>セミクジラ（イワシクジラ）</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Balaenoptera borealis</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>Sei whale</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>イワシクジラ</t>
         </is>
       </c>
     </row>
@@ -31554,7 +35571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G573"/>
+  <dimension ref="A1:G665"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -47932,6 +51949,2950 @@
       <c r="E573" t="inlineStr">
         <is>
           <t>哞哞</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>B096</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>ツグミ</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>クィクィ</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>地鳴き</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>B096</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>ツグミ</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>英語</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>Kwee-kwee</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>B097</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>シロハラ</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>ツィー</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>地鳴き</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>B097</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>シロハラ</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>英語</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>Tsee</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>B098</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>キクイタダキ</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>ツィツィツィ</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>さえずり</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>B098</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>キクイタダキ</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>英語</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>Tsee-tsee-tsee</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>song</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>B099</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>キレンジャク</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>チリリリリ</t>
+        </is>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>さえずり</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>B099</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>キレンジャク</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>英語</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>Triiiii</t>
+        </is>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>B108</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>イカル</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>キーコーキー</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>さえずり</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>B108</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>イカル</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>英語</t>
+        </is>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>Kee-ko-kee</t>
+        </is>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>song</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>B111</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>セグロセキレイ</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>ジジッ ジジッ</t>
+        </is>
+      </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>地鳴き</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>B111</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>セグロセキレイ</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>英語</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>Jit-jit</t>
+        </is>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>B112</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>キセキレイ</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>チチン チチン</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>地鳴き</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>B112</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>キセキレイ</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>英語</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>Chisit</t>
+        </is>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>B113</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>トラツグミ</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>ヒー ヒョー</t>
+        </is>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>夜間さえずり</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>B113</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>トラツグミ</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>英語</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>Hee hyoo</t>
+        </is>
+      </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>night song</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>B115</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>コサメビタキ</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>チチチチチ</t>
+        </is>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>さえずり</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>B115</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>コサメビタキ</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>英語</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>Chi-chi-chi-chi</t>
+        </is>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>song</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>B116</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>カナリア</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>ピロロロロ</t>
+        </is>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>さえずり</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>B116</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>カナリア</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>英語</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>Tweet-tweet-tweet</t>
+        </is>
+      </c>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>song</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>B117</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>オニオオハシ</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>グワッグワッ</t>
+        </is>
+      </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>さえずり</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>B117</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>オニオオハシ</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>英語</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>Grrawk-grrawk</t>
+        </is>
+      </c>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>B118</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>ノドアカハチドリ</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>チッチッチッ</t>
+        </is>
+      </c>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t>地鳴き</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>B118</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>ノドアカハチドリ</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>英語</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>Chit-chit-chit</t>
+        </is>
+      </c>
+      <c r="F597" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>B119</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>キバタン</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>ギャーギャー</t>
+        </is>
+      </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>地鳴き</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>B119</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>キバタン</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>英語</t>
+        </is>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>Screeech</t>
+        </is>
+      </c>
+      <c r="F599" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>B120</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>ヨウム</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>ピーヨ</t>
+        </is>
+      </c>
+      <c r="F600" t="inlineStr">
+        <is>
+          <t>地鳴き</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>B120</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>ヨウム</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>英語</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>Whistle</t>
+        </is>
+      </c>
+      <c r="F601" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>B121</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>ハクチョウ（コハクチョウ）</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>コォー コォー</t>
+        </is>
+      </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>群鳴き</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>B121</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>ハクチョウ（コハクチョウ）</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>英語</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>Koo-koo</t>
+        </is>
+      </c>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>flocking call</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>B122</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>アカショウビン</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>キョロロロロ</t>
+        </is>
+      </c>
+      <c r="F604" t="inlineStr">
+        <is>
+          <t>さえずり</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>B122</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>アカショウビン</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>英語</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>Kyorororo</t>
+        </is>
+      </c>
+      <c r="F605" t="inlineStr">
+        <is>
+          <t>song</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>M069</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>ジャガー</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>ガウッ ガウッ</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>威嚇</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>M069</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>ジャガー</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>英語</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>Saw-like roar</t>
+        </is>
+      </c>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>territorial call</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>M070</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>ヒョウ</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>ゴロゴロ ガウ</t>
+        </is>
+      </c>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>威嚇</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>M070</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>ヒョウ</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>英語</t>
+        </is>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>Rasping cough</t>
+        </is>
+      </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>M071</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>シマリス</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>チチチチ</t>
+        </is>
+      </c>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>警戒音</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>M071</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>シマリス</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>英語</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>Chip-chip-chip</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>alarm call</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>M073</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>ミーアキャット</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>ワッワッワッ</t>
+        </is>
+      </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>警戒音</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>M073</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>ミーアキャット</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>英語</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>Bark-bark</t>
+        </is>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>sentinel alarm</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>M074</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>ナマケモノ（フタユビナマケモノ）</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>アーアー</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>鳴き声</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>M074</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>ナマケモノ（フタユビナマケモノ）</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>英語</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>Aah-aah</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>M075</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>フェネック</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>キャンキャン</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>鳴き声</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>M075</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>フェネック</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>英語</t>
+        </is>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>Yip-yip</t>
+        </is>
+      </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>bark</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>M076</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>スカンク（シマスカンク）</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>シャーッ</t>
+        </is>
+      </c>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>威嚇</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>M076</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>スカンク（シマスカンク）</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>英語</t>
+        </is>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>Hiss-stomp</t>
+        </is>
+      </c>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>M077</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>マナティー</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>キュー</t>
+        </is>
+      </c>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>コミュニケーション</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>M077</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>マナティー</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>英語</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>Squeak-squeal</t>
+        </is>
+      </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>communication</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>M079</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>コヨーテ</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>ワォーン キャンキャン</t>
+        </is>
+      </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>遠吠え</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>M079</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>コヨーテ</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>英語</t>
+        </is>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>Yip-howl</t>
+        </is>
+      </c>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>group howl</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>M080</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>カワウソ（ユーラシアカワウソ）</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>キュッキュッ</t>
+        </is>
+      </c>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t>コミュニケーション</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>M080</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>カワウソ（ユーラシアカワウソ）</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>英語</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>Chirp-chirp</t>
+        </is>
+      </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>contact call</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>M081</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>オランウータン</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>ウォォォーン</t>
+        </is>
+      </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>ロングコール</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>M081</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>オランウータン</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>英語</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>Long call</t>
+        </is>
+      </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>territorial long call</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>I043</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>カマキリ（オオカマキリ）</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>シュー</t>
+        </is>
+      </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>威嚇音</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>I043</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>カマキリ（オオカマキリ）</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>英語</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>Hiss</t>
+        </is>
+      </c>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>threat display</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>I044</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>ケラ（オケラ）</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>ジーーー</t>
+        </is>
+      </c>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>鳴き声</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>I044</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>ケラ（オケラ）</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>英語</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>Jeeee</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>F030</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>アフリカウシガエル</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>ウォーウォー</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>繁殖期</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>F030</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>アフリカウシガエル</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>英語</t>
+        </is>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>Whoop-whoop</t>
+        </is>
+      </c>
+      <c r="F633" t="inlineStr">
+        <is>
+          <t>breeding call</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>F033</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>ナガレタゴガエル</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>グッグッグッ</t>
+        </is>
+      </c>
+      <c r="F634" t="inlineStr">
+        <is>
+          <t>繁殖期</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>F033</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>ナガレタゴガエル</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>英語</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>Guk-guk-guk</t>
+        </is>
+      </c>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>breeding call</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>R015</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>グリーンイグアナ</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>シュー フッ</t>
+        </is>
+      </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>威嚇</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>R015</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>グリーンイグアナ</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>英語</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>Hiss-huff</t>
+        </is>
+      </c>
+      <c r="F637" t="inlineStr">
+        <is>
+          <t>threat display</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>R016</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>ガラガラヘビ（ヒガシダイヤガラガラヘビ）</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>シャカシャカ</t>
+        </is>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>威嚇</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>R016</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>ガラガラヘビ（ヒガシダイヤガラガラヘビ）</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>英語</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>Rattle-rattle</t>
+        </is>
+      </c>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>warning rattle</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>R017</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>ミシシッピアカミミガメ</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>シュー</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>威嚇</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>R017</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>ミシシッピアカミミガメ</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>英語</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>Hiss</t>
+        </is>
+      </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>threat display</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>R018</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>ヒョウモントカゲモドキ</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>キュッ</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>鳴き声</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>R018</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>ヒョウモントカゲモドキ</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>英語</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>Chirp</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>vocalization</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>R019</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>ガビアル（インドガビアル）</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>ブーーン</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>繁殖期</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>R019</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>ガビアル（インドガビアル）</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>英語</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>Buzz-hiss</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>breeding call</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>R020</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>エリマキトカゲ</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>シャーッ</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>威嚇</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>R020</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>エリマキトカゲ</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>英語</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>Hiss</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>threat display</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>S013</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>ナマズ（マナマズ）</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>グーグー</t>
+        </is>
+      </c>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>鳴き声</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>S013</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>ナマズ（マナマズ）</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>英語</t>
+        </is>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>Grunt-grunt</t>
+        </is>
+      </c>
+      <c r="F649" t="inlineStr">
+        <is>
+          <t>drumming</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>S014</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>シログチ</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>グーグー</t>
+        </is>
+      </c>
+      <c r="F650" t="inlineStr">
+        <is>
+          <t>鳴き声</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>S014</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>シログチ</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>英語</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>Croak-croak</t>
+        </is>
+      </c>
+      <c r="F651" t="inlineStr">
+        <is>
+          <t>drumming</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>S016</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>コイ</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>パクパク</t>
+        </is>
+      </c>
+      <c r="F652" t="inlineStr">
+        <is>
+          <t>摂餌音</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>S016</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>コイ</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>英語</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>Gulp-gulp</t>
+        </is>
+      </c>
+      <c r="F653" t="inlineStr">
+        <is>
+          <t>feeding sound</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>S017</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>ハコフグ</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>ブッブッ</t>
+        </is>
+      </c>
+      <c r="F654" t="inlineStr">
+        <is>
+          <t>鳴き声</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>S017</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>ハコフグ</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>英語</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>Bub-bub</t>
+        </is>
+      </c>
+      <c r="F655" t="inlineStr">
+        <is>
+          <t>drumming</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>S018</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>タチウオ</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>ギリギリ</t>
+        </is>
+      </c>
+      <c r="F656" t="inlineStr">
+        <is>
+          <t>摂餌音</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>S018</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>タチウオ</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>英語</t>
+        </is>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>Grinding</t>
+        </is>
+      </c>
+      <c r="F657" t="inlineStr">
+        <is>
+          <t>feeding sound</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>V008</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>ヤドカリ（オカヤドカリ）</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>ギチギチ</t>
+        </is>
+      </c>
+      <c r="F658" t="inlineStr">
+        <is>
+          <t>威嚇</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>V008</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>ヤドカリ（オカヤドカリ）</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>英語</t>
+        </is>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>Chirp-chirp</t>
+        </is>
+      </c>
+      <c r="F659" t="inlineStr">
+        <is>
+          <t>stridulation</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>V009</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>カタツムリ（ミスジマイマイ）</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>ネチネチ</t>
+        </is>
+      </c>
+      <c r="F660" t="inlineStr">
+        <is>
+          <t>摂食音</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>V009</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>カタツムリ（ミスジマイマイ）</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>英語</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>Munch-munch</t>
+        </is>
+      </c>
+      <c r="F661" t="inlineStr">
+        <is>
+          <t>feeding sound</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>V010</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>ザリガニ（アメリカザリガニ）</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>キチキチ</t>
+        </is>
+      </c>
+      <c r="F662" t="inlineStr">
+        <is>
+          <t>威嚇</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>V010</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>ザリガニ（アメリカザリガニ）</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>英語</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>Click-click</t>
+        </is>
+      </c>
+      <c r="F663" t="inlineStr">
+        <is>
+          <t>claw snap</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>V012</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>セミクジラ（イワシクジラ）</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>ウォーーン</t>
+        </is>
+      </c>
+      <c r="F664" t="inlineStr">
+        <is>
+          <t>コミュニケーション</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>V012</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>セミクジラ（イワシクジラ）</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>英語</t>
+        </is>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>Low moan</t>
+        </is>
+      </c>
+      <c r="F665" t="inlineStr">
+        <is>
+          <t>contact call</t>
         </is>
       </c>
     </row>
@@ -49292,7 +56253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D401"/>
+  <dimension ref="A1:D494"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -58058,6 +65019,1587 @@
         </is>
       </c>
     </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>B096</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>ツグミ</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>REG01</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>B096</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>ツグミ</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>REG02</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>B096</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>ツグミ</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>REG03</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>B097</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>シロハラ</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>REG01</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>B097</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>シロハラ</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>REG02</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>B097</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>シロハラ</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>REG03</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>B098</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>キクイタダキ</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>REG01</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>B098</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>キクイタダキ</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>REG08</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>B099</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>キレンジャク</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>REG01</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>B099</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>キレンジャク</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>REG02</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>B099</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>キレンジャク</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>REG07</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>B108</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>イカル</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>REG01</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>B108</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>イカル</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>REG02</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>B108</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>イカル</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>REG03</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>B111</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>セグロセキレイ</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>REG01</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>B112</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>キセキレイ</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>REG01</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>B112</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>キセキレイ</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>REG08</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>B113</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>トラツグミ</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>REG01</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>B113</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>トラツグミ</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>REG03</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>B113</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>トラツグミ</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>REG05</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>B115</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>コサメビタキ</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>REG01</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>B115</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>コサメビタキ</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>REG02</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>B115</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>コサメビタキ</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>REG03</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>B116</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>カナリア</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>REG20</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>B117</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>オニオオハシ</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>REG14</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>B118</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>ノドアカハチドリ</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>REG12</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>B119</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>キバタン</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>REG15</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>B119</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>キバタン</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>REG16</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>B119</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>キバタン</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>REG26</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>B120</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>ヨウム</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>REG11</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>B121</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>ハクチョウ（コハクチョウ）</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>REG01</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>B121</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>ハクチョウ（コハクチョウ）</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>REG02</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>B121</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>ハクチョウ（コハクチョウ）</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>REG07</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>B121</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>ハクチョウ（コハクチョウ）</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>REG08</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>B121</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>ハクチョウ（コハクチョウ）</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>REG12</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>B122</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>アカショウビン</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>REG01</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>B122</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>アカショウビン</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>REG03</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>B122</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>アカショウビン</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>REG05</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>M069</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>ジャガー</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>REG13</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>M069</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>ジャガー</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>REG14</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>M070</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>ヒョウ</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>REG04</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>M070</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>ヒョウ</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>REG05</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>M070</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>ヒョウ</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>REG10</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>M070</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>ヒョウ</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>REG11</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>M071</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>シマリス</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>REG01</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>M071</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>シマリス</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>REG02</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>M071</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>シマリス</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>REG07</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>M073</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>ミーアキャット</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>REG10</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>M074</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>ナマケモノ（フタユビナマケモノ）</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>REG14</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>M075</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>フェネック</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>REG09</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>M076</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>スカンク（シマスカンク）</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>REG12</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>M077</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>マナティー</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>REG13</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>M079</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>コヨーテ</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>REG12</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>M080</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>カワウソ（ユーラシアカワウソ）</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>REG08</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>M080</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>カワウソ（ユーラシアカワウソ）</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>REG02</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>M081</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>オランウータン</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>REG06</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>I043</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>カマキリ（オオカマキリ）</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>REG01</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>I043</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>カマキリ（オオカマキリ）</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>REG03</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>I043</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>カマキリ（オオカマキリ）</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>REG12</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>I044</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>ケラ（オケラ）</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>REG01</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>I044</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>ケラ（オケラ）</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>REG03</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>F030</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>アフリカウシガエル</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>REG10</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>F033</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>ナガレタゴガエル</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>REG01</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>R015</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>グリーンイグアナ</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>REG13</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>R015</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>グリーンイグアナ</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>REG14</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>R016</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>ガラガラヘビ（ヒガシダイヤガラガラヘビ）</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>REG12</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>R017</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>ミシシッピアカミミガメ</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>REG12</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>R017</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>ミシシッピアカミミガメ</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>REG01</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>R018</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>ヒョウモントカゲモドキ</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>REG04</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>R018</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>ヒョウモントカゲモドキ</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>REG05</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>R019</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>ガビアル（インドガビアル）</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>REG22</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>R020</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>エリマキトカゲ</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>REG15</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>R020</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>エリマキトカゲ</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>REG16</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>S013</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>ナマズ（マナマズ）</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>REG01</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>S013</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>ナマズ（マナマズ）</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>REG03</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>S014</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>シログチ</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>REG01</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>S014</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>シログチ</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>REG03</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>S016</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>コイ</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>REG01</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>S016</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>コイ</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>REG08</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>S016</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>コイ</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>REG12</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>S017</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>ハコフグ</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>REG22</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>S017</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>ハコフグ</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>REG23</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>S018</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>タチウオ</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>REG01</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>S018</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>タチウオ</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>REG23</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>V008</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>ヤドカリ（オカヤドカリ）</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>REG22</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>V008</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>ヤドカリ（オカヤドカリ）</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>REG23</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>V009</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>カタツムリ（ミスジマイマイ）</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>REG01</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>V010</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>ザリガニ（アメリカザリガニ）</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>REG01</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>V010</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>ザリガニ（アメリカザリガニ）</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>REG12</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>V011</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>ダンゴムシ</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>REG01</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>V011</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>ダンゴムシ</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>REG08</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>V011</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>ダンゴムシ</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>REG12</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>V012</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>セミクジラ（イワシクジラ）</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>REG23</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D371"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/animal-sounds-data.xlsx
+++ b/data/animal-sounds-data.xlsx
@@ -22933,7 +22933,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>ニホンマカク</t>
+          <t>ニホンマカク, 日本猿</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -22963,7 +22963,11 @@
           <t>Large-billed crow</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>嘴太烏</t>
+        </is>
+      </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Jungle crow</t>
@@ -22991,7 +22995,11 @@
           <t>Japanese tree frog</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>日本雨蛙</t>
+        </is>
+      </c>
       <c r="F4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
@@ -23015,7 +23023,11 @@
           <t>Emma field cricket</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>閻魔蟋蟀</t>
+        </is>
+      </c>
       <c r="F5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
@@ -23039,7 +23051,11 @@
           <t>Loggerhead sea turtle</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>赤海亀</t>
+        </is>
+      </c>
       <c r="F6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
@@ -23063,7 +23079,11 @@
           <t>Eurasian tree sparrow</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr"/>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>雀</t>
+        </is>
+      </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Tree sparrow</t>
@@ -23091,7 +23111,11 @@
           <t>Carrion crow</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr"/>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>嘴細烏</t>
+        </is>
+      </c>
       <c r="F8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
@@ -23115,7 +23139,11 @@
           <t>Japanese bush warbler</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr"/>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>鶯</t>
+        </is>
+      </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Bush warbler</t>
@@ -23143,7 +23171,11 @@
           <t>Japanese white-eye</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr"/>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>目白</t>
+        </is>
+      </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
           <t>White-eye</t>
@@ -23171,7 +23203,11 @@
           <t>Japanese tit</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr"/>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>四十雀</t>
+        </is>
+      </c>
       <c r="F11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
@@ -23195,7 +23231,11 @@
           <t>Varied tit</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr"/>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>山雀</t>
+        </is>
+      </c>
       <c r="F12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
@@ -23219,7 +23259,11 @@
           <t>Eurasian skylark</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr"/>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>雲雀</t>
+        </is>
+      </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Skylark</t>
@@ -23247,7 +23291,11 @@
           <t>Barn swallow</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr"/>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>燕</t>
+        </is>
+      </c>
       <c r="F14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
@@ -23271,7 +23319,11 @@
           <t>Blue-and-white flycatcher</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr"/>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>大瑠璃</t>
+        </is>
+      </c>
       <c r="F15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
@@ -23295,7 +23347,11 @@
           <t>Japanese robin</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr"/>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>駒鳥</t>
+        </is>
+      </c>
       <c r="F16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
@@ -23319,7 +23375,11 @@
           <t>Daurian redstart</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr"/>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>尉鶲</t>
+        </is>
+      </c>
       <c r="F17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
@@ -23343,7 +23403,11 @@
           <t>Bull-headed shrike</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr"/>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>百舌鳥</t>
+        </is>
+      </c>
       <c r="F18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
@@ -23369,7 +23433,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>ハクセキレイ</t>
+          <t>ハクセキレイ, 鶺鴒</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr"/>
@@ -23395,7 +23459,11 @@
           <t>Oriental greenfinch</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr"/>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>河原鶸</t>
+        </is>
+      </c>
       <c r="F20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
@@ -23419,7 +23487,11 @@
           <t>Meadow bunting</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr"/>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>頬白</t>
+        </is>
+      </c>
       <c r="F21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
@@ -23443,7 +23515,11 @@
           <t>Eurasian jay</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr"/>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>懸巣</t>
+        </is>
+      </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Jay</t>
@@ -23471,7 +23547,11 @@
           <t>Azure-winged magpie</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr"/>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>尾長</t>
+        </is>
+      </c>
       <c r="F23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
@@ -23495,7 +23575,11 @@
           <t>Brown-eared bulbul</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr"/>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>鵯</t>
+        </is>
+      </c>
       <c r="F24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
@@ -23519,7 +23603,11 @@
           <t>White-cheeked starling</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr"/>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>椋鳥</t>
+        </is>
+      </c>
       <c r="F25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
@@ -23545,7 +23633,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>シマエナガ</t>
+          <t>シマエナガ, 柄長</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr"/>
@@ -23571,7 +23659,11 @@
           <t>Common kingfisher</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr"/>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>翡翠</t>
+        </is>
+      </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Kingfisher</t>
@@ -23599,7 +23691,11 @@
           <t>Japanese paradise flycatcher</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr"/>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>三光鳥</t>
+        </is>
+      </c>
       <c r="F28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
@@ -23623,7 +23719,11 @@
           <t>Blue rock thrush</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr"/>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>磯鵯</t>
+        </is>
+      </c>
       <c r="F29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
@@ -23647,7 +23747,11 @@
           <t>Eurasian wren</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr"/>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>鷦鷯</t>
+        </is>
+      </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Winter wren</t>
@@ -23675,7 +23779,11 @@
           <t>Green pheasant</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr"/>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>雉</t>
+        </is>
+      </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Japanese pheasant</t>
@@ -23703,7 +23811,11 @@
           <t>Copper pheasant</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr"/>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>山鳥</t>
+        </is>
+      </c>
       <c r="F32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
@@ -23727,7 +23839,11 @@
           <t>Rock ptarmigan</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr"/>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>雷鳥</t>
+        </is>
+      </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Ptarmigan</t>
@@ -23755,7 +23871,11 @@
           <t>Chinese bamboo partridge</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr"/>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>小綬鶏</t>
+        </is>
+      </c>
       <c r="F34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
@@ -23779,7 +23899,11 @@
           <t>Japanese quail</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr"/>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>鶉</t>
+        </is>
+      </c>
       <c r="F35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
@@ -23803,7 +23927,11 @@
           <t>Mallard</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr"/>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>真鴨</t>
+        </is>
+      </c>
       <c r="F36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
@@ -23827,7 +23955,11 @@
           <t>Mandarin duck</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr"/>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>鴛鴦</t>
+        </is>
+      </c>
       <c r="F37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
@@ -23853,7 +23985,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>オオハクチョウ</t>
+          <t>オオハクチョウ, 白鳥</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr"/>
@@ -23879,7 +24011,11 @@
           <t>Eastern spot-billed duck</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr"/>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>軽鴨</t>
+        </is>
+      </c>
       <c r="F39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
@@ -23903,7 +24039,11 @@
           <t>Eurasian teal</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr"/>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>小鴨</t>
+        </is>
+      </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Teal</t>
@@ -23933,7 +24073,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>ヤマバト</t>
+          <t>ヤマバト, 雉鳩</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr"/>
@@ -23961,7 +24101,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>カワラバト</t>
+          <t>カワラバト, 土鳩</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -23991,7 +24131,11 @@
           <t>White-bellied green pigeon</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr"/>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>青鳩</t>
+        </is>
+      </c>
       <c r="F43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
@@ -24015,7 +24159,11 @@
           <t>Northern goshawk</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr"/>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>大鷹</t>
+        </is>
+      </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Goshawk</t>
@@ -24045,7 +24193,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>トンビ</t>
+          <t>トンビ, 鳶</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -24075,7 +24223,11 @@
           <t>Japanese buzzard</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr"/>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>鵟</t>
+        </is>
+      </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Buzzard</t>
@@ -24103,7 +24255,11 @@
           <t>White-tailed eagle</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr"/>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>尾白鷲</t>
+        </is>
+      </c>
       <c r="F47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
@@ -24127,7 +24283,11 @@
           <t>Mountain hawk-eagle</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr"/>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>熊鷹</t>
+        </is>
+      </c>
       <c r="F48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
@@ -24151,7 +24311,11 @@
           <t>Ural owl</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr"/>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>梟</t>
+        </is>
+      </c>
       <c r="F49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
@@ -24175,7 +24339,11 @@
           <t>Brown hawk-owl</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr"/>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>青葉木菟</t>
+        </is>
+      </c>
       <c r="F50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
@@ -24199,7 +24367,11 @@
           <t>Eurasian scops owl</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr"/>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>木葉木菟</t>
+        </is>
+      </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Scops owl</t>
@@ -24227,7 +24399,11 @@
           <t>Blakiston's fish owl</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr"/>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>島梟</t>
+        </is>
+      </c>
       <c r="F52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
@@ -24251,7 +24427,11 @@
           <t>Common cuckoo</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr"/>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>郭公</t>
+        </is>
+      </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Cuckoo</t>
@@ -24279,7 +24459,11 @@
           <t>Lesser cuckoo</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr"/>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>杜鵑</t>
+        </is>
+      </c>
       <c r="F54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
@@ -24303,7 +24487,11 @@
           <t>Himalayan cuckoo</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr"/>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>筒鳥</t>
+        </is>
+      </c>
       <c r="F55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
@@ -24327,7 +24515,11 @@
           <t>Japanese green woodpecker</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr"/>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>青啄木鳥</t>
+        </is>
+      </c>
       <c r="F56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
@@ -24351,7 +24543,11 @@
           <t>Great spotted woodpecker</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr"/>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>赤啄木鳥</t>
+        </is>
+      </c>
       <c r="F57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
@@ -24375,7 +24571,11 @@
           <t>Japanese pygmy woodpecker</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr"/>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>小啄木鳥</t>
+        </is>
+      </c>
       <c r="F58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
@@ -24399,7 +24599,11 @@
           <t>Grey heron</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr"/>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>蒼鷺</t>
+        </is>
+      </c>
       <c r="F59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
@@ -24423,7 +24627,11 @@
           <t>Great egret</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr"/>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>大鷺</t>
+        </is>
+      </c>
       <c r="F60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
@@ -24447,7 +24655,11 @@
           <t>Black-crowned night heron</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr"/>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>五位鷺</t>
+        </is>
+      </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Night heron</t>
@@ -24475,7 +24687,11 @@
           <t>Red-crowned crane</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr"/>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>丹頂</t>
+        </is>
+      </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Japanese crane</t>
@@ -24503,7 +24719,11 @@
           <t>Hooded crane</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr"/>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>鍋鶴</t>
+        </is>
+      </c>
       <c r="F63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
@@ -24527,7 +24747,11 @@
           <t>Common moorhen</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr"/>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>鷭</t>
+        </is>
+      </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Moorhen</t>
@@ -24555,7 +24779,11 @@
           <t>Okinawa rail</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr"/>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>山原水鶏</t>
+        </is>
+      </c>
       <c r="F65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
@@ -24579,7 +24807,11 @@
           <t>Black-headed gull</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr"/>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>百合鷗</t>
+        </is>
+      </c>
       <c r="F66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
@@ -24603,7 +24835,11 @@
           <t>Black-tailed gull</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr"/>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>海猫</t>
+        </is>
+      </c>
       <c r="F67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
@@ -24627,7 +24863,11 @@
           <t>Little ringed plover</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr"/>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>小千鳥</t>
+        </is>
+      </c>
       <c r="F68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
@@ -24651,7 +24891,11 @@
           <t>Common snipe</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr"/>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>田鷸</t>
+        </is>
+      </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Snipe</t>
@@ -24679,7 +24923,11 @@
           <t>Oriental dollarbird</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr"/>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>仏法僧</t>
+        </is>
+      </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Dollarbird</t>
@@ -24707,7 +24955,11 @@
           <t>Crested kingfisher</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr"/>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>山翡翠</t>
+        </is>
+      </c>
       <c r="F71" s="2" t="inlineStr"/>
     </row>
     <row r="72">
@@ -24731,7 +24983,11 @@
           <t>Oriental stork</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr"/>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>鸛</t>
+        </is>
+      </c>
       <c r="F72" s="2" t="inlineStr"/>
     </row>
     <row r="73">
@@ -24755,7 +25011,11 @@
           <t>Little grebe</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr"/>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>鸊鷉</t>
+        </is>
+      </c>
       <c r="F73" s="2" t="inlineStr"/>
     </row>
     <row r="74">
@@ -24779,7 +25039,11 @@
           <t>Streaked shearwater</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr"/>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>大水薙鳥</t>
+        </is>
+      </c>
       <c r="F74" s="2" t="inlineStr"/>
     </row>
     <row r="75">
@@ -24827,7 +25091,11 @@
           <t>Eurasian hoopoe</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr"/>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>戴勝</t>
+        </is>
+      </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Hoopoe</t>
@@ -24855,7 +25123,11 @@
           <t>Pacific swift</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr"/>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>雨燕</t>
+        </is>
+      </c>
       <c r="F77" s="2" t="inlineStr"/>
     </row>
     <row r="78">
@@ -24879,7 +25151,11 @@
           <t>Chicken</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr"/>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>鶏</t>
+        </is>
+      </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Rooster/Hen</t>
@@ -24909,7 +25185,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>インドクジャク</t>
+          <t>インドクジャク, 孔雀</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -25107,7 +25383,11 @@
           <t>Japanese cormorant</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr"/>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>海鵜</t>
+        </is>
+      </c>
       <c r="F86" s="2" t="inlineStr"/>
     </row>
     <row r="87">
@@ -25131,7 +25411,11 @@
           <t>Brown dipper</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr"/>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>河烏</t>
+        </is>
+      </c>
       <c r="F87" s="2" t="inlineStr"/>
     </row>
     <row r="88">
@@ -25155,7 +25439,11 @@
           <t>Narcissus flycatcher</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr"/>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>黄鶲</t>
+        </is>
+      </c>
       <c r="F88" s="2" t="inlineStr"/>
     </row>
     <row r="89">
@@ -25179,7 +25467,11 @@
           <t>Ashy minivet</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr"/>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>山椒喰</t>
+        </is>
+      </c>
       <c r="F89" s="2" t="inlineStr"/>
     </row>
     <row r="90">
@@ -25203,7 +25495,11 @@
           <t>Japanese leaf warbler</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr"/>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>目細虫喰</t>
+        </is>
+      </c>
       <c r="F90" s="2" t="inlineStr"/>
     </row>
     <row r="91">
@@ -25227,7 +25523,11 @@
           <t>Eastern crowned warbler</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr"/>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>仙台虫喰</t>
+        </is>
+      </c>
       <c r="F91" s="2" t="inlineStr"/>
     </row>
     <row r="92">
@@ -25251,7 +25551,11 @@
           <t>Oriental reed warbler</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr"/>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>大葦切</t>
+        </is>
+      </c>
       <c r="F92" s="2" t="inlineStr"/>
     </row>
     <row r="93">
@@ -25275,7 +25579,11 @@
           <t>Crested ibis</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr"/>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>朱鷺,鴇</t>
+        </is>
+      </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
           <t>Japanese crested ibis</t>
@@ -25303,7 +25611,11 @@
           <t>Bean goose</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr"/>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>菱喰</t>
+        </is>
+      </c>
       <c r="F94" s="2" t="inlineStr"/>
     </row>
     <row r="95">
@@ -25327,7 +25639,11 @@
           <t>Red-throated loon</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr"/>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>阿比</t>
+        </is>
+      </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
           <t>Loon</t>
@@ -25355,7 +25671,11 @@
           <t>Common ostrich</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr"/>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>駝鳥</t>
+        </is>
+      </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
           <t>Ostrich</t>
@@ -25469,7 +25789,7 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>イエイヌ</t>
+          <t>イエイヌ, 犬</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr"/>
@@ -25497,7 +25817,7 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>イエネコ</t>
+          <t>イエネコ, 猫</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr"/>
@@ -25523,7 +25843,11 @@
           <t>Lion</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr"/>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>獅子</t>
+        </is>
+      </c>
       <c r="F102" s="2" t="inlineStr"/>
     </row>
     <row r="103">
@@ -25547,7 +25871,11 @@
           <t>Tiger</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr"/>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>虎</t>
+        </is>
+      </c>
       <c r="F103" s="2" t="inlineStr"/>
     </row>
     <row r="104">
@@ -25573,7 +25901,7 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>ハイイロオオカミ</t>
+          <t>ハイイロオオカミ, 狼</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
@@ -25605,7 +25933,7 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>ホンドギツネ</t>
+          <t>ホンドギツネ, 狐</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
@@ -25635,7 +25963,11 @@
           <t>Raccoon dog</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr"/>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>狸</t>
+        </is>
+      </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
           <t>Tanuki</t>
@@ -25663,7 +25995,11 @@
           <t>Asian black bear</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr"/>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>月輪熊</t>
+        </is>
+      </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
           <t>Moon bear</t>
@@ -25691,7 +26027,11 @@
           <t>Brown bear</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr"/>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>羆</t>
+        </is>
+      </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
           <t>Grizzly bear</t>
@@ -25721,7 +26061,7 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>シロクマ</t>
+          <t>シロクマ, 北極熊,白熊</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr"/>
@@ -25779,7 +26119,11 @@
           <t>Japanese otter</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr"/>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>日本川獺</t>
+        </is>
+      </c>
       <c r="F111" s="2" t="inlineStr"/>
     </row>
     <row r="112">
@@ -25803,7 +26147,11 @@
           <t>Sea otter</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr"/>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>海獺,猟虎</t>
+        </is>
+      </c>
       <c r="F112" s="2" t="inlineStr"/>
     </row>
     <row r="113">
@@ -25829,7 +26177,7 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>ゴマフアザラシ</t>
+          <t>ゴマフアザラシ, 海豹</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr"/>
@@ -25857,7 +26205,7 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>ニホンアシカ</t>
+          <t>ニホンアシカ, 海驢,葦鹿</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr"/>
@@ -25883,7 +26231,11 @@
           <t>Walrus</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr"/>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>海象</t>
+        </is>
+      </c>
       <c r="F115" s="2" t="inlineStr"/>
     </row>
     <row r="116">
@@ -26011,7 +26363,11 @@
           <t>Cattle</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr"/>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>牛</t>
+        </is>
+      </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
           <t>Cow</t>
@@ -26039,7 +26395,11 @@
           <t>Sheep</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr"/>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>羊</t>
+        </is>
+      </c>
       <c r="F121" s="2" t="inlineStr"/>
     </row>
     <row r="122">
@@ -26063,7 +26423,11 @@
           <t>Goat</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr"/>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>山羊</t>
+        </is>
+      </c>
       <c r="F122" s="2" t="inlineStr"/>
     </row>
     <row r="123">
@@ -26087,7 +26451,11 @@
           <t>Pig</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr"/>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>豚</t>
+        </is>
+      </c>
       <c r="F123" s="2" t="inlineStr"/>
     </row>
     <row r="124">
@@ -26111,7 +26479,11 @@
           <t>Wild boar</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr"/>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>猪</t>
+        </is>
+      </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
           <t>Boar</t>
@@ -26141,7 +26513,7 @@
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>シカ</t>
+          <t>シカ, 鹿</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr"/>
@@ -26167,7 +26539,11 @@
           <t>Reindeer</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr"/>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>馴鹿</t>
+        </is>
+      </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
           <t>Caribou</t>
@@ -26195,7 +26571,11 @@
           <t>Japanese serow</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr"/>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>日本氈鹿</t>
+        </is>
+      </c>
       <c r="F127" s="2" t="inlineStr"/>
     </row>
     <row r="128">
@@ -26219,7 +26599,11 @@
           <t>Giraffe</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr"/>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>麒麟</t>
+        </is>
+      </c>
       <c r="F128" s="2" t="inlineStr"/>
     </row>
     <row r="129">
@@ -26243,7 +26627,11 @@
           <t>Hippopotamus</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr"/>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>河馬</t>
+        </is>
+      </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
           <t>Hippo</t>
@@ -26271,7 +26659,11 @@
           <t>Humpback whale</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr"/>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>座頭鯨</t>
+        </is>
+      </c>
       <c r="F130" s="2" t="inlineStr"/>
     </row>
     <row r="131">
@@ -26295,7 +26687,11 @@
           <t>Sperm whale</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr"/>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>抹香鯨</t>
+        </is>
+      </c>
       <c r="F131" s="2" t="inlineStr"/>
     </row>
     <row r="132">
@@ -26319,7 +26715,11 @@
           <t>Orca</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr"/>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>鯱</t>
+        </is>
+      </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
           <t>Killer whale</t>
@@ -26349,7 +26749,7 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>バンドウイルカ</t>
+          <t>バンドウイルカ, 海豚</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr"/>
@@ -26377,7 +26777,7 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>ヒトコブラクダ</t>
+          <t>ヒトコブラクダ, 駱駝</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
@@ -26431,7 +26831,11 @@
           <t>Horse</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr"/>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>馬</t>
+        </is>
+      </c>
       <c r="F136" s="2" t="inlineStr"/>
     </row>
     <row r="137">
@@ -26455,7 +26859,11 @@
           <t>Donkey</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr"/>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>驢馬</t>
+        </is>
+      </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
           <t>Ass</t>
@@ -26483,7 +26891,11 @@
           <t>Plains zebra</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr"/>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>縞馬</t>
+        </is>
+      </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
           <t>Zebra</t>
@@ -26513,7 +26925,7 @@
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>シロサイ</t>
+          <t>シロサイ, 犀</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
@@ -26543,7 +26955,11 @@
           <t>African bush elephant</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr"/>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>象</t>
+        </is>
+      </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
           <t>Elephant</t>
@@ -26571,7 +26987,11 @@
           <t>Asian elephant</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr"/>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>象</t>
+        </is>
+      </c>
       <c r="F141" s="2" t="inlineStr"/>
     </row>
     <row r="142">
@@ -26595,7 +27015,11 @@
           <t>Chimpanzee</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr"/>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>黒猩々</t>
+        </is>
+      </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
           <t>Chimp</t>
@@ -26625,7 +27049,7 @@
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>ニシゴリラ</t>
+          <t>ニシゴリラ, 大猩々</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr">
@@ -26719,7 +27143,11 @@
           <t>Ring-tailed lemur</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr"/>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>輪尾狐猿</t>
+        </is>
+      </c>
       <c r="F146" s="2" t="inlineStr"/>
     </row>
     <row r="147">
@@ -26745,7 +27173,7 @@
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>ネズミ</t>
+          <t>ネズミ, 鼠</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr">
@@ -26803,7 +27231,11 @@
           <t>Japanese squirrel</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr"/>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>日本栗鼠</t>
+        </is>
+      </c>
       <c r="F149" s="2" t="inlineStr"/>
     </row>
     <row r="150">
@@ -26827,7 +27259,11 @@
           <t>Japanese giant flying squirrel</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr"/>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>鼯鼠</t>
+        </is>
+      </c>
       <c r="F150" s="2" t="inlineStr"/>
     </row>
     <row r="151">
@@ -26931,7 +27367,11 @@
           <t>North American beaver</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr"/>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>海狸</t>
+        </is>
+      </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
           <t>Beaver</t>
@@ -26959,7 +27399,11 @@
           <t>Japanese hare</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr"/>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>日本野兎</t>
+        </is>
+      </c>
       <c r="F155" s="2" t="inlineStr"/>
     </row>
     <row r="156">
@@ -27039,7 +27483,11 @@
           <t>Bonin flying fox</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr"/>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>小笠原大蝙蝠</t>
+        </is>
+      </c>
       <c r="F158" s="2" t="inlineStr"/>
     </row>
     <row r="159">
@@ -27063,7 +27511,11 @@
           <t>Japanese pipistrelle</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr"/>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>油蝙蝠</t>
+        </is>
+      </c>
       <c r="F159" s="2" t="inlineStr"/>
     </row>
     <row r="160">
@@ -27087,7 +27539,11 @@
           <t>Small Japanese mole</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr"/>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>東土竜</t>
+        </is>
+      </c>
       <c r="F160" s="2" t="inlineStr"/>
     </row>
     <row r="161">
@@ -27137,7 +27593,7 @@
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>アカカンガルー</t>
+          <t>アカカンガルー, 袋鼠</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr">
@@ -27191,7 +27647,11 @@
           <t>Aardvark</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr"/>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>土豚</t>
+        </is>
+      </c>
       <c r="F164" s="2" t="inlineStr"/>
     </row>
     <row r="165">
@@ -27275,7 +27735,11 @@
           <t>Japanese bell cricket</t>
         </is>
       </c>
-      <c r="E167" s="2" t="inlineStr"/>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>鈴虫</t>
+        </is>
+      </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
           <t>Bell cricket</t>
@@ -27303,7 +27767,11 @@
           <t>Pine cricket</t>
         </is>
       </c>
-      <c r="E168" s="2" t="inlineStr"/>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>松虫</t>
+        </is>
+      </c>
       <c r="F168" s="2" t="inlineStr"/>
     </row>
     <row r="169">
@@ -27327,7 +27795,11 @@
           <t>Mikado cricket</t>
         </is>
       </c>
-      <c r="E169" s="2" t="inlineStr"/>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>綴刺蟋蟀</t>
+        </is>
+      </c>
       <c r="F169" s="2" t="inlineStr"/>
     </row>
     <row r="170">
@@ -27351,7 +27823,11 @@
           <t>Three-horned cricket</t>
         </is>
       </c>
-      <c r="E170" s="2" t="inlineStr"/>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>三角蟋蟀</t>
+        </is>
+      </c>
       <c r="F170" s="2" t="inlineStr"/>
     </row>
     <row r="171">
@@ -27375,7 +27851,11 @@
           <t>Japanese tree cricket</t>
         </is>
       </c>
-      <c r="E171" s="2" t="inlineStr"/>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>邯鄲</t>
+        </is>
+      </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
           <t>Tree cricket</t>
@@ -27403,7 +27883,11 @@
           <t>Green bell cricket</t>
         </is>
       </c>
-      <c r="E172" s="2" t="inlineStr"/>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>青松虫</t>
+        </is>
+      </c>
       <c r="F172" s="2" t="inlineStr"/>
     </row>
     <row r="173">
@@ -27427,7 +27911,11 @@
           <t>Bell tapper</t>
         </is>
       </c>
-      <c r="E173" s="2" t="inlineStr"/>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>鉦叩</t>
+        </is>
+      </c>
       <c r="F173" s="2" t="inlineStr"/>
     </row>
     <row r="174">
@@ -27451,7 +27939,11 @@
           <t>Grass lark cricket</t>
         </is>
       </c>
-      <c r="E174" s="2" t="inlineStr"/>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>草雲雀</t>
+        </is>
+      </c>
       <c r="F174" s="2" t="inlineStr"/>
     </row>
     <row r="175">
@@ -27475,7 +27967,11 @@
           <t>Japanese katydid</t>
         </is>
       </c>
-      <c r="E175" s="2" t="inlineStr"/>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>螽斯</t>
+        </is>
+      </c>
       <c r="F175" s="2" t="inlineStr"/>
     </row>
     <row r="176">
@@ -27499,7 +27995,11 @@
           <t>Rattle katydid</t>
         </is>
       </c>
-      <c r="E176" s="2" t="inlineStr"/>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>轡虫</t>
+        </is>
+      </c>
       <c r="F176" s="2" t="inlineStr"/>
     </row>
     <row r="177">
@@ -27523,7 +28023,11 @@
           <t>Horse-chaser katydid</t>
         </is>
       </c>
-      <c r="E177" s="2" t="inlineStr"/>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>馬追</t>
+        </is>
+      </c>
       <c r="F177" s="2" t="inlineStr"/>
     </row>
     <row r="178">
@@ -27547,7 +28051,11 @@
           <t>Bamboo katydid</t>
         </is>
       </c>
-      <c r="E178" s="2" t="inlineStr"/>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>笹螽</t>
+        </is>
+      </c>
       <c r="F178" s="2" t="inlineStr"/>
     </row>
     <row r="179">
@@ -27571,7 +28079,11 @@
           <t>Migratory locust</t>
         </is>
       </c>
-      <c r="E179" s="2" t="inlineStr"/>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>殿様飛蝗</t>
+        </is>
+      </c>
       <c r="F179" s="2" t="inlineStr">
         <is>
           <t>Locust</t>
@@ -27599,7 +28111,11 @@
           <t>Oriental longheaded locust</t>
         </is>
       </c>
-      <c r="E180" s="2" t="inlineStr"/>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>精霊飛蝗</t>
+        </is>
+      </c>
       <c r="F180" s="2" t="inlineStr"/>
     </row>
     <row r="181">
@@ -27623,7 +28139,11 @@
           <t>Large brown cicada</t>
         </is>
       </c>
-      <c r="E181" s="2" t="inlineStr"/>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>油蝉</t>
+        </is>
+      </c>
       <c r="F181" s="2" t="inlineStr"/>
     </row>
     <row r="182">
@@ -27647,7 +28167,11 @@
           <t>Minmin cicada</t>
         </is>
       </c>
-      <c r="E182" s="2" t="inlineStr"/>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>蛁蟟</t>
+        </is>
+      </c>
       <c r="F182" s="2" t="inlineStr"/>
     </row>
     <row r="183">
@@ -27671,7 +28195,11 @@
           <t>Bear cicada</t>
         </is>
       </c>
-      <c r="E183" s="2" t="inlineStr"/>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>熊蝉</t>
+        </is>
+      </c>
       <c r="F183" s="2" t="inlineStr"/>
     </row>
     <row r="184">
@@ -27695,7 +28223,11 @@
           <t>Tsukutsuku cicada</t>
         </is>
       </c>
-      <c r="E184" s="2" t="inlineStr"/>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>寒蝉</t>
+        </is>
+      </c>
       <c r="F184" s="2" t="inlineStr"/>
     </row>
     <row r="185">
@@ -27719,7 +28251,11 @@
           <t>Evening cicada</t>
         </is>
       </c>
-      <c r="E185" s="2" t="inlineStr"/>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>蜩</t>
+        </is>
+      </c>
       <c r="F185" s="2" t="inlineStr"/>
     </row>
     <row r="186">
@@ -27743,7 +28279,11 @@
           <t>Niinii cicada</t>
         </is>
       </c>
-      <c r="E186" s="2" t="inlineStr"/>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>蟪蛄</t>
+        </is>
+      </c>
       <c r="F186" s="2" t="inlineStr"/>
     </row>
     <row r="187">
@@ -27767,7 +28307,11 @@
           <t>Spring cicada</t>
         </is>
       </c>
-      <c r="E187" s="2" t="inlineStr"/>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>春蝉</t>
+        </is>
+      </c>
       <c r="F187" s="2" t="inlineStr"/>
     </row>
     <row r="188">
@@ -27791,7 +28335,11 @@
           <t>Ezo cicada</t>
         </is>
       </c>
-      <c r="E188" s="2" t="inlineStr"/>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>蝦夷蝉</t>
+        </is>
+      </c>
       <c r="F188" s="2" t="inlineStr"/>
     </row>
     <row r="189">
@@ -27817,7 +28365,7 @@
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>セイヨウミツバチ</t>
+          <t>セイヨウミツバチ, 蜜蜂</t>
         </is>
       </c>
       <c r="F189" s="2" t="inlineStr">
@@ -27847,7 +28395,11 @@
           <t>Japanese honey bee</t>
         </is>
       </c>
-      <c r="E190" s="2" t="inlineStr"/>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>日本蜜蜂</t>
+        </is>
+      </c>
       <c r="F190" s="2" t="inlineStr"/>
     </row>
     <row r="191">
@@ -27871,7 +28423,11 @@
           <t>Asian giant hornet</t>
         </is>
       </c>
-      <c r="E191" s="2" t="inlineStr"/>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t>大雀蜂</t>
+        </is>
+      </c>
       <c r="F191" s="2" t="inlineStr">
         <is>
           <t>Murder hornet</t>
@@ -27901,7 +28457,7 @@
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>ヒトスジシマカ</t>
+          <t>ヒトスジシマカ, 蚊</t>
         </is>
       </c>
       <c r="F192" s="2" t="inlineStr">
@@ -27933,7 +28489,7 @@
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>イエバエ</t>
+          <t>イエバエ, 蠅</t>
         </is>
       </c>
       <c r="F193" s="2" t="inlineStr">
@@ -27963,7 +28519,11 @@
           <t>Japanese rhinoceros beetle</t>
         </is>
       </c>
-      <c r="E194" s="2" t="inlineStr"/>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>甲虫,兜虫</t>
+        </is>
+      </c>
       <c r="F194" s="2" t="inlineStr"/>
     </row>
     <row r="195">
@@ -27987,7 +28547,11 @@
           <t>Japanese diving beetle</t>
         </is>
       </c>
-      <c r="E195" s="2" t="inlineStr"/>
+      <c r="E195" s="2" t="inlineStr">
+        <is>
+          <t>源五郎</t>
+        </is>
+      </c>
       <c r="F195" s="2" t="inlineStr"/>
     </row>
     <row r="196">
@@ -28043,7 +28607,11 @@
           <t>Madagascar hissing cockroach</t>
         </is>
       </c>
-      <c r="E197" s="2" t="inlineStr"/>
+      <c r="E197" s="2" t="inlineStr">
+        <is>
+          <t>蜚蠊</t>
+        </is>
+      </c>
       <c r="F197" s="2" t="inlineStr">
         <is>
           <t>Hissing cockroach</t>
@@ -28071,7 +28639,11 @@
           <t>Golden-ringed dragonfly</t>
         </is>
       </c>
-      <c r="E198" s="2" t="inlineStr"/>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>鬼蜻蜓</t>
+        </is>
+      </c>
       <c r="F198" s="2" t="inlineStr"/>
     </row>
     <row r="199">
@@ -28095,7 +28667,11 @@
           <t>Black-spotted pond frog</t>
         </is>
       </c>
-      <c r="E199" s="2" t="inlineStr"/>
+      <c r="E199" s="2" t="inlineStr">
+        <is>
+          <t>殿様蛙</t>
+        </is>
+      </c>
       <c r="F199" s="2" t="inlineStr">
         <is>
           <t>Pond frog</t>
@@ -28123,7 +28699,11 @@
           <t>American bullfrog</t>
         </is>
       </c>
-      <c r="E200" s="2" t="inlineStr"/>
+      <c r="E200" s="2" t="inlineStr">
+        <is>
+          <t>牛蛙</t>
+        </is>
+      </c>
       <c r="F200" s="2" t="inlineStr">
         <is>
           <t>Bullfrog</t>
@@ -28151,7 +28731,11 @@
           <t>Japanese common toad</t>
         </is>
       </c>
-      <c r="E201" s="2" t="inlineStr"/>
+      <c r="E201" s="2" t="inlineStr">
+        <is>
+          <t>日本蟇蛙</t>
+        </is>
+      </c>
       <c r="F201" s="2" t="inlineStr">
         <is>
           <t>Toad</t>
@@ -28179,7 +28763,11 @@
           <t>Forest green tree frog</t>
         </is>
       </c>
-      <c r="E202" s="2" t="inlineStr"/>
+      <c r="E202" s="2" t="inlineStr">
+        <is>
+          <t>森青蛙</t>
+        </is>
+      </c>
       <c r="F202" s="2" t="inlineStr"/>
     </row>
     <row r="203">
@@ -28227,7 +28815,11 @@
           <t>Kajika frog</t>
         </is>
       </c>
-      <c r="E204" s="2" t="inlineStr"/>
+      <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t>河鹿蛙</t>
+        </is>
+      </c>
       <c r="F204" s="2" t="inlineStr"/>
     </row>
     <row r="205">
@@ -28275,7 +28867,11 @@
           <t>Montane brown frog</t>
         </is>
       </c>
-      <c r="E206" s="2" t="inlineStr"/>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t>山赤蛙</t>
+        </is>
+      </c>
       <c r="F206" s="2" t="inlineStr"/>
     </row>
     <row r="207">
@@ -28299,7 +28895,11 @@
           <t>Japanese brown frog</t>
         </is>
       </c>
-      <c r="E207" s="2" t="inlineStr"/>
+      <c r="E207" s="2" t="inlineStr">
+        <is>
+          <t>日本赤蛙</t>
+        </is>
+      </c>
       <c r="F207" s="2" t="inlineStr"/>
     </row>
     <row r="208">
@@ -28395,7 +28995,11 @@
           <t>Japanese giant salamander</t>
         </is>
       </c>
-      <c r="E211" s="2" t="inlineStr"/>
+      <c r="E211" s="2" t="inlineStr">
+        <is>
+          <t>大山椒魚</t>
+        </is>
+      </c>
       <c r="F211" s="2" t="inlineStr"/>
     </row>
     <row r="212">
@@ -28419,7 +29023,11 @@
           <t>Japanese fire belly newt</t>
         </is>
       </c>
-      <c r="E212" s="2" t="inlineStr"/>
+      <c r="E212" s="2" t="inlineStr">
+        <is>
+          <t>赤腹井守</t>
+        </is>
+      </c>
       <c r="F212" s="2" t="inlineStr"/>
     </row>
     <row r="213">
@@ -28503,7 +29111,11 @@
           <t>African clawed frog</t>
         </is>
       </c>
-      <c r="E215" s="2" t="inlineStr"/>
+      <c r="E215" s="2" t="inlineStr">
+        <is>
+          <t>阿弗利加爪蛙</t>
+        </is>
+      </c>
       <c r="F215" s="2" t="inlineStr"/>
     </row>
     <row r="216">
@@ -28527,7 +29139,11 @@
           <t>Japanese gecko</t>
         </is>
       </c>
-      <c r="E216" s="2" t="inlineStr"/>
+      <c r="E216" s="2" t="inlineStr">
+        <is>
+          <t>日本守宮</t>
+        </is>
+      </c>
       <c r="F216" s="2" t="inlineStr"/>
     </row>
     <row r="217">
@@ -28575,7 +29191,11 @@
           <t>Japanese rat snake</t>
         </is>
       </c>
-      <c r="E218" s="2" t="inlineStr"/>
+      <c r="E218" s="2" t="inlineStr">
+        <is>
+          <t>青大将</t>
+        </is>
+      </c>
       <c r="F218" s="2" t="inlineStr"/>
     </row>
     <row r="219">
@@ -28601,7 +29221,7 @@
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>ニホンマムシ</t>
+          <t>ニホンマムシ, 蝮</t>
         </is>
       </c>
       <c r="F219" s="2" t="inlineStr">
@@ -28631,7 +29251,11 @@
           <t>Western diamondback rattlesnake</t>
         </is>
       </c>
-      <c r="E220" s="2" t="inlineStr"/>
+      <c r="E220" s="2" t="inlineStr">
+        <is>
+          <t>響尾蛇</t>
+        </is>
+      </c>
       <c r="F220" s="2" t="inlineStr">
         <is>
           <t>Rattlesnake</t>
@@ -28683,7 +29307,11 @@
           <t>Saltwater crocodile</t>
         </is>
       </c>
-      <c r="E222" s="2" t="inlineStr"/>
+      <c r="E222" s="2" t="inlineStr">
+        <is>
+          <t>入江鰐</t>
+        </is>
+      </c>
       <c r="F222" s="2" t="inlineStr"/>
     </row>
     <row r="223">
@@ -28735,7 +29363,11 @@
           <t>Aldabra giant tortoise</t>
         </is>
       </c>
-      <c r="E224" s="2" t="inlineStr"/>
+      <c r="E224" s="2" t="inlineStr">
+        <is>
+          <t>象亀</t>
+        </is>
+      </c>
       <c r="F224" s="2" t="inlineStr"/>
     </row>
     <row r="225">
@@ -28759,7 +29391,11 @@
           <t>Chinese softshell turtle</t>
         </is>
       </c>
-      <c r="E225" s="2" t="inlineStr"/>
+      <c r="E225" s="2" t="inlineStr">
+        <is>
+          <t>日本鼈</t>
+        </is>
+      </c>
       <c r="F225" s="2" t="inlineStr"/>
     </row>
     <row r="226">
@@ -28807,7 +29443,11 @@
           <t>Japanese five-lined skink</t>
         </is>
       </c>
-      <c r="E227" s="2" t="inlineStr"/>
+      <c r="E227" s="2" t="inlineStr">
+        <is>
+          <t>日本蜥蜴</t>
+        </is>
+      </c>
       <c r="F227" s="2" t="inlineStr"/>
     </row>
     <row r="228">
@@ -28887,7 +29527,11 @@
           <t>Bluefin searobin</t>
         </is>
       </c>
-      <c r="E230" s="2" t="inlineStr"/>
+      <c r="E230" s="2" t="inlineStr">
+        <is>
+          <t>魴鮄</t>
+        </is>
+      </c>
       <c r="F230" s="2" t="inlineStr">
         <is>
           <t>Searobin</t>
@@ -28915,7 +29559,11 @@
           <t>Barred knifejaw</t>
         </is>
       </c>
-      <c r="E231" s="2" t="inlineStr"/>
+      <c r="E231" s="2" t="inlineStr">
+        <is>
+          <t>石鯛</t>
+        </is>
+      </c>
       <c r="F231" s="2" t="inlineStr"/>
     </row>
     <row r="232">
@@ -28939,7 +29587,11 @@
           <t>Japanese pufferfish</t>
         </is>
       </c>
-      <c r="E232" s="2" t="inlineStr"/>
+      <c r="E232" s="2" t="inlineStr">
+        <is>
+          <t>虎河豚</t>
+        </is>
+      </c>
       <c r="F232" s="2" t="inlineStr">
         <is>
           <t>Pufferfish</t>
@@ -28967,7 +29619,11 @@
           <t>Thread-sail filefish</t>
         </is>
       </c>
-      <c r="E233" s="2" t="inlineStr"/>
+      <c r="E233" s="2" t="inlineStr">
+        <is>
+          <t>皮剥</t>
+        </is>
+      </c>
       <c r="F233" s="2" t="inlineStr">
         <is>
           <t>Filefish</t>
@@ -29055,7 +29711,11 @@
           <t>Japanese croaker</t>
         </is>
       </c>
-      <c r="E236" s="2" t="inlineStr"/>
+      <c r="E236" s="2" t="inlineStr">
+        <is>
+          <t>鮸</t>
+        </is>
+      </c>
       <c r="F236" s="2" t="inlineStr">
         <is>
           <t>Croaker</t>
@@ -29173,7 +29833,7 @@
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>マダイ</t>
+          <t>マダイ, 鯛</t>
         </is>
       </c>
       <c r="F240" s="2" t="inlineStr"/>
@@ -29199,7 +29859,11 @@
           <t>False kelpfish</t>
         </is>
       </c>
-      <c r="E241" s="2" t="inlineStr"/>
+      <c r="E241" s="2" t="inlineStr">
+        <is>
+          <t>笠子</t>
+        </is>
+      </c>
       <c r="F241" s="2" t="inlineStr"/>
     </row>
     <row r="242">
@@ -29223,7 +29887,11 @@
           <t>Snapping shrimp</t>
         </is>
       </c>
-      <c r="E242" s="2" t="inlineStr"/>
+      <c r="E242" s="2" t="inlineStr">
+        <is>
+          <t>鉄砲蝦</t>
+        </is>
+      </c>
       <c r="F242" s="2" t="inlineStr">
         <is>
           <t>Pistol shrimp</t>
@@ -29251,7 +29919,11 @@
           <t>Japanese spiny lobster</t>
         </is>
       </c>
-      <c r="E243" s="2" t="inlineStr"/>
+      <c r="E243" s="2" t="inlineStr">
+        <is>
+          <t>伊勢海老</t>
+        </is>
+      </c>
       <c r="F243" s="2" t="inlineStr">
         <is>
           <t>Spiny lobster</t>
@@ -29311,7 +29983,11 @@
           <t>Stimpson ghost crab</t>
         </is>
       </c>
-      <c r="E245" s="2" t="inlineStr"/>
+      <c r="E245" s="2" t="inlineStr">
+        <is>
+          <t>砂蟹</t>
+        </is>
+      </c>
       <c r="F245" s="2" t="inlineStr">
         <is>
           <t>Ghost crab</t>
@@ -29367,7 +30043,11 @@
           <t>Yesso scallop</t>
         </is>
       </c>
-      <c r="E247" s="2" t="inlineStr"/>
+      <c r="E247" s="2" t="inlineStr">
+        <is>
+          <t>帆立貝</t>
+        </is>
+      </c>
       <c r="F247" s="2" t="inlineStr">
         <is>
           <t>Scallop</t>
@@ -29593,6 +30273,11 @@
           <t>Chinese Giant Salamander</t>
         </is>
       </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>中国大山椒魚</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -29659,6 +30344,11 @@
           <t>Naumann's thrush</t>
         </is>
       </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>鶫</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -29681,6 +30371,11 @@
           <t>Pale thrush</t>
         </is>
       </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>白腹</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -29703,6 +30398,11 @@
           <t>Goldcrest</t>
         </is>
       </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>菊戴</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -29725,6 +30425,11 @@
           <t>Japanese waxwing</t>
         </is>
       </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>黄連雀</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -29747,6 +30452,11 @@
           <t>Japanese grosbeak</t>
         </is>
       </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>鵤,斑鳩</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -29769,6 +30479,11 @@
           <t>Japanese wagtail</t>
         </is>
       </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>背黒鶺鴒</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -29791,6 +30506,11 @@
           <t>Grey wagtail</t>
         </is>
       </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>黄鶺鴒</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -29815,7 +30535,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>鵺（ぬえ）</t>
+          <t>鵺（ぬえ）, 虎鶫,鵺</t>
         </is>
       </c>
     </row>
@@ -29974,7 +30694,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>コハクチョウ</t>
+          <t>コハクチョウ, 白鳥</t>
         </is>
       </c>
     </row>
@@ -29999,6 +30719,11 @@
           <t>Ruddy kingfisher</t>
         </is>
       </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>赤翡翠</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -30065,6 +30790,11 @@
           <t>Siberian chipmunk</t>
         </is>
       </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>縞栗鼠</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -30231,7 +30961,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>ユーラシアカワウソ</t>
+          <t>ユーラシアカワウソ, 川獺</t>
         </is>
       </c>
     </row>
@@ -30256,6 +30986,11 @@
           <t>Bornean orangutan</t>
         </is>
       </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>猩々</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -30280,7 +31015,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>オオカマキリ</t>
+          <t>オオカマキリ, 蟷螂</t>
         </is>
       </c>
     </row>
@@ -30307,7 +31042,7 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>オケラ</t>
+          <t>オケラ, 螻蛄</t>
         </is>
       </c>
     </row>
@@ -30427,7 +31162,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>ミドリガメ</t>
+          <t>ミドリガメ, 緑亀</t>
         </is>
       </c>
     </row>
@@ -30530,7 +31265,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>マナマズ</t>
+          <t>マナマズ, 鯰</t>
         </is>
       </c>
     </row>
@@ -30582,6 +31317,11 @@
           <t>Common carp</t>
         </is>
       </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>鯉</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -30626,6 +31366,11 @@
           <t>Largehead hairtail</t>
         </is>
       </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>太刀魚</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -30677,7 +31422,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>ミスジマイマイ</t>
+          <t>ミスジマイマイ, 蝸牛</t>
         </is>
       </c>
     </row>
@@ -30704,7 +31449,7 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>アメリカザリガニ</t>
+          <t>アメリカザリガニ, 蝲蛄</t>
         </is>
       </c>
     </row>
@@ -30727,6 +31472,11 @@
       <c r="D305" t="inlineStr">
         <is>
           <t>Common pill-bug</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>団子虫</t>
         </is>
       </c>
     </row>

--- a/data/animal-sounds-data.xlsx
+++ b/data/animal-sounds-data.xlsx
@@ -36321,7 +36321,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1207"/>
+  <dimension ref="A1:G1211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -67567,6 +67567,104 @@
       <c r="E1207" t="inlineStr">
         <is>
           <t>呜呜</t>
+        </is>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" t="inlineStr">
+        <is>
+          <t>A002</t>
+        </is>
+      </c>
+      <c r="B1208" t="inlineStr">
+        <is>
+          <t>ハシブトガラス</t>
+        </is>
+      </c>
+      <c r="C1208" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="D1208" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="E1208" t="inlineStr">
+        <is>
+          <t>カーカー</t>
+        </is>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" t="inlineStr">
+        <is>
+          <t>A002</t>
+        </is>
+      </c>
+      <c r="B1209" t="inlineStr">
+        <is>
+          <t>ハシブトガラス</t>
+        </is>
+      </c>
+      <c r="C1209" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="D1209" t="inlineStr">
+        <is>
+          <t>英語</t>
+        </is>
+      </c>
+      <c r="E1209" t="inlineStr">
+        <is>
+          <t>Caw caw</t>
+        </is>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" t="inlineStr">
+        <is>
+          <t>B022</t>
+        </is>
+      </c>
+      <c r="C1210" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="D1210" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="E1210" t="inlineStr">
+        <is>
+          <t>Teet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" t="inlineStr">
+        <is>
+          <t>B069</t>
+        </is>
+      </c>
+      <c r="C1211" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="D1211" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="E1211" t="inlineStr">
+        <is>
+          <t>Aah-aah</t>
         </is>
       </c>
     </row>

--- a/data/animal-sounds-data.xlsx
+++ b/data/animal-sounds-data.xlsx
@@ -31520,7 +31520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D217"/>
+  <dimension ref="A1:D256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -36300,6 +36300,864 @@
       <c r="D217" s="2" t="inlineStr">
         <is>
           <t>Scallops</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>綱</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>条鰭綱</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Actinopterygii</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Ray-finned fishes</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>綱</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>腹足綱</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Gastropoda</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Gastropods</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>綱</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>軟甲綱</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Malacostraca</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Malacostracans</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>目</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>カエル目</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Anura</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Frogs and toads</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>目</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>カマキリ目</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Mantodea</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Mantises</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>目</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>キジ目</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Galliformes</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Galliformes</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>目</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>コイ目</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Cypriniformes</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Cypriniformes</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>目</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>サル目</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Primates</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Primates</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>目</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>ナマズ目</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Siluriformes</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Catfishes</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>目</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>ネコ目</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Carnivora</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Carnivorans</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>目</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>ネズミ目</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Rodentia</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Rodents</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>目</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>ワラジムシ目</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Isopoda</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Isopods</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>目</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>有毛目</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Pilosa</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Sloths and anteaters</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>目</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>柄眼目</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Stylommatophora</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Stylommatophora</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>目</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>海牛目</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Sirenia</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Sirenians</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>科</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>アガマ科</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Agamidae</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Agamid lizards</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>科</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>アメリカザリガニ科</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Cambaridae</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Cambarid crayfish</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>科</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>イグアナ科</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Iguanidae</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Iguanas</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>科</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>オオハシ科</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Ramphastidae</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Toucans</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>科</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>オカダンゴムシ科</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Armadillidiidae</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Pill woodlice</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>科</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>オカヤドカリ科</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Coenobitidae</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Land hermit crabs</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>科</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>オナジマイマイ科</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Bradybaenidae</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Bradybaenid snails</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>科</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>カマキリ科</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Mantidae</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Mantises</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>科</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>ガビアル科</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Gavialidae</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Gharials</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>科</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>キクイタダキ科</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Regulidae</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Kinglets</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>科</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>キジ科</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Phasianidae</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Pheasants</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>科</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>ケラ科</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Gryllotalpidae</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Mole crickets</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>科</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>コイ科</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Cyprinidae</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Cyprinids</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>科</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>スカンク科</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Mephitidae</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Skunks</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>科</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>タチウオ科</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Trichiuridae</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Cutlassfishes</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>科</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>トカゲモドキ科</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Eublepharidae</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Eyelid geckos</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>科</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>ナマズ科</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Siluridae</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Sheatfishes</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>科</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>ヌマガメ科</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Emydidae</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Pond turtles</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>科</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>ハコフグ科</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Ostraciidae</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Boxfishes</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>科</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>ハチドリ科</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Trochilidae</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Hummingbirds</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>科</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>フタユビナマケモノ科</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Megalonychidae</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Two-toed sloths</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>科</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>マナティー科</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Trichechidae</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Manatees</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>科</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>マングース科</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Herpestidae</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Mongooses</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>科</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>レンジャク科</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Bombycillidae</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Waxwings</t>
         </is>
       </c>
     </row>
@@ -36321,7 +37179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1211"/>
+  <dimension ref="A1:G1197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -55649,7 +56507,7 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>A005</t>
+          <t>B021</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
@@ -55664,14 +56522,14 @@
       </c>
       <c r="E666" t="inlineStr">
         <is>
-          <t>끼이끼이</t>
+          <t>쥬르르르</t>
         </is>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>A005</t>
+          <t>B021</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
@@ -55686,14 +56544,14 @@
       </c>
       <c r="E667" t="inlineStr">
         <is>
-          <t>嘎嘎</t>
+          <t>啾啾啾</t>
         </is>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>B021</t>
+          <t>B022</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
@@ -55708,14 +56566,14 @@
       </c>
       <c r="E668" t="inlineStr">
         <is>
-          <t>쥬르르르</t>
+          <t>찌이이</t>
         </is>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>B021</t>
+          <t>B022</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
@@ -55730,14 +56588,14 @@
       </c>
       <c r="E669" t="inlineStr">
         <is>
-          <t>啾啾啾</t>
+          <t>唧唧</t>
         </is>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>B022</t>
+          <t>B023</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
@@ -55752,14 +56610,14 @@
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>찌이이</t>
+          <t>호이호이호이</t>
         </is>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>B022</t>
+          <t>B023</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
@@ -55774,14 +56632,14 @@
       </c>
       <c r="E671" t="inlineStr">
         <is>
-          <t>唧唧</t>
+          <t>啾啾</t>
         </is>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>B023</t>
+          <t>B024</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
@@ -55796,14 +56654,14 @@
       </c>
       <c r="E672" t="inlineStr">
         <is>
-          <t>호이호이호이</t>
+          <t>찌이삐이</t>
         </is>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>B023</t>
+          <t>B024</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
@@ -55818,14 +56676,14 @@
       </c>
       <c r="E673" t="inlineStr">
         <is>
-          <t>啾啾</t>
+          <t>嘀嘀</t>
         </is>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>B024</t>
+          <t>B025</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
@@ -55840,14 +56698,14 @@
       </c>
       <c r="E674" t="inlineStr">
         <is>
-          <t>찌이삐이</t>
+          <t>지지지</t>
         </is>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>B024</t>
+          <t>B025</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
@@ -55862,14 +56720,14 @@
       </c>
       <c r="E675" t="inlineStr">
         <is>
-          <t>嘀嘀</t>
+          <t>叽叽叽</t>
         </is>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>B025</t>
+          <t>B027</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
@@ -55884,14 +56742,14 @@
       </c>
       <c r="E676" t="inlineStr">
         <is>
-          <t>지지지</t>
+          <t>도도도</t>
         </is>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>B025</t>
+          <t>B027</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
@@ -55906,14 +56764,14 @@
       </c>
       <c r="E677" t="inlineStr">
         <is>
-          <t>叽叽叽</t>
+          <t>咯咯</t>
         </is>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>B027</t>
+          <t>B028</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
@@ -55928,14 +56786,14 @@
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>도도도</t>
+          <t>꽈아꽈아</t>
         </is>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>B027</t>
+          <t>B028</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
@@ -55950,14 +56808,14 @@
       </c>
       <c r="E679" t="inlineStr">
         <is>
-          <t>咯咯</t>
+          <t>嘎嘎</t>
         </is>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>B028</t>
+          <t>B029</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
@@ -55972,14 +56830,14 @@
       </c>
       <c r="E680" t="inlineStr">
         <is>
-          <t>꽈아꽈아</t>
+          <t>좀오라</t>
         </is>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>B028</t>
+          <t>B029</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
@@ -55994,14 +56852,14 @@
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>嘎嘎</t>
+          <t>咕咕</t>
         </is>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>B029</t>
+          <t>B030</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
@@ -56016,14 +56874,14 @@
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>좀오라</t>
+          <t>삐이삐이</t>
         </is>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>B029</t>
+          <t>B030</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
@@ -56038,14 +56896,14 @@
       </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t>咕咕</t>
+          <t>嘀嘀</t>
         </is>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>B030</t>
+          <t>B032</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
@@ -56067,7 +56925,7 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>B030</t>
+          <t>B032</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
@@ -56089,7 +56947,7 @@
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>B032</t>
+          <t>B033</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
@@ -56104,14 +56962,14 @@
       </c>
       <c r="E686" t="inlineStr">
         <is>
-          <t>삐이삐이</t>
+          <t>코오코오</t>
         </is>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>B032</t>
+          <t>B033</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
@@ -56126,14 +56984,14 @@
       </c>
       <c r="E687" t="inlineStr">
         <is>
-          <t>嘀嘀</t>
+          <t>鹅鹅</t>
         </is>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>B033</t>
+          <t>B035</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
@@ -56148,14 +57006,14 @@
       </c>
       <c r="E688" t="inlineStr">
         <is>
-          <t>코오코오</t>
+          <t>삐리삐리</t>
         </is>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>B033</t>
+          <t>B035</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
@@ -56170,14 +57028,14 @@
       </c>
       <c r="E689" t="inlineStr">
         <is>
-          <t>鹅鹅</t>
+          <t>嘀嘀</t>
         </is>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>B035</t>
+          <t>B038</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
@@ -56192,14 +57050,14 @@
       </c>
       <c r="E690" t="inlineStr">
         <is>
-          <t>삐리삐리</t>
+          <t>아오아오</t>
         </is>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>B035</t>
+          <t>B038</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
@@ -56214,14 +57072,14 @@
       </c>
       <c r="E691" t="inlineStr">
         <is>
-          <t>嘀嘀</t>
+          <t>啊呜</t>
         </is>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>B038</t>
+          <t>B039</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
@@ -56236,14 +57094,14 @@
       </c>
       <c r="E692" t="inlineStr">
         <is>
-          <t>아오아오</t>
+          <t>끼이끼이</t>
         </is>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>B038</t>
+          <t>B039</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
@@ -56258,14 +57116,14 @@
       </c>
       <c r="E693" t="inlineStr">
         <is>
-          <t>啊呜</t>
+          <t>叽叽</t>
         </is>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>B039</t>
+          <t>B040</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
@@ -56280,14 +57138,14 @@
       </c>
       <c r="E694" t="inlineStr">
         <is>
-          <t>끼이끼이</t>
+          <t>삐이효로로</t>
         </is>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>B039</t>
+          <t>B040</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
@@ -56302,14 +57160,14 @@
       </c>
       <c r="E695" t="inlineStr">
         <is>
-          <t>叽叽</t>
+          <t>嘀哟哟</t>
         </is>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>B040</t>
+          <t>B041</t>
         </is>
       </c>
       <c r="C696" t="inlineStr">
@@ -56324,14 +57182,14 @@
       </c>
       <c r="E696" t="inlineStr">
         <is>
-          <t>삐이효로로</t>
+          <t>삐이에이</t>
         </is>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>B040</t>
+          <t>B041</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
@@ -56346,14 +57204,14 @@
       </c>
       <c r="E697" t="inlineStr">
         <is>
-          <t>嘀哟哟</t>
+          <t>嘀嘀</t>
         </is>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>B041</t>
+          <t>B042</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
@@ -56368,14 +57226,14 @@
       </c>
       <c r="E698" t="inlineStr">
         <is>
-          <t>삐이에이</t>
+          <t>꽉꽉</t>
         </is>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>B041</t>
+          <t>B042</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
@@ -56390,14 +57248,14 @@
       </c>
       <c r="E699" t="inlineStr">
         <is>
-          <t>嘀嘀</t>
+          <t>嘎嘎</t>
         </is>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>B042</t>
+          <t>B043</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
@@ -56412,14 +57270,14 @@
       </c>
       <c r="E700" t="inlineStr">
         <is>
-          <t>꽉꽉</t>
+          <t>삐이이</t>
         </is>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>B042</t>
+          <t>B043</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
@@ -56434,14 +57292,14 @@
       </c>
       <c r="E701" t="inlineStr">
         <is>
-          <t>嘎嘎</t>
+          <t>嘀嘀</t>
         </is>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>B043</t>
+          <t>B045</t>
         </is>
       </c>
       <c r="C702" t="inlineStr">
@@ -56456,14 +57314,14 @@
       </c>
       <c r="E702" t="inlineStr">
         <is>
-          <t>삐이이</t>
+          <t>혹혹혹혹</t>
         </is>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>B043</t>
+          <t>B045</t>
         </is>
       </c>
       <c r="C703" t="inlineStr">
@@ -56478,14 +57336,14 @@
       </c>
       <c r="E703" t="inlineStr">
         <is>
-          <t>嘀嘀</t>
+          <t>呼呼</t>
         </is>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>B045</t>
+          <t>B046</t>
         </is>
       </c>
       <c r="C704" t="inlineStr">
@@ -56500,14 +57358,14 @@
       </c>
       <c r="E704" t="inlineStr">
         <is>
-          <t>혹혹혹혹</t>
+          <t>붓포우소우</t>
         </is>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>B045</t>
+          <t>B046</t>
         </is>
       </c>
       <c r="C705" t="inlineStr">
@@ -56522,14 +57380,14 @@
       </c>
       <c r="E705" t="inlineStr">
         <is>
-          <t>呼呼</t>
+          <t>布谷</t>
         </is>
       </c>
     </row>
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>B046</t>
+          <t>B047</t>
         </is>
       </c>
       <c r="C706" t="inlineStr">
@@ -56544,14 +57402,14 @@
       </c>
       <c r="E706" t="inlineStr">
         <is>
-          <t>붓포우소우</t>
+          <t>보오보오</t>
         </is>
       </c>
     </row>
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>B046</t>
+          <t>B047</t>
         </is>
       </c>
       <c r="C707" t="inlineStr">
@@ -56566,14 +57424,14 @@
       </c>
       <c r="E707" t="inlineStr">
         <is>
-          <t>布谷</t>
+          <t>呜呜</t>
         </is>
       </c>
     </row>
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>B047</t>
+          <t>B050</t>
         </is>
       </c>
       <c r="C708" t="inlineStr">
@@ -56588,14 +57446,14 @@
       </c>
       <c r="E708" t="inlineStr">
         <is>
-          <t>보오보오</t>
+          <t>뽀뽀뽀</t>
         </is>
       </c>
     </row>
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>B047</t>
+          <t>B050</t>
         </is>
       </c>
       <c r="C709" t="inlineStr">
@@ -56610,14 +57468,14 @@
       </c>
       <c r="E709" t="inlineStr">
         <is>
-          <t>呜呜</t>
+          <t>布谷布谷</t>
         </is>
       </c>
     </row>
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>B050</t>
+          <t>B051</t>
         </is>
       </c>
       <c r="C710" t="inlineStr">
@@ -56632,14 +57490,14 @@
       </c>
       <c r="E710" t="inlineStr">
         <is>
-          <t>뽀뽀뽀</t>
+          <t>삐요삐요</t>
         </is>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>B050</t>
+          <t>B051</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
@@ -56654,14 +57512,14 @@
       </c>
       <c r="E711" t="inlineStr">
         <is>
-          <t>布谷布谷</t>
+          <t>嘀嘀</t>
         </is>
       </c>
     </row>
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>B051</t>
+          <t>B052</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
@@ -56676,14 +57534,14 @@
       </c>
       <c r="E712" t="inlineStr">
         <is>
-          <t>삐요삐요</t>
+          <t>꾸욱꾸욱</t>
         </is>
       </c>
     </row>
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>B051</t>
+          <t>B052</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
@@ -56698,14 +57556,14 @@
       </c>
       <c r="E713" t="inlineStr">
         <is>
-          <t>嘀嘀</t>
+          <t>咯咯</t>
         </is>
       </c>
     </row>
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>B052</t>
+          <t>B053</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
@@ -56720,14 +57578,14 @@
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>꾸욱꾸욱</t>
+          <t>기이기이</t>
         </is>
       </c>
     </row>
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>B052</t>
+          <t>B053</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
@@ -56742,14 +57600,14 @@
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>咯咯</t>
+          <t>叽叽</t>
         </is>
       </c>
     </row>
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>B053</t>
+          <t>B055</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
@@ -56764,14 +57622,14 @@
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>기이기이</t>
+          <t>고아아</t>
         </is>
       </c>
     </row>
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>B053</t>
+          <t>B055</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
@@ -56786,14 +57644,14 @@
       </c>
       <c r="E717" t="inlineStr">
         <is>
-          <t>叽叽</t>
+          <t>呱呱</t>
         </is>
       </c>
     </row>
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>B055</t>
+          <t>B056</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
@@ -56808,14 +57666,14 @@
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>고아아</t>
+          <t>꽉</t>
         </is>
       </c>
     </row>
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>B055</t>
+          <t>B056</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
@@ -56830,14 +57688,14 @@
       </c>
       <c r="E719" t="inlineStr">
         <is>
-          <t>呱呱</t>
+          <t>呱</t>
         </is>
       </c>
     </row>
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>B056</t>
+          <t>B057</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
@@ -56852,14 +57710,14 @@
       </c>
       <c r="E720" t="inlineStr">
         <is>
-          <t>꽉</t>
+          <t>크르르르</t>
         </is>
       </c>
     </row>
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>B056</t>
+          <t>B057</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
@@ -56874,14 +57732,14 @@
       </c>
       <c r="E721" t="inlineStr">
         <is>
-          <t>呱</t>
+          <t>咕噜噜</t>
         </is>
       </c>
     </row>
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>B057</t>
+          <t>B058</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
@@ -56896,14 +57754,14 @@
       </c>
       <c r="E722" t="inlineStr">
         <is>
-          <t>크르르르</t>
+          <t>크르르</t>
         </is>
       </c>
     </row>
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>B057</t>
+          <t>B058</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
@@ -56918,14 +57776,14 @@
       </c>
       <c r="E723" t="inlineStr">
         <is>
-          <t>咕噜噜</t>
+          <t>咕噜</t>
         </is>
       </c>
     </row>
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>B058</t>
+          <t>B059</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
@@ -56947,7 +57805,7 @@
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>B058</t>
+          <t>B059</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
@@ -56969,7 +57827,7 @@
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>B059</t>
+          <t>B060</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
@@ -56984,14 +57842,14 @@
       </c>
       <c r="E726" t="inlineStr">
         <is>
-          <t>크르르</t>
+          <t>쿄쿄쿄</t>
         </is>
       </c>
     </row>
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>B059</t>
+          <t>B060</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
@@ -57006,14 +57864,14 @@
       </c>
       <c r="E727" t="inlineStr">
         <is>
-          <t>咕噜</t>
+          <t>咯咯咯</t>
         </is>
       </c>
     </row>
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>B060</t>
+          <t>B061</t>
         </is>
       </c>
       <c r="C728" t="inlineStr">
@@ -57028,14 +57886,14 @@
       </c>
       <c r="E728" t="inlineStr">
         <is>
-          <t>쿄쿄쿄</t>
+          <t>갸아갸아</t>
         </is>
       </c>
     </row>
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>B060</t>
+          <t>B061</t>
         </is>
       </c>
       <c r="C729" t="inlineStr">
@@ -57050,14 +57908,14 @@
       </c>
       <c r="E729" t="inlineStr">
         <is>
-          <t>咯咯咯</t>
+          <t>嘎嘎</t>
         </is>
       </c>
     </row>
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>B061</t>
+          <t>B062</t>
         </is>
       </c>
       <c r="C730" t="inlineStr">
@@ -57072,14 +57930,14 @@
       </c>
       <c r="E730" t="inlineStr">
         <is>
-          <t>갸아갸아</t>
+          <t>먀아오먀아오</t>
         </is>
       </c>
     </row>
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>B061</t>
+          <t>B062</t>
         </is>
       </c>
       <c r="C731" t="inlineStr">
@@ -57094,14 +57952,14 @@
       </c>
       <c r="E731" t="inlineStr">
         <is>
-          <t>嘎嘎</t>
+          <t>喵喵</t>
         </is>
       </c>
     </row>
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>B062</t>
+          <t>B063</t>
         </is>
       </c>
       <c r="C732" t="inlineStr">
@@ -57116,14 +57974,14 @@
       </c>
       <c r="E732" t="inlineStr">
         <is>
-          <t>먀아오먀아오</t>
+          <t>삐오삐오</t>
         </is>
       </c>
     </row>
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>B062</t>
+          <t>B063</t>
         </is>
       </c>
       <c r="C733" t="inlineStr">
@@ -57138,14 +57996,14 @@
       </c>
       <c r="E733" t="inlineStr">
         <is>
-          <t>喵喵</t>
+          <t>嘀嘀</t>
         </is>
       </c>
     </row>
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>B063</t>
+          <t>B064</t>
         </is>
       </c>
       <c r="C734" t="inlineStr">
@@ -57160,14 +58018,14 @@
       </c>
       <c r="E734" t="inlineStr">
         <is>
-          <t>삐오삐오</t>
+          <t>쩩쩩</t>
         </is>
       </c>
     </row>
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>B063</t>
+          <t>B064</t>
         </is>
       </c>
       <c r="C735" t="inlineStr">
@@ -57182,14 +58040,14 @@
       </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>嘀嘀</t>
+          <t>嘎嘎</t>
         </is>
       </c>
     </row>
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>B064</t>
+          <t>B065</t>
         </is>
       </c>
       <c r="C736" t="inlineStr">
@@ -57204,14 +58062,14 @@
       </c>
       <c r="E736" t="inlineStr">
         <is>
-          <t>쩩쩩</t>
+          <t>겟겟</t>
         </is>
       </c>
     </row>
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>B064</t>
+          <t>B065</t>
         </is>
       </c>
       <c r="C737" t="inlineStr">
@@ -57226,14 +58084,14 @@
       </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t>嘎嘎</t>
+          <t>咯咯</t>
         </is>
       </c>
     </row>
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>B065</t>
+          <t>B066</t>
         </is>
       </c>
       <c r="C738" t="inlineStr">
@@ -57248,14 +58106,14 @@
       </c>
       <c r="E738" t="inlineStr">
         <is>
-          <t>겟겟</t>
+          <t>케렛케렛</t>
         </is>
       </c>
     </row>
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>B065</t>
+          <t>B066</t>
         </is>
       </c>
       <c r="C739" t="inlineStr">
@@ -57277,7 +58135,7 @@
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>B066</t>
+          <t>B067</t>
         </is>
       </c>
       <c r="C740" t="inlineStr">
@@ -57292,14 +58150,14 @@
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>케렛케렛</t>
+          <t>딱딱딱</t>
         </is>
       </c>
     </row>
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>B066</t>
+          <t>B067</t>
         </is>
       </c>
       <c r="C741" t="inlineStr">
@@ -57314,14 +58172,14 @@
       </c>
       <c r="E741" t="inlineStr">
         <is>
-          <t>咯咯</t>
+          <t>哒哒哒</t>
         </is>
       </c>
     </row>
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>B067</t>
+          <t>B068</t>
         </is>
       </c>
       <c r="C742" t="inlineStr">
@@ -57336,14 +58194,14 @@
       </c>
       <c r="E742" t="inlineStr">
         <is>
-          <t>딱딱딱</t>
+          <t>큐리리리</t>
         </is>
       </c>
     </row>
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>B067</t>
+          <t>B068</t>
         </is>
       </c>
       <c r="C743" t="inlineStr">
@@ -57358,14 +58216,14 @@
       </c>
       <c r="E743" t="inlineStr">
         <is>
-          <t>哒哒哒</t>
+          <t>咕噜噜</t>
         </is>
       </c>
     </row>
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>B068</t>
+          <t>B069</t>
         </is>
       </c>
       <c r="C744" t="inlineStr">
@@ -57380,14 +58238,14 @@
       </c>
       <c r="E744" t="inlineStr">
         <is>
-          <t>큐리리리</t>
+          <t>아아아</t>
         </is>
       </c>
     </row>
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>B068</t>
+          <t>B069</t>
         </is>
       </c>
       <c r="C745" t="inlineStr">
@@ -57402,14 +58260,14 @@
       </c>
       <c r="E745" t="inlineStr">
         <is>
-          <t>咕噜噜</t>
+          <t>啊啊</t>
         </is>
       </c>
     </row>
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>B069</t>
+          <t>B070</t>
         </is>
       </c>
       <c r="C746" t="inlineStr">
@@ -57424,14 +58282,14 @@
       </c>
       <c r="E746" t="inlineStr">
         <is>
-          <t>아아아</t>
+          <t>꺄아꺄아</t>
         </is>
       </c>
     </row>
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>B069</t>
+          <t>B070</t>
         </is>
       </c>
       <c r="C747" t="inlineStr">
@@ -57446,14 +58304,14 @@
       </c>
       <c r="E747" t="inlineStr">
         <is>
-          <t>啊啊</t>
+          <t>嘎嘎</t>
         </is>
       </c>
     </row>
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>B070</t>
+          <t>B071</t>
         </is>
       </c>
       <c r="C748" t="inlineStr">
@@ -57468,14 +58326,14 @@
       </c>
       <c r="E748" t="inlineStr">
         <is>
-          <t>꺄아꺄아</t>
+          <t>뽀뽀뽀</t>
         </is>
       </c>
     </row>
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>B070</t>
+          <t>B071</t>
         </is>
       </c>
       <c r="C749" t="inlineStr">
@@ -57490,14 +58348,14 @@
       </c>
       <c r="E749" t="inlineStr">
         <is>
-          <t>嘎嘎</t>
+          <t>布谷</t>
         </is>
       </c>
     </row>
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>B071</t>
+          <t>B072</t>
         </is>
       </c>
       <c r="C750" t="inlineStr">
@@ -57512,14 +58370,14 @@
       </c>
       <c r="E750" t="inlineStr">
         <is>
-          <t>뽀뽀뽀</t>
+          <t>쥬이이</t>
         </is>
       </c>
     </row>
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>B071</t>
+          <t>B072</t>
         </is>
       </c>
       <c r="C751" t="inlineStr">
@@ -57534,14 +58392,14 @@
       </c>
       <c r="E751" t="inlineStr">
         <is>
-          <t>布谷</t>
+          <t>唧唧</t>
         </is>
       </c>
     </row>
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>B072</t>
+          <t>B074</t>
         </is>
       </c>
       <c r="C752" t="inlineStr">
@@ -57556,14 +58414,14 @@
       </c>
       <c r="E752" t="inlineStr">
         <is>
-          <t>쥬이이</t>
+          <t>꺄아꺄아</t>
         </is>
       </c>
     </row>
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>B072</t>
+          <t>B074</t>
         </is>
       </c>
       <c r="C753" t="inlineStr">
@@ -57578,14 +58436,14 @@
       </c>
       <c r="E753" t="inlineStr">
         <is>
-          <t>唧唧</t>
+          <t>嘎嘎</t>
         </is>
       </c>
     </row>
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>B074</t>
+          <t>B075</t>
         </is>
       </c>
       <c r="C754" t="inlineStr">
@@ -57600,14 +58458,14 @@
       </c>
       <c r="E754" t="inlineStr">
         <is>
-          <t>꺄아꺄아</t>
+          <t>끼이끼이</t>
         </is>
       </c>
     </row>
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>B074</t>
+          <t>B075</t>
         </is>
       </c>
       <c r="C755" t="inlineStr">
@@ -57622,14 +58480,14 @@
       </c>
       <c r="E755" t="inlineStr">
         <is>
-          <t>嘎嘎</t>
+          <t>叽叽</t>
         </is>
       </c>
     </row>
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>B075</t>
+          <t>B076</t>
         </is>
       </c>
       <c r="C756" t="inlineStr">
@@ -57644,14 +58502,14 @@
       </c>
       <c r="E756" t="inlineStr">
         <is>
-          <t>끼이끼이</t>
+          <t>여러 소리 모방</t>
         </is>
       </c>
     </row>
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>B075</t>
+          <t>B076</t>
         </is>
       </c>
       <c r="C757" t="inlineStr">
@@ -57666,14 +58524,14 @@
       </c>
       <c r="E757" t="inlineStr">
         <is>
-          <t>叽叽</t>
+          <t>各种模仿</t>
         </is>
       </c>
     </row>
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>B076</t>
+          <t>B077</t>
         </is>
       </c>
       <c r="C758" t="inlineStr">
@@ -57688,14 +58546,14 @@
       </c>
       <c r="E758" t="inlineStr">
         <is>
-          <t>여러 소리 모방</t>
+          <t>찌이찌이</t>
         </is>
       </c>
     </row>
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>B076</t>
+          <t>B077</t>
         </is>
       </c>
       <c r="C759" t="inlineStr">
@@ -57710,14 +58568,14 @@
       </c>
       <c r="E759" t="inlineStr">
         <is>
-          <t>各种模仿</t>
+          <t>唧唧</t>
         </is>
       </c>
     </row>
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>B077</t>
+          <t>B078</t>
         </is>
       </c>
       <c r="C760" t="inlineStr">
@@ -57732,14 +58590,14 @@
       </c>
       <c r="E760" t="inlineStr">
         <is>
-          <t>찌이찌이</t>
+          <t>끼이이</t>
         </is>
       </c>
     </row>
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>B077</t>
+          <t>B078</t>
         </is>
       </c>
       <c r="C761" t="inlineStr">
@@ -57754,14 +58612,14 @@
       </c>
       <c r="E761" t="inlineStr">
         <is>
-          <t>唧唧</t>
+          <t>叽叽</t>
         </is>
       </c>
     </row>
     <row r="762">
       <c r="A762" t="inlineStr">
         <is>
-          <t>B078</t>
+          <t>B079</t>
         </is>
       </c>
       <c r="C762" t="inlineStr">
@@ -57776,14 +58634,14 @@
       </c>
       <c r="E762" t="inlineStr">
         <is>
-          <t>끼이이</t>
+          <t>하하하하</t>
         </is>
       </c>
     </row>
     <row r="763">
       <c r="A763" t="inlineStr">
         <is>
-          <t>B078</t>
+          <t>B079</t>
         </is>
       </c>
       <c r="C763" t="inlineStr">
@@ -57798,14 +58656,14 @@
       </c>
       <c r="E763" t="inlineStr">
         <is>
-          <t>叽叽</t>
+          <t>哈哈哈</t>
         </is>
       </c>
     </row>
     <row r="764">
       <c r="A764" t="inlineStr">
         <is>
-          <t>B079</t>
+          <t>B080</t>
         </is>
       </c>
       <c r="C764" t="inlineStr">
@@ -57820,14 +58678,14 @@
       </c>
       <c r="E764" t="inlineStr">
         <is>
-          <t>하하하하</t>
+          <t>씩씩</t>
         </is>
       </c>
     </row>
     <row r="765">
       <c r="A765" t="inlineStr">
         <is>
-          <t>B079</t>
+          <t>B080</t>
         </is>
       </c>
       <c r="C765" t="inlineStr">
@@ -57842,14 +58700,14 @@
       </c>
       <c r="E765" t="inlineStr">
         <is>
-          <t>哈哈哈</t>
+          <t>嘶嘶</t>
         </is>
       </c>
     </row>
     <row r="766">
       <c r="A766" t="inlineStr">
         <is>
-          <t>B080</t>
+          <t>B081</t>
         </is>
       </c>
       <c r="C766" t="inlineStr">
@@ -57864,14 +58722,14 @@
       </c>
       <c r="E766" t="inlineStr">
         <is>
-          <t>씩씩</t>
+          <t>까아까아</t>
         </is>
       </c>
     </row>
     <row r="767">
       <c r="A767" t="inlineStr">
         <is>
-          <t>B080</t>
+          <t>B081</t>
         </is>
       </c>
       <c r="C767" t="inlineStr">
@@ -57886,14 +58744,14 @@
       </c>
       <c r="E767" t="inlineStr">
         <is>
-          <t>嘶嘶</t>
+          <t>呱呱</t>
         </is>
       </c>
     </row>
     <row r="768">
       <c r="A768" t="inlineStr">
         <is>
-          <t>B081</t>
+          <t>B082</t>
         </is>
       </c>
       <c r="C768" t="inlineStr">
@@ -57908,14 +58766,14 @@
       </c>
       <c r="E768" t="inlineStr">
         <is>
-          <t>까아까아</t>
+          <t>짯짯</t>
         </is>
       </c>
     </row>
     <row r="769">
       <c r="A769" t="inlineStr">
         <is>
-          <t>B081</t>
+          <t>B082</t>
         </is>
       </c>
       <c r="C769" t="inlineStr">
@@ -57930,14 +58788,14 @@
       </c>
       <c r="E769" t="inlineStr">
         <is>
-          <t>呱呱</t>
+          <t>叽叽</t>
         </is>
       </c>
     </row>
     <row r="770">
       <c r="A770" t="inlineStr">
         <is>
-          <t>B082</t>
+          <t>B083</t>
         </is>
       </c>
       <c r="C770" t="inlineStr">
@@ -57952,14 +58810,14 @@
       </c>
       <c r="E770" t="inlineStr">
         <is>
-          <t>짯짯</t>
+          <t>찌르르</t>
         </is>
       </c>
     </row>
     <row r="771">
       <c r="A771" t="inlineStr">
         <is>
-          <t>B082</t>
+          <t>B083</t>
         </is>
       </c>
       <c r="C771" t="inlineStr">
@@ -57974,14 +58832,14 @@
       </c>
       <c r="E771" t="inlineStr">
         <is>
-          <t>叽叽</t>
+          <t>唧唧</t>
         </is>
       </c>
     </row>
     <row r="772">
       <c r="A772" t="inlineStr">
         <is>
-          <t>B083</t>
+          <t>B084</t>
         </is>
       </c>
       <c r="C772" t="inlineStr">
@@ -57996,14 +58854,14 @@
       </c>
       <c r="E772" t="inlineStr">
         <is>
-          <t>찌르르</t>
+          <t>삐리리</t>
         </is>
       </c>
     </row>
     <row r="773">
       <c r="A773" t="inlineStr">
         <is>
-          <t>B083</t>
+          <t>B084</t>
         </is>
       </c>
       <c r="C773" t="inlineStr">
@@ -58018,14 +58876,14 @@
       </c>
       <c r="E773" t="inlineStr">
         <is>
-          <t>唧唧</t>
+          <t>嘀哩</t>
         </is>
       </c>
     </row>
     <row r="774">
       <c r="A774" t="inlineStr">
         <is>
-          <t>B084</t>
+          <t>B085</t>
         </is>
       </c>
       <c r="C774" t="inlineStr">
@@ -58040,14 +58898,14 @@
       </c>
       <c r="E774" t="inlineStr">
         <is>
-          <t>삐리리</t>
+          <t>지지지</t>
         </is>
       </c>
     </row>
     <row r="775">
       <c r="A775" t="inlineStr">
         <is>
-          <t>B084</t>
+          <t>B085</t>
         </is>
       </c>
       <c r="C775" t="inlineStr">
@@ -58062,14 +58920,14 @@
       </c>
       <c r="E775" t="inlineStr">
         <is>
-          <t>嘀哩</t>
+          <t>叽叽叽</t>
         </is>
       </c>
     </row>
     <row r="776">
       <c r="A776" t="inlineStr">
         <is>
-          <t>B085</t>
+          <t>B086</t>
         </is>
       </c>
       <c r="C776" t="inlineStr">
@@ -58084,14 +58942,14 @@
       </c>
       <c r="E776" t="inlineStr">
         <is>
-          <t>지지지</t>
+          <t>초이초이</t>
         </is>
       </c>
     </row>
     <row r="777">
       <c r="A777" t="inlineStr">
         <is>
-          <t>B085</t>
+          <t>B086</t>
         </is>
       </c>
       <c r="C777" t="inlineStr">
@@ -58106,14 +58964,14 @@
       </c>
       <c r="E777" t="inlineStr">
         <is>
-          <t>叽叽叽</t>
+          <t>啾啾</t>
         </is>
       </c>
     </row>
     <row r="778">
       <c r="A778" t="inlineStr">
         <is>
-          <t>B086</t>
+          <t>B087</t>
         </is>
       </c>
       <c r="C778" t="inlineStr">
@@ -58128,14 +58986,14 @@
       </c>
       <c r="E778" t="inlineStr">
         <is>
-          <t>초이초이</t>
+          <t>꺄꺄꺄</t>
         </is>
       </c>
     </row>
     <row r="779">
       <c r="A779" t="inlineStr">
         <is>
-          <t>B086</t>
+          <t>B087</t>
         </is>
       </c>
       <c r="C779" t="inlineStr">
@@ -58150,14 +59008,14 @@
       </c>
       <c r="E779" t="inlineStr">
         <is>
-          <t>啾啾</t>
+          <t>嘎嘎嘎</t>
         </is>
       </c>
     </row>
     <row r="780">
       <c r="A780" t="inlineStr">
         <is>
-          <t>B087</t>
+          <t>B088</t>
         </is>
       </c>
       <c r="C780" t="inlineStr">
@@ -58172,14 +59030,14 @@
       </c>
       <c r="E780" t="inlineStr">
         <is>
-          <t>꺄꺄꺄</t>
+          <t>또옥또옥</t>
         </is>
       </c>
     </row>
     <row r="781">
       <c r="A781" t="inlineStr">
         <is>
-          <t>B087</t>
+          <t>B088</t>
         </is>
       </c>
       <c r="C781" t="inlineStr">
@@ -58194,14 +59052,14 @@
       </c>
       <c r="E781" t="inlineStr">
         <is>
-          <t>嘎嘎嘎</t>
+          <t>咕咕</t>
         </is>
       </c>
     </row>
     <row r="782">
       <c r="A782" t="inlineStr">
         <is>
-          <t>B088</t>
+          <t>B089</t>
         </is>
       </c>
       <c r="C782" t="inlineStr">
@@ -58216,14 +59074,14 @@
       </c>
       <c r="E782" t="inlineStr">
         <is>
-          <t>또옥또옥</t>
+          <t>끼익끼익</t>
         </is>
       </c>
     </row>
     <row r="783">
       <c r="A783" t="inlineStr">
         <is>
-          <t>B088</t>
+          <t>B089</t>
         </is>
       </c>
       <c r="C783" t="inlineStr">
@@ -58238,14 +59096,14 @@
       </c>
       <c r="E783" t="inlineStr">
         <is>
-          <t>咕咕</t>
+          <t>嘎嘎</t>
         </is>
       </c>
     </row>
     <row r="784">
       <c r="A784" t="inlineStr">
         <is>
-          <t>B089</t>
+          <t>B090</t>
         </is>
       </c>
       <c r="C784" t="inlineStr">
@@ -58260,14 +59118,14 @@
       </c>
       <c r="E784" t="inlineStr">
         <is>
-          <t>끼익끼익</t>
+          <t>아아아</t>
         </is>
       </c>
     </row>
     <row r="785">
       <c r="A785" t="inlineStr">
         <is>
-          <t>B089</t>
+          <t>B090</t>
         </is>
       </c>
       <c r="C785" t="inlineStr">
@@ -58282,14 +59140,14 @@
       </c>
       <c r="E785" t="inlineStr">
         <is>
-          <t>嘎嘎</t>
+          <t>啊啊</t>
         </is>
       </c>
     </row>
     <row r="786">
       <c r="A786" t="inlineStr">
         <is>
-          <t>B090</t>
+          <t>B091</t>
         </is>
       </c>
       <c r="C786" t="inlineStr">
@@ -58304,14 +59162,14 @@
       </c>
       <c r="E786" t="inlineStr">
         <is>
-          <t>아아아</t>
+          <t>부우부우</t>
         </is>
       </c>
     </row>
     <row r="787">
       <c r="A787" t="inlineStr">
         <is>
-          <t>B090</t>
+          <t>B091</t>
         </is>
       </c>
       <c r="C787" t="inlineStr">
@@ -58326,14 +59184,14 @@
       </c>
       <c r="E787" t="inlineStr">
         <is>
-          <t>啊啊</t>
+          <t>嘭嘭</t>
         </is>
       </c>
     </row>
     <row r="788">
       <c r="A788" t="inlineStr">
         <is>
-          <t>B091</t>
+          <t>B092</t>
         </is>
       </c>
       <c r="C788" t="inlineStr">
@@ -58348,14 +59206,14 @@
       </c>
       <c r="E788" t="inlineStr">
         <is>
-          <t>부우부우</t>
+          <t>짹짹</t>
         </is>
       </c>
     </row>
     <row r="789">
       <c r="A789" t="inlineStr">
         <is>
-          <t>B091</t>
+          <t>B092</t>
         </is>
       </c>
       <c r="C789" t="inlineStr">
@@ -58370,14 +59228,14 @@
       </c>
       <c r="E789" t="inlineStr">
         <is>
-          <t>嘭嘭</t>
+          <t>叽叽</t>
         </is>
       </c>
     </row>
     <row r="790">
       <c r="A790" t="inlineStr">
         <is>
-          <t>B092</t>
+          <t>B093</t>
         </is>
       </c>
       <c r="C790" t="inlineStr">
@@ -58392,14 +59250,14 @@
       </c>
       <c r="E790" t="inlineStr">
         <is>
-          <t>짹짹</t>
+          <t>쀼이이</t>
         </is>
       </c>
     </row>
     <row r="791">
       <c r="A791" t="inlineStr">
         <is>
-          <t>B092</t>
+          <t>B093</t>
         </is>
       </c>
       <c r="C791" t="inlineStr">
@@ -58414,14 +59272,14 @@
       </c>
       <c r="E791" t="inlineStr">
         <is>
-          <t>叽叽</t>
+          <t>嘀嘀</t>
         </is>
       </c>
     </row>
     <row r="792">
       <c r="A792" t="inlineStr">
         <is>
-          <t>B093</t>
+          <t>B095</t>
         </is>
       </c>
       <c r="C792" t="inlineStr">
@@ -58436,14 +59294,14 @@
       </c>
       <c r="E792" t="inlineStr">
         <is>
-          <t>쀼이이</t>
+          <t>꿔꿔꿔</t>
         </is>
       </c>
     </row>
     <row r="793">
       <c r="A793" t="inlineStr">
         <is>
-          <t>B093</t>
+          <t>B095</t>
         </is>
       </c>
       <c r="C793" t="inlineStr">
@@ -58458,14 +59316,14 @@
       </c>
       <c r="E793" t="inlineStr">
         <is>
-          <t>嘀嘀</t>
+          <t>嘎嘎</t>
         </is>
       </c>
     </row>
     <row r="794">
       <c r="A794" t="inlineStr">
         <is>
-          <t>B095</t>
+          <t>B096</t>
         </is>
       </c>
       <c r="C794" t="inlineStr">
@@ -58480,14 +59338,14 @@
       </c>
       <c r="E794" t="inlineStr">
         <is>
-          <t>꿔꿔꿔</t>
+          <t>찌이찌이</t>
         </is>
       </c>
     </row>
     <row r="795">
       <c r="A795" t="inlineStr">
         <is>
-          <t>B095</t>
+          <t>B096</t>
         </is>
       </c>
       <c r="C795" t="inlineStr">
@@ -58502,14 +59360,14 @@
       </c>
       <c r="E795" t="inlineStr">
         <is>
-          <t>嘎嘎</t>
+          <t>叽叽</t>
         </is>
       </c>
     </row>
     <row r="796">
       <c r="A796" t="inlineStr">
         <is>
-          <t>B096</t>
+          <t>B097</t>
         </is>
       </c>
       <c r="C796" t="inlineStr">
@@ -58531,7 +59389,7 @@
     <row r="797">
       <c r="A797" t="inlineStr">
         <is>
-          <t>B096</t>
+          <t>B097</t>
         </is>
       </c>
       <c r="C797" t="inlineStr">
@@ -58553,7 +59411,7 @@
     <row r="798">
       <c r="A798" t="inlineStr">
         <is>
-          <t>B097</t>
+          <t>B098</t>
         </is>
       </c>
       <c r="C798" t="inlineStr">
@@ -58568,14 +59426,14 @@
       </c>
       <c r="E798" t="inlineStr">
         <is>
-          <t>찌이찌이</t>
+          <t>찌찌찌</t>
         </is>
       </c>
     </row>
     <row r="799">
       <c r="A799" t="inlineStr">
         <is>
-          <t>B097</t>
+          <t>B098</t>
         </is>
       </c>
       <c r="C799" t="inlineStr">
@@ -58590,14 +59448,14 @@
       </c>
       <c r="E799" t="inlineStr">
         <is>
-          <t>叽叽</t>
+          <t>叽叽叽</t>
         </is>
       </c>
     </row>
     <row r="800">
       <c r="A800" t="inlineStr">
         <is>
-          <t>B098</t>
+          <t>B099</t>
         </is>
       </c>
       <c r="C800" t="inlineStr">
@@ -58612,14 +59470,14 @@
       </c>
       <c r="E800" t="inlineStr">
         <is>
-          <t>찌찌찌</t>
+          <t>찌이르르</t>
         </is>
       </c>
     </row>
     <row r="801">
       <c r="A801" t="inlineStr">
         <is>
-          <t>B098</t>
+          <t>B099</t>
         </is>
       </c>
       <c r="C801" t="inlineStr">
@@ -58634,14 +59492,14 @@
       </c>
       <c r="E801" t="inlineStr">
         <is>
-          <t>叽叽叽</t>
+          <t>唧唧</t>
         </is>
       </c>
     </row>
     <row r="802">
       <c r="A802" t="inlineStr">
         <is>
-          <t>B099</t>
+          <t>B108</t>
         </is>
       </c>
       <c r="C802" t="inlineStr">
@@ -58656,14 +59514,14 @@
       </c>
       <c r="E802" t="inlineStr">
         <is>
-          <t>찌이르르</t>
+          <t>끼이끼이</t>
         </is>
       </c>
     </row>
     <row r="803">
       <c r="A803" t="inlineStr">
         <is>
-          <t>B099</t>
+          <t>B108</t>
         </is>
       </c>
       <c r="C803" t="inlineStr">
@@ -58678,14 +59536,14 @@
       </c>
       <c r="E803" t="inlineStr">
         <is>
-          <t>唧唧</t>
+          <t>叽叽</t>
         </is>
       </c>
     </row>
     <row r="804">
       <c r="A804" t="inlineStr">
         <is>
-          <t>B108</t>
+          <t>B111</t>
         </is>
       </c>
       <c r="C804" t="inlineStr">
@@ -58700,14 +59558,14 @@
       </c>
       <c r="E804" t="inlineStr">
         <is>
-          <t>끼이끼이</t>
+          <t>찌찌</t>
         </is>
       </c>
     </row>
     <row r="805">
       <c r="A805" t="inlineStr">
         <is>
-          <t>B108</t>
+          <t>B111</t>
         </is>
       </c>
       <c r="C805" t="inlineStr">
@@ -58729,7 +59587,7 @@
     <row r="806">
       <c r="A806" t="inlineStr">
         <is>
-          <t>B111</t>
+          <t>B112</t>
         </is>
       </c>
       <c r="C806" t="inlineStr">
@@ -58751,7 +59609,7 @@
     <row r="807">
       <c r="A807" t="inlineStr">
         <is>
-          <t>B111</t>
+          <t>B112</t>
         </is>
       </c>
       <c r="C807" t="inlineStr">
@@ -58773,7 +59631,7 @@
     <row r="808">
       <c r="A808" t="inlineStr">
         <is>
-          <t>B112</t>
+          <t>B113</t>
         </is>
       </c>
       <c r="C808" t="inlineStr">
@@ -58788,14 +59646,14 @@
       </c>
       <c r="E808" t="inlineStr">
         <is>
-          <t>찌찌</t>
+          <t>효오효오</t>
         </is>
       </c>
     </row>
     <row r="809">
       <c r="A809" t="inlineStr">
         <is>
-          <t>B112</t>
+          <t>B113</t>
         </is>
       </c>
       <c r="C809" t="inlineStr">
@@ -58810,14 +59668,14 @@
       </c>
       <c r="E809" t="inlineStr">
         <is>
-          <t>叽叽</t>
+          <t>呜呜</t>
         </is>
       </c>
     </row>
     <row r="810">
       <c r="A810" t="inlineStr">
         <is>
-          <t>B113</t>
+          <t>B115</t>
         </is>
       </c>
       <c r="C810" t="inlineStr">
@@ -58832,14 +59690,14 @@
       </c>
       <c r="E810" t="inlineStr">
         <is>
-          <t>효오효오</t>
+          <t>지지</t>
         </is>
       </c>
     </row>
     <row r="811">
       <c r="A811" t="inlineStr">
         <is>
-          <t>B113</t>
+          <t>B115</t>
         </is>
       </c>
       <c r="C811" t="inlineStr">
@@ -58854,14 +59712,14 @@
       </c>
       <c r="E811" t="inlineStr">
         <is>
-          <t>呜呜</t>
+          <t>叽叽</t>
         </is>
       </c>
     </row>
     <row r="812">
       <c r="A812" t="inlineStr">
         <is>
-          <t>B115</t>
+          <t>B116</t>
         </is>
       </c>
       <c r="C812" t="inlineStr">
@@ -58876,14 +59734,14 @@
       </c>
       <c r="E812" t="inlineStr">
         <is>
-          <t>지지</t>
+          <t>삐삐삐</t>
         </is>
       </c>
     </row>
     <row r="813">
       <c r="A813" t="inlineStr">
         <is>
-          <t>B115</t>
+          <t>B116</t>
         </is>
       </c>
       <c r="C813" t="inlineStr">
@@ -58898,14 +59756,14 @@
       </c>
       <c r="E813" t="inlineStr">
         <is>
-          <t>叽叽</t>
+          <t>嘀嘀嘀</t>
         </is>
       </c>
     </row>
     <row r="814">
       <c r="A814" t="inlineStr">
         <is>
-          <t>B116</t>
+          <t>B117</t>
         </is>
       </c>
       <c r="C814" t="inlineStr">
@@ -58920,14 +59778,14 @@
       </c>
       <c r="E814" t="inlineStr">
         <is>
-          <t>삐삐삐</t>
+          <t>또옥또옥</t>
         </is>
       </c>
     </row>
     <row r="815">
       <c r="A815" t="inlineStr">
         <is>
-          <t>B116</t>
+          <t>B117</t>
         </is>
       </c>
       <c r="C815" t="inlineStr">
@@ -58942,14 +59800,14 @@
       </c>
       <c r="E815" t="inlineStr">
         <is>
-          <t>嘀嘀嘀</t>
+          <t>咕咕</t>
         </is>
       </c>
     </row>
     <row r="816">
       <c r="A816" t="inlineStr">
         <is>
-          <t>B117</t>
+          <t>B118</t>
         </is>
       </c>
       <c r="C816" t="inlineStr">
@@ -58964,14 +59822,14 @@
       </c>
       <c r="E816" t="inlineStr">
         <is>
-          <t>또옥또옥</t>
+          <t>즈즈즈</t>
         </is>
       </c>
     </row>
     <row r="817">
       <c r="A817" t="inlineStr">
         <is>
-          <t>B117</t>
+          <t>B118</t>
         </is>
       </c>
       <c r="C817" t="inlineStr">
@@ -58986,14 +59844,14 @@
       </c>
       <c r="E817" t="inlineStr">
         <is>
-          <t>咕咕</t>
+          <t>嗡嗡</t>
         </is>
       </c>
     </row>
     <row r="818">
       <c r="A818" t="inlineStr">
         <is>
-          <t>B118</t>
+          <t>B119</t>
         </is>
       </c>
       <c r="C818" t="inlineStr">
@@ -59008,14 +59866,14 @@
       </c>
       <c r="E818" t="inlineStr">
         <is>
-          <t>즈즈즈</t>
+          <t>까악까악</t>
         </is>
       </c>
     </row>
     <row r="819">
       <c r="A819" t="inlineStr">
         <is>
-          <t>B118</t>
+          <t>B119</t>
         </is>
       </c>
       <c r="C819" t="inlineStr">
@@ -59030,14 +59888,14 @@
       </c>
       <c r="E819" t="inlineStr">
         <is>
-          <t>嗡嗡</t>
+          <t>嘎嘎</t>
         </is>
       </c>
     </row>
     <row r="820">
       <c r="A820" t="inlineStr">
         <is>
-          <t>B119</t>
+          <t>B120</t>
         </is>
       </c>
       <c r="C820" t="inlineStr">
@@ -59052,14 +59910,14 @@
       </c>
       <c r="E820" t="inlineStr">
         <is>
-          <t>까악까악</t>
+          <t>여러 소리 모방</t>
         </is>
       </c>
     </row>
     <row r="821">
       <c r="A821" t="inlineStr">
         <is>
-          <t>B119</t>
+          <t>B120</t>
         </is>
       </c>
       <c r="C821" t="inlineStr">
@@ -59074,14 +59932,14 @@
       </c>
       <c r="E821" t="inlineStr">
         <is>
-          <t>嘎嘎</t>
+          <t>各种模仿</t>
         </is>
       </c>
     </row>
     <row r="822">
       <c r="A822" t="inlineStr">
         <is>
-          <t>B120</t>
+          <t>B121</t>
         </is>
       </c>
       <c r="C822" t="inlineStr">
@@ -59096,14 +59954,14 @@
       </c>
       <c r="E822" t="inlineStr">
         <is>
-          <t>여러 소리 모방</t>
+          <t>코오코오</t>
         </is>
       </c>
     </row>
     <row r="823">
       <c r="A823" t="inlineStr">
         <is>
-          <t>B120</t>
+          <t>B121</t>
         </is>
       </c>
       <c r="C823" t="inlineStr">
@@ -59118,14 +59976,14 @@
       </c>
       <c r="E823" t="inlineStr">
         <is>
-          <t>各种模仿</t>
+          <t>鹅鹅</t>
         </is>
       </c>
     </row>
     <row r="824">
       <c r="A824" t="inlineStr">
         <is>
-          <t>B121</t>
+          <t>B122</t>
         </is>
       </c>
       <c r="C824" t="inlineStr">
@@ -59140,14 +59998,14 @@
       </c>
       <c r="E824" t="inlineStr">
         <is>
-          <t>코오코오</t>
+          <t>끼요끼요</t>
         </is>
       </c>
     </row>
     <row r="825">
       <c r="A825" t="inlineStr">
         <is>
-          <t>B121</t>
+          <t>B122</t>
         </is>
       </c>
       <c r="C825" t="inlineStr">
@@ -59162,14 +60020,14 @@
       </c>
       <c r="E825" t="inlineStr">
         <is>
-          <t>鹅鹅</t>
+          <t>咯咯</t>
         </is>
       </c>
     </row>
     <row r="826">
       <c r="A826" t="inlineStr">
         <is>
-          <t>B122</t>
+          <t>F003</t>
         </is>
       </c>
       <c r="C826" t="inlineStr">
@@ -59184,14 +60042,14 @@
       </c>
       <c r="E826" t="inlineStr">
         <is>
-          <t>끼요끼요</t>
+          <t>개굴개굴</t>
         </is>
       </c>
     </row>
     <row r="827">
       <c r="A827" t="inlineStr">
         <is>
-          <t>B122</t>
+          <t>F003</t>
         </is>
       </c>
       <c r="C827" t="inlineStr">
@@ -59206,14 +60064,14 @@
       </c>
       <c r="E827" t="inlineStr">
         <is>
-          <t>咯咯</t>
+          <t>呱呱</t>
         </is>
       </c>
     </row>
     <row r="828">
       <c r="A828" t="inlineStr">
         <is>
-          <t>F003</t>
+          <t>F004</t>
         </is>
       </c>
       <c r="C828" t="inlineStr">
@@ -59235,7 +60093,7 @@
     <row r="829">
       <c r="A829" t="inlineStr">
         <is>
-          <t>F003</t>
+          <t>F004</t>
         </is>
       </c>
       <c r="C829" t="inlineStr">
@@ -59257,7 +60115,7 @@
     <row r="830">
       <c r="A830" t="inlineStr">
         <is>
-          <t>F004</t>
+          <t>F005</t>
         </is>
       </c>
       <c r="C830" t="inlineStr">
@@ -59272,14 +60130,14 @@
       </c>
       <c r="E830" t="inlineStr">
         <is>
-          <t>개굴개굴</t>
+          <t>코로코로</t>
         </is>
       </c>
     </row>
     <row r="831">
       <c r="A831" t="inlineStr">
         <is>
-          <t>F004</t>
+          <t>F005</t>
         </is>
       </c>
       <c r="C831" t="inlineStr">
@@ -59294,14 +60152,14 @@
       </c>
       <c r="E831" t="inlineStr">
         <is>
-          <t>呱呱</t>
+          <t>咯咯</t>
         </is>
       </c>
     </row>
     <row r="832">
       <c r="A832" t="inlineStr">
         <is>
-          <t>F005</t>
+          <t>F006</t>
         </is>
       </c>
       <c r="C832" t="inlineStr">
@@ -59316,14 +60174,14 @@
       </c>
       <c r="E832" t="inlineStr">
         <is>
-          <t>코로코로</t>
+          <t>카지카지</t>
         </is>
       </c>
     </row>
     <row r="833">
       <c r="A833" t="inlineStr">
         <is>
-          <t>F005</t>
+          <t>F006</t>
         </is>
       </c>
       <c r="C833" t="inlineStr">
@@ -59338,14 +60196,14 @@
       </c>
       <c r="E833" t="inlineStr">
         <is>
-          <t>咯咯</t>
+          <t>咕咕</t>
         </is>
       </c>
     </row>
     <row r="834">
       <c r="A834" t="inlineStr">
         <is>
-          <t>F006</t>
+          <t>F007</t>
         </is>
       </c>
       <c r="C834" t="inlineStr">
@@ -59360,14 +60218,14 @@
       </c>
       <c r="E834" t="inlineStr">
         <is>
-          <t>카지카지</t>
+          <t>구구구</t>
         </is>
       </c>
     </row>
     <row r="835">
       <c r="A835" t="inlineStr">
         <is>
-          <t>F006</t>
+          <t>F007</t>
         </is>
       </c>
       <c r="C835" t="inlineStr">
@@ -59389,7 +60247,7 @@
     <row r="836">
       <c r="A836" t="inlineStr">
         <is>
-          <t>F007</t>
+          <t>F008</t>
         </is>
       </c>
       <c r="C836" t="inlineStr">
@@ -59404,14 +60262,14 @@
       </c>
       <c r="E836" t="inlineStr">
         <is>
-          <t>구구구</t>
+          <t>개굴개굴</t>
         </is>
       </c>
     </row>
     <row r="837">
       <c r="A837" t="inlineStr">
         <is>
-          <t>F007</t>
+          <t>F008</t>
         </is>
       </c>
       <c r="C837" t="inlineStr">
@@ -59426,14 +60284,14 @@
       </c>
       <c r="E837" t="inlineStr">
         <is>
-          <t>咕咕</t>
+          <t>呱呱</t>
         </is>
       </c>
     </row>
     <row r="838">
       <c r="A838" t="inlineStr">
         <is>
-          <t>F008</t>
+          <t>F009</t>
         </is>
       </c>
       <c r="C838" t="inlineStr">
@@ -59455,7 +60313,7 @@
     <row r="839">
       <c r="A839" t="inlineStr">
         <is>
-          <t>F008</t>
+          <t>F009</t>
         </is>
       </c>
       <c r="C839" t="inlineStr">
@@ -59477,7 +60335,7 @@
     <row r="840">
       <c r="A840" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F010</t>
         </is>
       </c>
       <c r="C840" t="inlineStr">
@@ -59499,7 +60357,7 @@
     <row r="841">
       <c r="A841" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F010</t>
         </is>
       </c>
       <c r="C841" t="inlineStr">
@@ -59521,7 +60379,7 @@
     <row r="842">
       <c r="A842" t="inlineStr">
         <is>
-          <t>F010</t>
+          <t>F011</t>
         </is>
       </c>
       <c r="C842" t="inlineStr">
@@ -59536,14 +60394,14 @@
       </c>
       <c r="E842" t="inlineStr">
         <is>
-          <t>개굴개굴</t>
+          <t>삐이삐이</t>
         </is>
       </c>
     </row>
     <row r="843">
       <c r="A843" t="inlineStr">
         <is>
-          <t>F010</t>
+          <t>F011</t>
         </is>
       </c>
       <c r="C843" t="inlineStr">
@@ -59558,14 +60416,14 @@
       </c>
       <c r="E843" t="inlineStr">
         <is>
-          <t>呱呱</t>
+          <t>嘀嘀</t>
         </is>
       </c>
     </row>
     <row r="844">
       <c r="A844" t="inlineStr">
         <is>
-          <t>F011</t>
+          <t>F012</t>
         </is>
       </c>
       <c r="C844" t="inlineStr">
@@ -59580,14 +60438,14 @@
       </c>
       <c r="E844" t="inlineStr">
         <is>
-          <t>삐이삐이</t>
+          <t>피이피이</t>
         </is>
       </c>
     </row>
     <row r="845">
       <c r="A845" t="inlineStr">
         <is>
-          <t>F011</t>
+          <t>F012</t>
         </is>
       </c>
       <c r="C845" t="inlineStr">
@@ -59609,7 +60467,7 @@
     <row r="846">
       <c r="A846" t="inlineStr">
         <is>
-          <t>F012</t>
+          <t>F013</t>
         </is>
       </c>
       <c r="C846" t="inlineStr">
@@ -59624,14 +60482,14 @@
       </c>
       <c r="E846" t="inlineStr">
         <is>
-          <t>피이피이</t>
+          <t>으으</t>
         </is>
       </c>
     </row>
     <row r="847">
       <c r="A847" t="inlineStr">
         <is>
-          <t>F012</t>
+          <t>F013</t>
         </is>
       </c>
       <c r="C847" t="inlineStr">
@@ -59646,14 +60504,14 @@
       </c>
       <c r="E847" t="inlineStr">
         <is>
-          <t>嘀嘀</t>
+          <t>嗯嗯</t>
         </is>
       </c>
     </row>
     <row r="848">
       <c r="A848" t="inlineStr">
         <is>
-          <t>F013</t>
+          <t>F014</t>
         </is>
       </c>
       <c r="C848" t="inlineStr">
@@ -59668,14 +60526,14 @@
       </c>
       <c r="E848" t="inlineStr">
         <is>
-          <t>으으</t>
+          <t>끼이끼이</t>
         </is>
       </c>
     </row>
     <row r="849">
       <c r="A849" t="inlineStr">
         <is>
-          <t>F013</t>
+          <t>F014</t>
         </is>
       </c>
       <c r="C849" t="inlineStr">
@@ -59690,14 +60548,14 @@
       </c>
       <c r="E849" t="inlineStr">
         <is>
-          <t>嗯嗯</t>
+          <t>吱吱</t>
         </is>
       </c>
     </row>
     <row r="850">
       <c r="A850" t="inlineStr">
         <is>
-          <t>F014</t>
+          <t>F015</t>
         </is>
       </c>
       <c r="C850" t="inlineStr">
@@ -59712,14 +60570,14 @@
       </c>
       <c r="E850" t="inlineStr">
         <is>
-          <t>끼이끼이</t>
+          <t>삐이삐이</t>
         </is>
       </c>
     </row>
     <row r="851">
       <c r="A851" t="inlineStr">
         <is>
-          <t>F014</t>
+          <t>F015</t>
         </is>
       </c>
       <c r="C851" t="inlineStr">
@@ -59734,14 +60592,14 @@
       </c>
       <c r="E851" t="inlineStr">
         <is>
-          <t>吱吱</t>
+          <t>嘀嘀</t>
         </is>
       </c>
     </row>
     <row r="852">
       <c r="A852" t="inlineStr">
         <is>
-          <t>F015</t>
+          <t>F016</t>
         </is>
       </c>
       <c r="C852" t="inlineStr">
@@ -59756,14 +60614,14 @@
       </c>
       <c r="E852" t="inlineStr">
         <is>
-          <t>삐이삐이</t>
+          <t>코키코키</t>
         </is>
       </c>
     </row>
     <row r="853">
       <c r="A853" t="inlineStr">
         <is>
-          <t>F015</t>
+          <t>F016</t>
         </is>
       </c>
       <c r="C853" t="inlineStr">
@@ -59778,14 +60636,14 @@
       </c>
       <c r="E853" t="inlineStr">
         <is>
-          <t>嘀嘀</t>
+          <t>咯叽</t>
         </is>
       </c>
     </row>
     <row r="854">
       <c r="A854" t="inlineStr">
         <is>
-          <t>F016</t>
+          <t>F017</t>
         </is>
       </c>
       <c r="C854" t="inlineStr">
@@ -59800,14 +60658,14 @@
       </c>
       <c r="E854" t="inlineStr">
         <is>
-          <t>코키코키</t>
+          <t>딱딱딱</t>
         </is>
       </c>
     </row>
     <row r="855">
       <c r="A855" t="inlineStr">
         <is>
-          <t>F016</t>
+          <t>F017</t>
         </is>
       </c>
       <c r="C855" t="inlineStr">
@@ -59822,14 +60680,14 @@
       </c>
       <c r="E855" t="inlineStr">
         <is>
-          <t>咯叽</t>
+          <t>嗒嗒</t>
         </is>
       </c>
     </row>
     <row r="856">
       <c r="A856" t="inlineStr">
         <is>
-          <t>F017</t>
+          <t>F018</t>
         </is>
       </c>
       <c r="C856" t="inlineStr">
@@ -59844,14 +60702,14 @@
       </c>
       <c r="E856" t="inlineStr">
         <is>
-          <t>딱딱딱</t>
+          <t>쨔아</t>
         </is>
       </c>
     </row>
     <row r="857">
       <c r="A857" t="inlineStr">
         <is>
-          <t>F017</t>
+          <t>F018</t>
         </is>
       </c>
       <c r="C857" t="inlineStr">
@@ -59866,14 +60724,14 @@
       </c>
       <c r="E857" t="inlineStr">
         <is>
-          <t>嗒嗒</t>
+          <t>嘎嘎</t>
         </is>
       </c>
     </row>
     <row r="858">
       <c r="A858" t="inlineStr">
         <is>
-          <t>F018</t>
+          <t>F019</t>
         </is>
       </c>
       <c r="C858" t="inlineStr">
@@ -59888,14 +60746,14 @@
       </c>
       <c r="E858" t="inlineStr">
         <is>
-          <t>쨔아</t>
+          <t>삐이삐이</t>
         </is>
       </c>
     </row>
     <row r="859">
       <c r="A859" t="inlineStr">
         <is>
-          <t>F018</t>
+          <t>F019</t>
         </is>
       </c>
       <c r="C859" t="inlineStr">
@@ -59910,14 +60768,14 @@
       </c>
       <c r="E859" t="inlineStr">
         <is>
-          <t>嘎嘎</t>
+          <t>嘀嘀</t>
         </is>
       </c>
     </row>
     <row r="860">
       <c r="A860" t="inlineStr">
         <is>
-          <t>F019</t>
+          <t>F020</t>
         </is>
       </c>
       <c r="C860" t="inlineStr">
@@ -59932,14 +60790,14 @@
       </c>
       <c r="E860" t="inlineStr">
         <is>
-          <t>삐이삐이</t>
+          <t>개굴개굴</t>
         </is>
       </c>
     </row>
     <row r="861">
       <c r="A861" t="inlineStr">
         <is>
-          <t>F019</t>
+          <t>F020</t>
         </is>
       </c>
       <c r="C861" t="inlineStr">
@@ -59954,14 +60812,14 @@
       </c>
       <c r="E861" t="inlineStr">
         <is>
-          <t>嘀嘀</t>
+          <t>呱呱</t>
         </is>
       </c>
     </row>
     <row r="862">
       <c r="A862" t="inlineStr">
         <is>
-          <t>F020</t>
+          <t>F021</t>
         </is>
       </c>
       <c r="C862" t="inlineStr">
@@ -59983,7 +60841,7 @@
     <row r="863">
       <c r="A863" t="inlineStr">
         <is>
-          <t>F020</t>
+          <t>F021</t>
         </is>
       </c>
       <c r="C863" t="inlineStr">
@@ -60005,7 +60863,7 @@
     <row r="864">
       <c r="A864" t="inlineStr">
         <is>
-          <t>F021</t>
+          <t>F023</t>
         </is>
       </c>
       <c r="C864" t="inlineStr">
@@ -60027,7 +60885,7 @@
     <row r="865">
       <c r="A865" t="inlineStr">
         <is>
-          <t>F021</t>
+          <t>F023</t>
         </is>
       </c>
       <c r="C865" t="inlineStr">
@@ -60049,7 +60907,7 @@
     <row r="866">
       <c r="A866" t="inlineStr">
         <is>
-          <t>F022</t>
+          <t>F024</t>
         </is>
       </c>
       <c r="C866" t="inlineStr">
@@ -60064,14 +60922,14 @@
       </c>
       <c r="E866" t="inlineStr">
         <is>
-          <t>끼이끼이</t>
+          <t>삐이삐이</t>
         </is>
       </c>
     </row>
     <row r="867">
       <c r="A867" t="inlineStr">
         <is>
-          <t>F022</t>
+          <t>F024</t>
         </is>
       </c>
       <c r="C867" t="inlineStr">
@@ -60086,14 +60944,14 @@
       </c>
       <c r="E867" t="inlineStr">
         <is>
-          <t>吱吱</t>
+          <t>嘀嘀</t>
         </is>
       </c>
     </row>
     <row r="868">
       <c r="A868" t="inlineStr">
         <is>
-          <t>F023</t>
+          <t>F025</t>
         </is>
       </c>
       <c r="C868" t="inlineStr">
@@ -60115,7 +60973,7 @@
     <row r="869">
       <c r="A869" t="inlineStr">
         <is>
-          <t>F023</t>
+          <t>F025</t>
         </is>
       </c>
       <c r="C869" t="inlineStr">
@@ -60137,7 +60995,7 @@
     <row r="870">
       <c r="A870" t="inlineStr">
         <is>
-          <t>F024</t>
+          <t>F027</t>
         </is>
       </c>
       <c r="C870" t="inlineStr">
@@ -60152,14 +61010,14 @@
       </c>
       <c r="E870" t="inlineStr">
         <is>
-          <t>삐이삐이</t>
+          <t>으으</t>
         </is>
       </c>
     </row>
     <row r="871">
       <c r="A871" t="inlineStr">
         <is>
-          <t>F024</t>
+          <t>F027</t>
         </is>
       </c>
       <c r="C871" t="inlineStr">
@@ -60174,14 +61032,14 @@
       </c>
       <c r="E871" t="inlineStr">
         <is>
-          <t>嘀嘀</t>
+          <t>嗯嗯</t>
         </is>
       </c>
     </row>
     <row r="872">
       <c r="A872" t="inlineStr">
         <is>
-          <t>F025</t>
+          <t>F029</t>
         </is>
       </c>
       <c r="C872" t="inlineStr">
@@ -60203,7 +61061,7 @@
     <row r="873">
       <c r="A873" t="inlineStr">
         <is>
-          <t>F025</t>
+          <t>F029</t>
         </is>
       </c>
       <c r="C873" t="inlineStr">
@@ -60225,7 +61083,7 @@
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
-          <t>F026</t>
+          <t>F030</t>
         </is>
       </c>
       <c r="C874" t="inlineStr">
@@ -60240,14 +61098,14 @@
       </c>
       <c r="E874" t="inlineStr">
         <is>
-          <t>끼이끼이</t>
+          <t>개굴개굴</t>
         </is>
       </c>
     </row>
     <row r="875">
       <c r="A875" t="inlineStr">
         <is>
-          <t>F026</t>
+          <t>F030</t>
         </is>
       </c>
       <c r="C875" t="inlineStr">
@@ -60262,14 +61120,14 @@
       </c>
       <c r="E875" t="inlineStr">
         <is>
-          <t>吱吱</t>
+          <t>呱呱</t>
         </is>
       </c>
     </row>
     <row r="876">
       <c r="A876" t="inlineStr">
         <is>
-          <t>F027</t>
+          <t>F033</t>
         </is>
       </c>
       <c r="C876" t="inlineStr">
@@ -60284,14 +61142,14 @@
       </c>
       <c r="E876" t="inlineStr">
         <is>
-          <t>으으</t>
+          <t>개굴개굴</t>
         </is>
       </c>
     </row>
     <row r="877">
       <c r="A877" t="inlineStr">
         <is>
-          <t>F027</t>
+          <t>F033</t>
         </is>
       </c>
       <c r="C877" t="inlineStr">
@@ -60306,14 +61164,14 @@
       </c>
       <c r="E877" t="inlineStr">
         <is>
-          <t>嗯嗯</t>
+          <t>呱呱</t>
         </is>
       </c>
     </row>
     <row r="878">
       <c r="A878" t="inlineStr">
         <is>
-          <t>F028</t>
+          <t>I001</t>
         </is>
       </c>
       <c r="C878" t="inlineStr">
@@ -60328,14 +61186,14 @@
       </c>
       <c r="E878" t="inlineStr">
         <is>
-          <t>끼이끼이</t>
+          <t>릴릴릴</t>
         </is>
       </c>
     </row>
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>F028</t>
+          <t>I001</t>
         </is>
       </c>
       <c r="C879" t="inlineStr">
@@ -60350,14 +61208,14 @@
       </c>
       <c r="E879" t="inlineStr">
         <is>
-          <t>吱吱</t>
+          <t>铃铃铃</t>
         </is>
       </c>
     </row>
     <row r="880">
       <c r="A880" t="inlineStr">
         <is>
-          <t>F029</t>
+          <t>I002</t>
         </is>
       </c>
       <c r="C880" t="inlineStr">
@@ -60372,14 +61230,14 @@
       </c>
       <c r="E880" t="inlineStr">
         <is>
-          <t>개굴개굴</t>
+          <t>찌르르르</t>
         </is>
       </c>
     </row>
     <row r="881">
       <c r="A881" t="inlineStr">
         <is>
-          <t>F029</t>
+          <t>I002</t>
         </is>
       </c>
       <c r="C881" t="inlineStr">
@@ -60394,14 +61252,14 @@
       </c>
       <c r="E881" t="inlineStr">
         <is>
-          <t>呱呱</t>
+          <t>唧唧</t>
         </is>
       </c>
     </row>
     <row r="882">
       <c r="A882" t="inlineStr">
         <is>
-          <t>F030</t>
+          <t>I003</t>
         </is>
       </c>
       <c r="C882" t="inlineStr">
@@ -60416,14 +61274,14 @@
       </c>
       <c r="E882" t="inlineStr">
         <is>
-          <t>개굴개굴</t>
+          <t>리리리리</t>
         </is>
       </c>
     </row>
     <row r="883">
       <c r="A883" t="inlineStr">
         <is>
-          <t>F030</t>
+          <t>I003</t>
         </is>
       </c>
       <c r="C883" t="inlineStr">
@@ -60438,14 +61296,14 @@
       </c>
       <c r="E883" t="inlineStr">
         <is>
-          <t>呱呱</t>
+          <t>唧唧</t>
         </is>
       </c>
     </row>
     <row r="884">
       <c r="A884" t="inlineStr">
         <is>
-          <t>F033</t>
+          <t>I004</t>
         </is>
       </c>
       <c r="C884" t="inlineStr">
@@ -60460,14 +61318,14 @@
       </c>
       <c r="E884" t="inlineStr">
         <is>
-          <t>개굴개굴</t>
+          <t>리리리</t>
         </is>
       </c>
     </row>
     <row r="885">
       <c r="A885" t="inlineStr">
         <is>
-          <t>F033</t>
+          <t>I004</t>
         </is>
       </c>
       <c r="C885" t="inlineStr">
@@ -60482,14 +61340,14 @@
       </c>
       <c r="E885" t="inlineStr">
         <is>
-          <t>呱呱</t>
+          <t>唧唧</t>
         </is>
       </c>
     </row>
     <row r="886">
       <c r="A886" t="inlineStr">
         <is>
-          <t>I001</t>
+          <t>I005</t>
         </is>
       </c>
       <c r="C886" t="inlineStr">
@@ -60504,14 +61362,14 @@
       </c>
       <c r="E886" t="inlineStr">
         <is>
-          <t>릴릴릴</t>
+          <t>르르르르</t>
         </is>
       </c>
     </row>
     <row r="887">
       <c r="A887" t="inlineStr">
         <is>
-          <t>I001</t>
+          <t>I005</t>
         </is>
       </c>
       <c r="C887" t="inlineStr">
@@ -60526,14 +61384,14 @@
       </c>
       <c r="E887" t="inlineStr">
         <is>
-          <t>铃铃铃</t>
+          <t>铃铃</t>
         </is>
       </c>
     </row>
     <row r="888">
       <c r="A888" t="inlineStr">
         <is>
-          <t>I002</t>
+          <t>I006</t>
         </is>
       </c>
       <c r="C888" t="inlineStr">
@@ -60548,14 +61406,14 @@
       </c>
       <c r="E888" t="inlineStr">
         <is>
-          <t>찌르르르</t>
+          <t>르르르르</t>
         </is>
       </c>
     </row>
     <row r="889">
       <c r="A889" t="inlineStr">
         <is>
-          <t>I002</t>
+          <t>I006</t>
         </is>
       </c>
       <c r="C889" t="inlineStr">
@@ -60570,14 +61428,14 @@
       </c>
       <c r="E889" t="inlineStr">
         <is>
-          <t>唧唧</t>
+          <t>铃铃</t>
         </is>
       </c>
     </row>
     <row r="890">
       <c r="A890" t="inlineStr">
         <is>
-          <t>I003</t>
+          <t>I007</t>
         </is>
       </c>
       <c r="C890" t="inlineStr">
@@ -60592,14 +61450,14 @@
       </c>
       <c r="E890" t="inlineStr">
         <is>
-          <t>리리리리</t>
+          <t>딱딱딱</t>
         </is>
       </c>
     </row>
     <row r="891">
       <c r="A891" t="inlineStr">
         <is>
-          <t>I003</t>
+          <t>I007</t>
         </is>
       </c>
       <c r="C891" t="inlineStr">
@@ -60614,14 +61472,14 @@
       </c>
       <c r="E891" t="inlineStr">
         <is>
-          <t>唧唧</t>
+          <t>嗒嗒嗒</t>
         </is>
       </c>
     </row>
     <row r="892">
       <c r="A892" t="inlineStr">
         <is>
-          <t>I004</t>
+          <t>I008</t>
         </is>
       </c>
       <c r="C892" t="inlineStr">
@@ -60636,14 +61494,14 @@
       </c>
       <c r="E892" t="inlineStr">
         <is>
-          <t>리리리</t>
+          <t>리리리리</t>
         </is>
       </c>
     </row>
     <row r="893">
       <c r="A893" t="inlineStr">
         <is>
-          <t>I004</t>
+          <t>I008</t>
         </is>
       </c>
       <c r="C893" t="inlineStr">
@@ -60665,7 +61523,7 @@
     <row r="894">
       <c r="A894" t="inlineStr">
         <is>
-          <t>I005</t>
+          <t>I009</t>
         </is>
       </c>
       <c r="C894" t="inlineStr">
@@ -60680,14 +61538,14 @@
       </c>
       <c r="E894" t="inlineStr">
         <is>
-          <t>르르르르</t>
+          <t>기이기이</t>
         </is>
       </c>
     </row>
     <row r="895">
       <c r="A895" t="inlineStr">
         <is>
-          <t>I005</t>
+          <t>I009</t>
         </is>
       </c>
       <c r="C895" t="inlineStr">
@@ -60702,14 +61560,14 @@
       </c>
       <c r="E895" t="inlineStr">
         <is>
-          <t>铃铃</t>
+          <t>叽叽</t>
         </is>
       </c>
     </row>
     <row r="896">
       <c r="A896" t="inlineStr">
         <is>
-          <t>I006</t>
+          <t>I010</t>
         </is>
       </c>
       <c r="C896" t="inlineStr">
@@ -60724,14 +61582,14 @@
       </c>
       <c r="E896" t="inlineStr">
         <is>
-          <t>르르르르</t>
+          <t>가챠가챠</t>
         </is>
       </c>
     </row>
     <row r="897">
       <c r="A897" t="inlineStr">
         <is>
-          <t>I006</t>
+          <t>I010</t>
         </is>
       </c>
       <c r="C897" t="inlineStr">
@@ -60746,14 +61604,14 @@
       </c>
       <c r="E897" t="inlineStr">
         <is>
-          <t>铃铃</t>
+          <t>嘎嘎</t>
         </is>
       </c>
     </row>
     <row r="898">
       <c r="A898" t="inlineStr">
         <is>
-          <t>I007</t>
+          <t>I011</t>
         </is>
       </c>
       <c r="C898" t="inlineStr">
@@ -60768,14 +61626,14 @@
       </c>
       <c r="E898" t="inlineStr">
         <is>
-          <t>딱딱딱</t>
+          <t>스이잇</t>
         </is>
       </c>
     </row>
     <row r="899">
       <c r="A899" t="inlineStr">
         <is>
-          <t>I007</t>
+          <t>I011</t>
         </is>
       </c>
       <c r="C899" t="inlineStr">
@@ -60790,14 +61648,14 @@
       </c>
       <c r="E899" t="inlineStr">
         <is>
-          <t>嗒嗒嗒</t>
+          <t>嘘嘘</t>
         </is>
       </c>
     </row>
     <row r="900">
       <c r="A900" t="inlineStr">
         <is>
-          <t>I008</t>
+          <t>I012</t>
         </is>
       </c>
       <c r="C900" t="inlineStr">
@@ -60812,14 +61670,14 @@
       </c>
       <c r="E900" t="inlineStr">
         <is>
-          <t>리리리리</t>
+          <t>지지지</t>
         </is>
       </c>
     </row>
     <row r="901">
       <c r="A901" t="inlineStr">
         <is>
-          <t>I008</t>
+          <t>I012</t>
         </is>
       </c>
       <c r="C901" t="inlineStr">
@@ -60834,14 +61692,14 @@
       </c>
       <c r="E901" t="inlineStr">
         <is>
-          <t>唧唧</t>
+          <t>叽叽</t>
         </is>
       </c>
     </row>
     <row r="902">
       <c r="A902" t="inlineStr">
         <is>
-          <t>I009</t>
+          <t>I013</t>
         </is>
       </c>
       <c r="C902" t="inlineStr">
@@ -60856,14 +61714,14 @@
       </c>
       <c r="E902" t="inlineStr">
         <is>
-          <t>기이기이</t>
+          <t>바사바사</t>
         </is>
       </c>
     </row>
     <row r="903">
       <c r="A903" t="inlineStr">
         <is>
-          <t>I009</t>
+          <t>I013</t>
         </is>
       </c>
       <c r="C903" t="inlineStr">
@@ -60878,14 +61736,14 @@
       </c>
       <c r="E903" t="inlineStr">
         <is>
-          <t>叽叽</t>
+          <t>扑扑</t>
         </is>
       </c>
     </row>
     <row r="904">
       <c r="A904" t="inlineStr">
         <is>
-          <t>I010</t>
+          <t>I014</t>
         </is>
       </c>
       <c r="C904" t="inlineStr">
@@ -60900,14 +61758,14 @@
       </c>
       <c r="E904" t="inlineStr">
         <is>
-          <t>가챠가챠</t>
+          <t>치키치키</t>
         </is>
       </c>
     </row>
     <row r="905">
       <c r="A905" t="inlineStr">
         <is>
-          <t>I010</t>
+          <t>I014</t>
         </is>
       </c>
       <c r="C905" t="inlineStr">
@@ -60922,14 +61780,14 @@
       </c>
       <c r="E905" t="inlineStr">
         <is>
-          <t>嘎嘎</t>
+          <t>嘶嘶</t>
         </is>
       </c>
     </row>
     <row r="906">
       <c r="A906" t="inlineStr">
         <is>
-          <t>I011</t>
+          <t>I015</t>
         </is>
       </c>
       <c r="C906" t="inlineStr">
@@ -60944,14 +61802,14 @@
       </c>
       <c r="E906" t="inlineStr">
         <is>
-          <t>스이잇</t>
+          <t>지이지이</t>
         </is>
       </c>
     </row>
     <row r="907">
       <c r="A907" t="inlineStr">
         <is>
-          <t>I011</t>
+          <t>I015</t>
         </is>
       </c>
       <c r="C907" t="inlineStr">
@@ -60966,14 +61824,14 @@
       </c>
       <c r="E907" t="inlineStr">
         <is>
-          <t>嘘嘘</t>
+          <t>知了知了</t>
         </is>
       </c>
     </row>
     <row r="908">
       <c r="A908" t="inlineStr">
         <is>
-          <t>I012</t>
+          <t>I016</t>
         </is>
       </c>
       <c r="C908" t="inlineStr">
@@ -60988,14 +61846,14 @@
       </c>
       <c r="E908" t="inlineStr">
         <is>
-          <t>지지지</t>
+          <t>밍밍</t>
         </is>
       </c>
     </row>
     <row r="909">
       <c r="A909" t="inlineStr">
         <is>
-          <t>I012</t>
+          <t>I016</t>
         </is>
       </c>
       <c r="C909" t="inlineStr">
@@ -61010,14 +61868,14 @@
       </c>
       <c r="E909" t="inlineStr">
         <is>
-          <t>叽叽</t>
+          <t>知了知了</t>
         </is>
       </c>
     </row>
     <row r="910">
       <c r="A910" t="inlineStr">
         <is>
-          <t>I013</t>
+          <t>I017</t>
         </is>
       </c>
       <c r="C910" t="inlineStr">
@@ -61032,14 +61890,14 @@
       </c>
       <c r="E910" t="inlineStr">
         <is>
-          <t>바사바사</t>
+          <t>쌔앵쌔앵</t>
         </is>
       </c>
     </row>
     <row r="911">
       <c r="A911" t="inlineStr">
         <is>
-          <t>I013</t>
+          <t>I017</t>
         </is>
       </c>
       <c r="C911" t="inlineStr">
@@ -61054,14 +61912,14 @@
       </c>
       <c r="E911" t="inlineStr">
         <is>
-          <t>扑扑</t>
+          <t>知了知了</t>
         </is>
       </c>
     </row>
     <row r="912">
       <c r="A912" t="inlineStr">
         <is>
-          <t>I014</t>
+          <t>I018</t>
         </is>
       </c>
       <c r="C912" t="inlineStr">
@@ -61076,14 +61934,14 @@
       </c>
       <c r="E912" t="inlineStr">
         <is>
-          <t>치키치키</t>
+          <t>쯔쿠쯔쿠</t>
         </is>
       </c>
     </row>
     <row r="913">
       <c r="A913" t="inlineStr">
         <is>
-          <t>I014</t>
+          <t>I018</t>
         </is>
       </c>
       <c r="C913" t="inlineStr">
@@ -61098,14 +61956,14 @@
       </c>
       <c r="E913" t="inlineStr">
         <is>
-          <t>嘶嘶</t>
+          <t>知了知了</t>
         </is>
       </c>
     </row>
     <row r="914">
       <c r="A914" t="inlineStr">
         <is>
-          <t>I015</t>
+          <t>I019</t>
         </is>
       </c>
       <c r="C914" t="inlineStr">
@@ -61120,14 +61978,14 @@
       </c>
       <c r="E914" t="inlineStr">
         <is>
-          <t>지이지이</t>
+          <t>카나카나</t>
         </is>
       </c>
     </row>
     <row r="915">
       <c r="A915" t="inlineStr">
         <is>
-          <t>I015</t>
+          <t>I019</t>
         </is>
       </c>
       <c r="C915" t="inlineStr">
@@ -61142,14 +62000,14 @@
       </c>
       <c r="E915" t="inlineStr">
         <is>
-          <t>知了知了</t>
+          <t>蝉蝉</t>
         </is>
       </c>
     </row>
     <row r="916">
       <c r="A916" t="inlineStr">
         <is>
-          <t>I016</t>
+          <t>I020</t>
         </is>
       </c>
       <c r="C916" t="inlineStr">
@@ -61164,14 +62022,14 @@
       </c>
       <c r="E916" t="inlineStr">
         <is>
-          <t>밍밍</t>
+          <t>지이지이</t>
         </is>
       </c>
     </row>
     <row r="917">
       <c r="A917" t="inlineStr">
         <is>
-          <t>I016</t>
+          <t>I020</t>
         </is>
       </c>
       <c r="C917" t="inlineStr">
@@ -61193,7 +62051,7 @@
     <row r="918">
       <c r="A918" t="inlineStr">
         <is>
-          <t>I017</t>
+          <t>I021</t>
         </is>
       </c>
       <c r="C918" t="inlineStr">
@@ -61208,14 +62066,14 @@
       </c>
       <c r="E918" t="inlineStr">
         <is>
-          <t>쌔앵쌔앵</t>
+          <t>지이지이</t>
         </is>
       </c>
     </row>
     <row r="919">
       <c r="A919" t="inlineStr">
         <is>
-          <t>I017</t>
+          <t>I021</t>
         </is>
       </c>
       <c r="C919" t="inlineStr">
@@ -61237,7 +62095,7 @@
     <row r="920">
       <c r="A920" t="inlineStr">
         <is>
-          <t>I018</t>
+          <t>I022</t>
         </is>
       </c>
       <c r="C920" t="inlineStr">
@@ -61252,14 +62110,14 @@
       </c>
       <c r="E920" t="inlineStr">
         <is>
-          <t>쯔쿠쯔쿠</t>
+          <t>지이지이</t>
         </is>
       </c>
     </row>
     <row r="921">
       <c r="A921" t="inlineStr">
         <is>
-          <t>I018</t>
+          <t>I022</t>
         </is>
       </c>
       <c r="C921" t="inlineStr">
@@ -61281,7 +62139,7 @@
     <row r="922">
       <c r="A922" t="inlineStr">
         <is>
-          <t>I019</t>
+          <t>I023</t>
         </is>
       </c>
       <c r="C922" t="inlineStr">
@@ -61296,14 +62154,14 @@
       </c>
       <c r="E922" t="inlineStr">
         <is>
-          <t>카나카나</t>
+          <t>붕붕</t>
         </is>
       </c>
     </row>
     <row r="923">
       <c r="A923" t="inlineStr">
         <is>
-          <t>I019</t>
+          <t>I023</t>
         </is>
       </c>
       <c r="C923" t="inlineStr">
@@ -61318,14 +62176,14 @@
       </c>
       <c r="E923" t="inlineStr">
         <is>
-          <t>蝉蝉</t>
+          <t>嗡嗡</t>
         </is>
       </c>
     </row>
     <row r="924">
       <c r="A924" t="inlineStr">
         <is>
-          <t>I020</t>
+          <t>I024</t>
         </is>
       </c>
       <c r="C924" t="inlineStr">
@@ -61340,14 +62198,14 @@
       </c>
       <c r="E924" t="inlineStr">
         <is>
-          <t>지이지이</t>
+          <t>붕붕</t>
         </is>
       </c>
     </row>
     <row r="925">
       <c r="A925" t="inlineStr">
         <is>
-          <t>I020</t>
+          <t>I024</t>
         </is>
       </c>
       <c r="C925" t="inlineStr">
@@ -61362,14 +62220,14 @@
       </c>
       <c r="E925" t="inlineStr">
         <is>
-          <t>知了知了</t>
+          <t>嗡嗡</t>
         </is>
       </c>
     </row>
     <row r="926">
       <c r="A926" t="inlineStr">
         <is>
-          <t>I021</t>
+          <t>I025</t>
         </is>
       </c>
       <c r="C926" t="inlineStr">
@@ -61384,14 +62242,14 @@
       </c>
       <c r="E926" t="inlineStr">
         <is>
-          <t>지이지이</t>
+          <t>붕붕</t>
         </is>
       </c>
     </row>
     <row r="927">
       <c r="A927" t="inlineStr">
         <is>
-          <t>I021</t>
+          <t>I025</t>
         </is>
       </c>
       <c r="C927" t="inlineStr">
@@ -61406,14 +62264,14 @@
       </c>
       <c r="E927" t="inlineStr">
         <is>
-          <t>知了知了</t>
+          <t>嗡嗡</t>
         </is>
       </c>
     </row>
     <row r="928">
       <c r="A928" t="inlineStr">
         <is>
-          <t>I022</t>
+          <t>I026</t>
         </is>
       </c>
       <c r="C928" t="inlineStr">
@@ -61428,14 +62286,14 @@
       </c>
       <c r="E928" t="inlineStr">
         <is>
-          <t>지이지이</t>
+          <t>잉잉</t>
         </is>
       </c>
     </row>
     <row r="929">
       <c r="A929" t="inlineStr">
         <is>
-          <t>I022</t>
+          <t>I026</t>
         </is>
       </c>
       <c r="C929" t="inlineStr">
@@ -61450,14 +62308,14 @@
       </c>
       <c r="E929" t="inlineStr">
         <is>
-          <t>知了知了</t>
+          <t>嗡嗡</t>
         </is>
       </c>
     </row>
     <row r="930">
       <c r="A930" t="inlineStr">
         <is>
-          <t>I023</t>
+          <t>I027</t>
         </is>
       </c>
       <c r="C930" t="inlineStr">
@@ -61479,7 +62337,7 @@
     <row r="931">
       <c r="A931" t="inlineStr">
         <is>
-          <t>I023</t>
+          <t>I027</t>
         </is>
       </c>
       <c r="C931" t="inlineStr">
@@ -61501,7 +62359,7 @@
     <row r="932">
       <c r="A932" t="inlineStr">
         <is>
-          <t>I024</t>
+          <t>I028</t>
         </is>
       </c>
       <c r="C932" t="inlineStr">
@@ -61516,14 +62374,14 @@
       </c>
       <c r="E932" t="inlineStr">
         <is>
-          <t>붕붕</t>
+          <t>부우부우</t>
         </is>
       </c>
     </row>
     <row r="933">
       <c r="A933" t="inlineStr">
         <is>
-          <t>I024</t>
+          <t>I028</t>
         </is>
       </c>
       <c r="C933" t="inlineStr">
@@ -61545,7 +62403,7 @@
     <row r="934">
       <c r="A934" t="inlineStr">
         <is>
-          <t>I025</t>
+          <t>I029</t>
         </is>
       </c>
       <c r="C934" t="inlineStr">
@@ -61560,14 +62418,14 @@
       </c>
       <c r="E934" t="inlineStr">
         <is>
-          <t>붕붕</t>
+          <t>부우</t>
         </is>
       </c>
     </row>
     <row r="935">
       <c r="A935" t="inlineStr">
         <is>
-          <t>I025</t>
+          <t>I029</t>
         </is>
       </c>
       <c r="C935" t="inlineStr">
@@ -61589,7 +62447,7 @@
     <row r="936">
       <c r="A936" t="inlineStr">
         <is>
-          <t>I026</t>
+          <t>I030</t>
         </is>
       </c>
       <c r="C936" t="inlineStr">
@@ -61604,14 +62462,14 @@
       </c>
       <c r="E936" t="inlineStr">
         <is>
-          <t>잉잉</t>
+          <t>붕붕</t>
         </is>
       </c>
     </row>
     <row r="937">
       <c r="A937" t="inlineStr">
         <is>
-          <t>I026</t>
+          <t>I030</t>
         </is>
       </c>
       <c r="C937" t="inlineStr">
@@ -61633,7 +62491,7 @@
     <row r="938">
       <c r="A938" t="inlineStr">
         <is>
-          <t>I027</t>
+          <t>I031</t>
         </is>
       </c>
       <c r="C938" t="inlineStr">
@@ -61648,14 +62506,14 @@
       </c>
       <c r="E938" t="inlineStr">
         <is>
-          <t>붕붕</t>
+          <t>씩씩</t>
         </is>
       </c>
     </row>
     <row r="939">
       <c r="A939" t="inlineStr">
         <is>
-          <t>I027</t>
+          <t>I031</t>
         </is>
       </c>
       <c r="C939" t="inlineStr">
@@ -61670,14 +62528,14 @@
       </c>
       <c r="E939" t="inlineStr">
         <is>
-          <t>嗡嗡</t>
+          <t>嘶嘶</t>
         </is>
       </c>
     </row>
     <row r="940">
       <c r="A940" t="inlineStr">
         <is>
-          <t>I028</t>
+          <t>I032</t>
         </is>
       </c>
       <c r="C940" t="inlineStr">
@@ -61692,14 +62550,14 @@
       </c>
       <c r="E940" t="inlineStr">
         <is>
-          <t>부우부우</t>
+          <t>붕붕</t>
         </is>
       </c>
     </row>
     <row r="941">
       <c r="A941" t="inlineStr">
         <is>
-          <t>I028</t>
+          <t>I032</t>
         </is>
       </c>
       <c r="C941" t="inlineStr">
@@ -61721,7 +62579,7 @@
     <row r="942">
       <c r="A942" t="inlineStr">
         <is>
-          <t>I029</t>
+          <t>I043</t>
         </is>
       </c>
       <c r="C942" t="inlineStr">
@@ -61736,14 +62594,14 @@
       </c>
       <c r="E942" t="inlineStr">
         <is>
-          <t>부우</t>
+          <t>사각</t>
         </is>
       </c>
     </row>
     <row r="943">
       <c r="A943" t="inlineStr">
         <is>
-          <t>I029</t>
+          <t>I043</t>
         </is>
       </c>
       <c r="C943" t="inlineStr">
@@ -61758,14 +62616,14 @@
       </c>
       <c r="E943" t="inlineStr">
         <is>
-          <t>嗡嗡</t>
+          <t>沙沙</t>
         </is>
       </c>
     </row>
     <row r="944">
       <c r="A944" t="inlineStr">
         <is>
-          <t>I030</t>
+          <t>I044</t>
         </is>
       </c>
       <c r="C944" t="inlineStr">
@@ -61780,14 +62638,14 @@
       </c>
       <c r="E944" t="inlineStr">
         <is>
-          <t>붕붕</t>
+          <t>지이지이</t>
         </is>
       </c>
     </row>
     <row r="945">
       <c r="A945" t="inlineStr">
         <is>
-          <t>I030</t>
+          <t>I044</t>
         </is>
       </c>
       <c r="C945" t="inlineStr">
@@ -61802,14 +62660,14 @@
       </c>
       <c r="E945" t="inlineStr">
         <is>
-          <t>嗡嗡</t>
+          <t>叽叽</t>
         </is>
       </c>
     </row>
     <row r="946">
       <c r="A946" t="inlineStr">
         <is>
-          <t>I031</t>
+          <t>M001</t>
         </is>
       </c>
       <c r="C946" t="inlineStr">
@@ -61824,14 +62682,14 @@
       </c>
       <c r="E946" t="inlineStr">
         <is>
-          <t>씩씩</t>
+          <t>멍멍</t>
         </is>
       </c>
     </row>
     <row r="947">
       <c r="A947" t="inlineStr">
         <is>
-          <t>I031</t>
+          <t>M001</t>
         </is>
       </c>
       <c r="C947" t="inlineStr">
@@ -61846,14 +62704,14 @@
       </c>
       <c r="E947" t="inlineStr">
         <is>
-          <t>嘶嘶</t>
+          <t>汪汪</t>
         </is>
       </c>
     </row>
     <row r="948">
       <c r="A948" t="inlineStr">
         <is>
-          <t>I032</t>
+          <t>M002</t>
         </is>
       </c>
       <c r="C948" t="inlineStr">
@@ -61868,14 +62726,14 @@
       </c>
       <c r="E948" t="inlineStr">
         <is>
-          <t>붕붕</t>
+          <t>야옹</t>
         </is>
       </c>
     </row>
     <row r="949">
       <c r="A949" t="inlineStr">
         <is>
-          <t>I032</t>
+          <t>M002</t>
         </is>
       </c>
       <c r="C949" t="inlineStr">
@@ -61890,14 +62748,14 @@
       </c>
       <c r="E949" t="inlineStr">
         <is>
-          <t>嗡嗡</t>
+          <t>喵喵</t>
         </is>
       </c>
     </row>
     <row r="950">
       <c r="A950" t="inlineStr">
         <is>
-          <t>I033</t>
+          <t>M003</t>
         </is>
       </c>
       <c r="C950" t="inlineStr">
@@ -61912,14 +62770,14 @@
       </c>
       <c r="E950" t="inlineStr">
         <is>
-          <t>사각사각</t>
+          <t>으르르</t>
         </is>
       </c>
     </row>
     <row r="951">
       <c r="A951" t="inlineStr">
         <is>
-          <t>I033</t>
+          <t>M003</t>
         </is>
       </c>
       <c r="C951" t="inlineStr">
@@ -61934,14 +62792,14 @@
       </c>
       <c r="E951" t="inlineStr">
         <is>
-          <t>沙沙</t>
+          <t>吼吼</t>
         </is>
       </c>
     </row>
     <row r="952">
       <c r="A952" t="inlineStr">
         <is>
-          <t>I043</t>
+          <t>M004</t>
         </is>
       </c>
       <c r="C952" t="inlineStr">
@@ -61956,14 +62814,14 @@
       </c>
       <c r="E952" t="inlineStr">
         <is>
-          <t>사각</t>
+          <t>어흥</t>
         </is>
       </c>
     </row>
     <row r="953">
       <c r="A953" t="inlineStr">
         <is>
-          <t>I043</t>
+          <t>M004</t>
         </is>
       </c>
       <c r="C953" t="inlineStr">
@@ -61978,14 +62836,14 @@
       </c>
       <c r="E953" t="inlineStr">
         <is>
-          <t>沙沙</t>
+          <t>嗷嗷</t>
         </is>
       </c>
     </row>
     <row r="954">
       <c r="A954" t="inlineStr">
         <is>
-          <t>I044</t>
+          <t>M005</t>
         </is>
       </c>
       <c r="C954" t="inlineStr">
@@ -62000,14 +62858,14 @@
       </c>
       <c r="E954" t="inlineStr">
         <is>
-          <t>지이지이</t>
+          <t>아우우</t>
         </is>
       </c>
     </row>
     <row r="955">
       <c r="A955" t="inlineStr">
         <is>
-          <t>I044</t>
+          <t>M005</t>
         </is>
       </c>
       <c r="C955" t="inlineStr">
@@ -62022,14 +62880,14 @@
       </c>
       <c r="E955" t="inlineStr">
         <is>
-          <t>叽叽</t>
+          <t>嗷呜</t>
         </is>
       </c>
     </row>
     <row r="956">
       <c r="A956" t="inlineStr">
         <is>
-          <t>M001</t>
+          <t>M006</t>
         </is>
       </c>
       <c r="C956" t="inlineStr">
@@ -62044,14 +62902,14 @@
       </c>
       <c r="E956" t="inlineStr">
         <is>
-          <t>멍멍</t>
+          <t>캥캥</t>
         </is>
       </c>
     </row>
     <row r="957">
       <c r="A957" t="inlineStr">
         <is>
-          <t>M001</t>
+          <t>M006</t>
         </is>
       </c>
       <c r="C957" t="inlineStr">
@@ -62066,14 +62924,14 @@
       </c>
       <c r="E957" t="inlineStr">
         <is>
-          <t>汪汪</t>
+          <t>嗷嗷</t>
         </is>
       </c>
     </row>
     <row r="958">
       <c r="A958" t="inlineStr">
         <is>
-          <t>M002</t>
+          <t>M007</t>
         </is>
       </c>
       <c r="C958" t="inlineStr">
@@ -62088,14 +62946,14 @@
       </c>
       <c r="E958" t="inlineStr">
         <is>
-          <t>야옹</t>
+          <t>꾸우</t>
         </is>
       </c>
     </row>
     <row r="959">
       <c r="A959" t="inlineStr">
         <is>
-          <t>M002</t>
+          <t>M007</t>
         </is>
       </c>
       <c r="C959" t="inlineStr">
@@ -62110,14 +62968,14 @@
       </c>
       <c r="E959" t="inlineStr">
         <is>
-          <t>喵喵</t>
+          <t>咕咕</t>
         </is>
       </c>
     </row>
     <row r="960">
       <c r="A960" t="inlineStr">
         <is>
-          <t>M003</t>
+          <t>M008</t>
         </is>
       </c>
       <c r="C960" t="inlineStr">
@@ -62139,7 +62997,7 @@
     <row r="961">
       <c r="A961" t="inlineStr">
         <is>
-          <t>M003</t>
+          <t>M008</t>
         </is>
       </c>
       <c r="C961" t="inlineStr">
@@ -62161,7 +63019,7 @@
     <row r="962">
       <c r="A962" t="inlineStr">
         <is>
-          <t>M004</t>
+          <t>M009</t>
         </is>
       </c>
       <c r="C962" t="inlineStr">
@@ -62176,14 +63034,14 @@
       </c>
       <c r="E962" t="inlineStr">
         <is>
-          <t>어흥</t>
+          <t>으르르</t>
         </is>
       </c>
     </row>
     <row r="963">
       <c r="A963" t="inlineStr">
         <is>
-          <t>M004</t>
+          <t>M009</t>
         </is>
       </c>
       <c r="C963" t="inlineStr">
@@ -62198,14 +63056,14 @@
       </c>
       <c r="E963" t="inlineStr">
         <is>
-          <t>嗷嗷</t>
+          <t>吼吼</t>
         </is>
       </c>
     </row>
     <row r="964">
       <c r="A964" t="inlineStr">
         <is>
-          <t>M005</t>
+          <t>M010</t>
         </is>
       </c>
       <c r="C964" t="inlineStr">
@@ -62220,14 +63078,14 @@
       </c>
       <c r="E964" t="inlineStr">
         <is>
-          <t>아우우</t>
+          <t>으르르</t>
         </is>
       </c>
     </row>
     <row r="965">
       <c r="A965" t="inlineStr">
         <is>
-          <t>M005</t>
+          <t>M010</t>
         </is>
       </c>
       <c r="C965" t="inlineStr">
@@ -62242,14 +63100,14 @@
       </c>
       <c r="E965" t="inlineStr">
         <is>
-          <t>嗷呜</t>
+          <t>吼吼</t>
         </is>
       </c>
     </row>
     <row r="966">
       <c r="A966" t="inlineStr">
         <is>
-          <t>M006</t>
+          <t>M011</t>
         </is>
       </c>
       <c r="C966" t="inlineStr">
@@ -62264,14 +63122,14 @@
       </c>
       <c r="E966" t="inlineStr">
         <is>
-          <t>캥캥</t>
+          <t>맴맴</t>
         </is>
       </c>
     </row>
     <row r="967">
       <c r="A967" t="inlineStr">
         <is>
-          <t>M006</t>
+          <t>M011</t>
         </is>
       </c>
       <c r="C967" t="inlineStr">
@@ -62286,14 +63144,14 @@
       </c>
       <c r="E967" t="inlineStr">
         <is>
-          <t>嗷嗷</t>
+          <t>咩咩</t>
         </is>
       </c>
     </row>
     <row r="968">
       <c r="A968" t="inlineStr">
         <is>
-          <t>M007</t>
+          <t>M012</t>
         </is>
       </c>
       <c r="C968" t="inlineStr">
@@ -62308,14 +63166,14 @@
       </c>
       <c r="E968" t="inlineStr">
         <is>
-          <t>꾸우</t>
+          <t>끼이끼이</t>
         </is>
       </c>
     </row>
     <row r="969">
       <c r="A969" t="inlineStr">
         <is>
-          <t>M007</t>
+          <t>M012</t>
         </is>
       </c>
       <c r="C969" t="inlineStr">
@@ -62330,14 +63188,14 @@
       </c>
       <c r="E969" t="inlineStr">
         <is>
-          <t>咕咕</t>
+          <t>吱吱</t>
         </is>
       </c>
     </row>
     <row r="970">
       <c r="A970" t="inlineStr">
         <is>
-          <t>M008</t>
+          <t>M013</t>
         </is>
       </c>
       <c r="C970" t="inlineStr">
@@ -62352,14 +63210,14 @@
       </c>
       <c r="E970" t="inlineStr">
         <is>
-          <t>으르르</t>
+          <t>끼이끼이</t>
         </is>
       </c>
     </row>
     <row r="971">
       <c r="A971" t="inlineStr">
         <is>
-          <t>M008</t>
+          <t>M013</t>
         </is>
       </c>
       <c r="C971" t="inlineStr">
@@ -62374,14 +63232,14 @@
       </c>
       <c r="E971" t="inlineStr">
         <is>
-          <t>吼吼</t>
+          <t>吱吱</t>
         </is>
       </c>
     </row>
     <row r="972">
       <c r="A972" t="inlineStr">
         <is>
-          <t>M009</t>
+          <t>M014</t>
         </is>
       </c>
       <c r="C972" t="inlineStr">
@@ -62396,14 +63254,14 @@
       </c>
       <c r="E972" t="inlineStr">
         <is>
-          <t>으르르</t>
+          <t>아우아우</t>
         </is>
       </c>
     </row>
     <row r="973">
       <c r="A973" t="inlineStr">
         <is>
-          <t>M009</t>
+          <t>M014</t>
         </is>
       </c>
       <c r="C973" t="inlineStr">
@@ -62418,14 +63276,14 @@
       </c>
       <c r="E973" t="inlineStr">
         <is>
-          <t>吼吼</t>
+          <t>嗷嗷</t>
         </is>
       </c>
     </row>
     <row r="974">
       <c r="A974" t="inlineStr">
         <is>
-          <t>M010</t>
+          <t>M015</t>
         </is>
       </c>
       <c r="C974" t="inlineStr">
@@ -62440,14 +63298,14 @@
       </c>
       <c r="E974" t="inlineStr">
         <is>
-          <t>으르르</t>
+          <t>아우아우</t>
         </is>
       </c>
     </row>
     <row r="975">
       <c r="A975" t="inlineStr">
         <is>
-          <t>M010</t>
+          <t>M015</t>
         </is>
       </c>
       <c r="C975" t="inlineStr">
@@ -62462,14 +63320,14 @@
       </c>
       <c r="E975" t="inlineStr">
         <is>
-          <t>吼吼</t>
+          <t>嗷嗷</t>
         </is>
       </c>
     </row>
     <row r="976">
       <c r="A976" t="inlineStr">
         <is>
-          <t>M011</t>
+          <t>M016</t>
         </is>
       </c>
       <c r="C976" t="inlineStr">
@@ -62484,14 +63342,14 @@
       </c>
       <c r="E976" t="inlineStr">
         <is>
-          <t>맴맴</t>
+          <t>으르르</t>
         </is>
       </c>
     </row>
     <row r="977">
       <c r="A977" t="inlineStr">
         <is>
-          <t>M011</t>
+          <t>M016</t>
         </is>
       </c>
       <c r="C977" t="inlineStr">
@@ -62506,14 +63364,14 @@
       </c>
       <c r="E977" t="inlineStr">
         <is>
-          <t>咩咩</t>
+          <t>吼吼</t>
         </is>
       </c>
     </row>
     <row r="978">
       <c r="A978" t="inlineStr">
         <is>
-          <t>M012</t>
+          <t>M017</t>
         </is>
       </c>
       <c r="C978" t="inlineStr">
@@ -62528,14 +63386,14 @@
       </c>
       <c r="E978" t="inlineStr">
         <is>
-          <t>끼이끼이</t>
+          <t>크크크</t>
         </is>
       </c>
     </row>
     <row r="979">
       <c r="A979" t="inlineStr">
         <is>
-          <t>M012</t>
+          <t>M017</t>
         </is>
       </c>
       <c r="C979" t="inlineStr">
@@ -62550,14 +63408,14 @@
       </c>
       <c r="E979" t="inlineStr">
         <is>
-          <t>吱吱</t>
+          <t>嘿嘿</t>
         </is>
       </c>
     </row>
     <row r="980">
       <c r="A980" t="inlineStr">
         <is>
-          <t>M013</t>
+          <t>M018</t>
         </is>
       </c>
       <c r="C980" t="inlineStr">
@@ -62579,7 +63437,7 @@
     <row r="981">
       <c r="A981" t="inlineStr">
         <is>
-          <t>M013</t>
+          <t>M018</t>
         </is>
       </c>
       <c r="C981" t="inlineStr">
@@ -62594,14 +63452,14 @@
       </c>
       <c r="E981" t="inlineStr">
         <is>
-          <t>吱吱</t>
+          <t>叽叽</t>
         </is>
       </c>
     </row>
     <row r="982">
       <c r="A982" t="inlineStr">
         <is>
-          <t>M014</t>
+          <t>M019</t>
         </is>
       </c>
       <c r="C982" t="inlineStr">
@@ -62616,14 +63474,14 @@
       </c>
       <c r="E982" t="inlineStr">
         <is>
-          <t>아우아우</t>
+          <t>끼이끼이</t>
         </is>
       </c>
     </row>
     <row r="983">
       <c r="A983" t="inlineStr">
         <is>
-          <t>M014</t>
+          <t>M019</t>
         </is>
       </c>
       <c r="C983" t="inlineStr">
@@ -62638,14 +63496,14 @@
       </c>
       <c r="E983" t="inlineStr">
         <is>
-          <t>嗷嗷</t>
+          <t>吱吱</t>
         </is>
       </c>
     </row>
     <row r="984">
       <c r="A984" t="inlineStr">
         <is>
-          <t>M015</t>
+          <t>M020</t>
         </is>
       </c>
       <c r="C984" t="inlineStr">
@@ -62660,14 +63518,14 @@
       </c>
       <c r="E984" t="inlineStr">
         <is>
-          <t>아우아우</t>
+          <t>끼이끼이</t>
         </is>
       </c>
     </row>
     <row r="985">
       <c r="A985" t="inlineStr">
         <is>
-          <t>M015</t>
+          <t>M020</t>
         </is>
       </c>
       <c r="C985" t="inlineStr">
@@ -62682,14 +63540,14 @@
       </c>
       <c r="E985" t="inlineStr">
         <is>
-          <t>嗷嗷</t>
+          <t>吱吱</t>
         </is>
       </c>
     </row>
     <row r="986">
       <c r="A986" t="inlineStr">
         <is>
-          <t>M016</t>
+          <t>M021</t>
         </is>
       </c>
       <c r="C986" t="inlineStr">
@@ -62704,14 +63562,14 @@
       </c>
       <c r="E986" t="inlineStr">
         <is>
-          <t>으르르</t>
+          <t>음메</t>
         </is>
       </c>
     </row>
     <row r="987">
       <c r="A987" t="inlineStr">
         <is>
-          <t>M016</t>
+          <t>M021</t>
         </is>
       </c>
       <c r="C987" t="inlineStr">
@@ -62726,14 +63584,14 @@
       </c>
       <c r="E987" t="inlineStr">
         <is>
-          <t>吼吼</t>
+          <t>哞哞</t>
         </is>
       </c>
     </row>
     <row r="988">
       <c r="A988" t="inlineStr">
         <is>
-          <t>M017</t>
+          <t>M022</t>
         </is>
       </c>
       <c r="C988" t="inlineStr">
@@ -62748,14 +63606,14 @@
       </c>
       <c r="E988" t="inlineStr">
         <is>
-          <t>크크크</t>
+          <t>메에</t>
         </is>
       </c>
     </row>
     <row r="989">
       <c r="A989" t="inlineStr">
         <is>
-          <t>M017</t>
+          <t>M022</t>
         </is>
       </c>
       <c r="C989" t="inlineStr">
@@ -62770,14 +63628,14 @@
       </c>
       <c r="E989" t="inlineStr">
         <is>
-          <t>嘿嘿</t>
+          <t>咩咩</t>
         </is>
       </c>
     </row>
     <row r="990">
       <c r="A990" t="inlineStr">
         <is>
-          <t>M018</t>
+          <t>M023</t>
         </is>
       </c>
       <c r="C990" t="inlineStr">
@@ -62792,14 +63650,14 @@
       </c>
       <c r="E990" t="inlineStr">
         <is>
-          <t>끼이끼이</t>
+          <t>메에</t>
         </is>
       </c>
     </row>
     <row r="991">
       <c r="A991" t="inlineStr">
         <is>
-          <t>M018</t>
+          <t>M023</t>
         </is>
       </c>
       <c r="C991" t="inlineStr">
@@ -62814,14 +63672,14 @@
       </c>
       <c r="E991" t="inlineStr">
         <is>
-          <t>叽叽</t>
+          <t>咩咩</t>
         </is>
       </c>
     </row>
     <row r="992">
       <c r="A992" t="inlineStr">
         <is>
-          <t>M019</t>
+          <t>M024</t>
         </is>
       </c>
       <c r="C992" t="inlineStr">
@@ -62836,14 +63694,14 @@
       </c>
       <c r="E992" t="inlineStr">
         <is>
-          <t>끼이끼이</t>
+          <t>꿀꿀</t>
         </is>
       </c>
     </row>
     <row r="993">
       <c r="A993" t="inlineStr">
         <is>
-          <t>M019</t>
+          <t>M024</t>
         </is>
       </c>
       <c r="C993" t="inlineStr">
@@ -62858,14 +63716,14 @@
       </c>
       <c r="E993" t="inlineStr">
         <is>
-          <t>吱吱</t>
+          <t>哼哼</t>
         </is>
       </c>
     </row>
     <row r="994">
       <c r="A994" t="inlineStr">
         <is>
-          <t>M020</t>
+          <t>M025</t>
         </is>
       </c>
       <c r="C994" t="inlineStr">
@@ -62880,14 +63738,14 @@
       </c>
       <c r="E994" t="inlineStr">
         <is>
-          <t>끼이끼이</t>
+          <t>꿀꿀</t>
         </is>
       </c>
     </row>
     <row r="995">
       <c r="A995" t="inlineStr">
         <is>
-          <t>M020</t>
+          <t>M025</t>
         </is>
       </c>
       <c r="C995" t="inlineStr">
@@ -62902,14 +63760,14 @@
       </c>
       <c r="E995" t="inlineStr">
         <is>
-          <t>吱吱</t>
+          <t>哼哼</t>
         </is>
       </c>
     </row>
     <row r="996">
       <c r="A996" t="inlineStr">
         <is>
-          <t>M021</t>
+          <t>M026</t>
         </is>
       </c>
       <c r="C996" t="inlineStr">
@@ -62924,14 +63782,14 @@
       </c>
       <c r="E996" t="inlineStr">
         <is>
-          <t>음메</t>
+          <t>삐이이</t>
         </is>
       </c>
     </row>
     <row r="997">
       <c r="A997" t="inlineStr">
         <is>
-          <t>M021</t>
+          <t>M026</t>
         </is>
       </c>
       <c r="C997" t="inlineStr">
@@ -62946,14 +63804,14 @@
       </c>
       <c r="E997" t="inlineStr">
         <is>
-          <t>哞哞</t>
+          <t>呦呦</t>
         </is>
       </c>
     </row>
     <row r="998">
       <c r="A998" t="inlineStr">
         <is>
-          <t>M022</t>
+          <t>M027</t>
         </is>
       </c>
       <c r="C998" t="inlineStr">
@@ -62968,14 +63826,14 @@
       </c>
       <c r="E998" t="inlineStr">
         <is>
-          <t>메에</t>
+          <t>으르르</t>
         </is>
       </c>
     </row>
     <row r="999">
       <c r="A999" t="inlineStr">
         <is>
-          <t>M022</t>
+          <t>M027</t>
         </is>
       </c>
       <c r="C999" t="inlineStr">
@@ -62990,14 +63848,14 @@
       </c>
       <c r="E999" t="inlineStr">
         <is>
-          <t>咩咩</t>
+          <t>呼噜</t>
         </is>
       </c>
     </row>
     <row r="1000">
       <c r="A1000" t="inlineStr">
         <is>
-          <t>M023</t>
+          <t>M028</t>
         </is>
       </c>
       <c r="C1000" t="inlineStr">
@@ -63012,14 +63870,14 @@
       </c>
       <c r="E1000" t="inlineStr">
         <is>
-          <t>메에</t>
+          <t>삐이이</t>
         </is>
       </c>
     </row>
     <row r="1001">
       <c r="A1001" t="inlineStr">
         <is>
-          <t>M023</t>
+          <t>M028</t>
         </is>
       </c>
       <c r="C1001" t="inlineStr">
@@ -63034,14 +63892,14 @@
       </c>
       <c r="E1001" t="inlineStr">
         <is>
-          <t>咩咩</t>
+          <t>嘀嘀</t>
         </is>
       </c>
     </row>
     <row r="1002">
       <c r="A1002" t="inlineStr">
         <is>
-          <t>M024</t>
+          <t>M029</t>
         </is>
       </c>
       <c r="C1002" t="inlineStr">
@@ -63056,14 +63914,14 @@
       </c>
       <c r="E1002" t="inlineStr">
         <is>
-          <t>꿀꿀</t>
+          <t>음음</t>
         </is>
       </c>
     </row>
     <row r="1003">
       <c r="A1003" t="inlineStr">
         <is>
-          <t>M024</t>
+          <t>M029</t>
         </is>
       </c>
       <c r="C1003" t="inlineStr">
@@ -63085,7 +63943,7 @@
     <row r="1004">
       <c r="A1004" t="inlineStr">
         <is>
-          <t>M025</t>
+          <t>M030</t>
         </is>
       </c>
       <c r="C1004" t="inlineStr">
@@ -63100,14 +63958,14 @@
       </c>
       <c r="E1004" t="inlineStr">
         <is>
-          <t>꿀꿀</t>
+          <t>으아아</t>
         </is>
       </c>
     </row>
     <row r="1005">
       <c r="A1005" t="inlineStr">
         <is>
-          <t>M025</t>
+          <t>M030</t>
         </is>
       </c>
       <c r="C1005" t="inlineStr">
@@ -63122,14 +63980,14 @@
       </c>
       <c r="E1005" t="inlineStr">
         <is>
-          <t>哼哼</t>
+          <t>吼吼</t>
         </is>
       </c>
     </row>
     <row r="1006">
       <c r="A1006" t="inlineStr">
         <is>
-          <t>M026</t>
+          <t>M031</t>
         </is>
       </c>
       <c r="C1006" t="inlineStr">
@@ -63144,14 +64002,14 @@
       </c>
       <c r="E1006" t="inlineStr">
         <is>
-          <t>삐이이</t>
+          <t>으으으</t>
         </is>
       </c>
     </row>
     <row r="1007">
       <c r="A1007" t="inlineStr">
         <is>
-          <t>M026</t>
+          <t>M031</t>
         </is>
       </c>
       <c r="C1007" t="inlineStr">
@@ -63166,14 +64024,14 @@
       </c>
       <c r="E1007" t="inlineStr">
         <is>
-          <t>呦呦</t>
+          <t>呜呜</t>
         </is>
       </c>
     </row>
     <row r="1008">
       <c r="A1008" t="inlineStr">
         <is>
-          <t>M027</t>
+          <t>M032</t>
         </is>
       </c>
       <c r="C1008" t="inlineStr">
@@ -63188,14 +64046,14 @@
       </c>
       <c r="E1008" t="inlineStr">
         <is>
-          <t>으르르</t>
+          <t>딸깍딸깍</t>
         </is>
       </c>
     </row>
     <row r="1009">
       <c r="A1009" t="inlineStr">
         <is>
-          <t>M027</t>
+          <t>M032</t>
         </is>
       </c>
       <c r="C1009" t="inlineStr">
@@ -63210,14 +64068,14 @@
       </c>
       <c r="E1009" t="inlineStr">
         <is>
-          <t>呼噜</t>
+          <t>嗒嗒</t>
         </is>
       </c>
     </row>
     <row r="1010">
       <c r="A1010" t="inlineStr">
         <is>
-          <t>M028</t>
+          <t>M033</t>
         </is>
       </c>
       <c r="C1010" t="inlineStr">
@@ -63232,14 +64090,14 @@
       </c>
       <c r="E1010" t="inlineStr">
         <is>
-          <t>삐이이</t>
+          <t>끼이끼이</t>
         </is>
       </c>
     </row>
     <row r="1011">
       <c r="A1011" t="inlineStr">
         <is>
-          <t>M028</t>
+          <t>M033</t>
         </is>
       </c>
       <c r="C1011" t="inlineStr">
@@ -63254,14 +64112,14 @@
       </c>
       <c r="E1011" t="inlineStr">
         <is>
-          <t>嘀嘀</t>
+          <t>叽叽</t>
         </is>
       </c>
     </row>
     <row r="1012">
       <c r="A1012" t="inlineStr">
         <is>
-          <t>M029</t>
+          <t>M034</t>
         </is>
       </c>
       <c r="C1012" t="inlineStr">
@@ -63276,14 +64134,14 @@
       </c>
       <c r="E1012" t="inlineStr">
         <is>
-          <t>음음</t>
+          <t>끼이끼이</t>
         </is>
       </c>
     </row>
     <row r="1013">
       <c r="A1013" t="inlineStr">
         <is>
-          <t>M029</t>
+          <t>M034</t>
         </is>
       </c>
       <c r="C1013" t="inlineStr">
@@ -63298,14 +64156,14 @@
       </c>
       <c r="E1013" t="inlineStr">
         <is>
-          <t>哼哼</t>
+          <t>叽叽</t>
         </is>
       </c>
     </row>
     <row r="1014">
       <c r="A1014" t="inlineStr">
         <is>
-          <t>M030</t>
+          <t>M035</t>
         </is>
       </c>
       <c r="C1014" t="inlineStr">
@@ -63320,14 +64178,14 @@
       </c>
       <c r="E1014" t="inlineStr">
         <is>
-          <t>으아아</t>
+          <t>으으</t>
         </is>
       </c>
     </row>
     <row r="1015">
       <c r="A1015" t="inlineStr">
         <is>
-          <t>M030</t>
+          <t>M035</t>
         </is>
       </c>
       <c r="C1015" t="inlineStr">
@@ -63342,14 +64200,14 @@
       </c>
       <c r="E1015" t="inlineStr">
         <is>
-          <t>吼吼</t>
+          <t>咴咴</t>
         </is>
       </c>
     </row>
     <row r="1016">
       <c r="A1016" t="inlineStr">
         <is>
-          <t>M031</t>
+          <t>M036</t>
         </is>
       </c>
       <c r="C1016" t="inlineStr">
@@ -63364,14 +64222,14 @@
       </c>
       <c r="E1016" t="inlineStr">
         <is>
-          <t>으으으</t>
+          <t>음음</t>
         </is>
       </c>
     </row>
     <row r="1017">
       <c r="A1017" t="inlineStr">
         <is>
-          <t>M031</t>
+          <t>M036</t>
         </is>
       </c>
       <c r="C1017" t="inlineStr">
@@ -63386,14 +64244,14 @@
       </c>
       <c r="E1017" t="inlineStr">
         <is>
-          <t>呜呜</t>
+          <t>哼哼</t>
         </is>
       </c>
     </row>
     <row r="1018">
       <c r="A1018" t="inlineStr">
         <is>
-          <t>M032</t>
+          <t>M037</t>
         </is>
       </c>
       <c r="C1018" t="inlineStr">
@@ -63408,14 +64266,14 @@
       </c>
       <c r="E1018" t="inlineStr">
         <is>
-          <t>딸깍딸깍</t>
+          <t>히이힝</t>
         </is>
       </c>
     </row>
     <row r="1019">
       <c r="A1019" t="inlineStr">
         <is>
-          <t>M032</t>
+          <t>M037</t>
         </is>
       </c>
       <c r="C1019" t="inlineStr">
@@ -63430,14 +64288,14 @@
       </c>
       <c r="E1019" t="inlineStr">
         <is>
-          <t>嗒嗒</t>
+          <t>咴儿咴儿</t>
         </is>
       </c>
     </row>
     <row r="1020">
       <c r="A1020" t="inlineStr">
         <is>
-          <t>M033</t>
+          <t>M038</t>
         </is>
       </c>
       <c r="C1020" t="inlineStr">
@@ -63452,14 +64310,14 @@
       </c>
       <c r="E1020" t="inlineStr">
         <is>
-          <t>끼이끼이</t>
+          <t>히이힝</t>
         </is>
       </c>
     </row>
     <row r="1021">
       <c r="A1021" t="inlineStr">
         <is>
-          <t>M033</t>
+          <t>M038</t>
         </is>
       </c>
       <c r="C1021" t="inlineStr">
@@ -63474,14 +64332,14 @@
       </c>
       <c r="E1021" t="inlineStr">
         <is>
-          <t>叽叽</t>
+          <t>咴咴</t>
         </is>
       </c>
     </row>
     <row r="1022">
       <c r="A1022" t="inlineStr">
         <is>
-          <t>M034</t>
+          <t>M039</t>
         </is>
       </c>
       <c r="C1022" t="inlineStr">
@@ -63496,14 +64354,14 @@
       </c>
       <c r="E1022" t="inlineStr">
         <is>
-          <t>끼이끼이</t>
+          <t>히이힝</t>
         </is>
       </c>
     </row>
     <row r="1023">
       <c r="A1023" t="inlineStr">
         <is>
-          <t>M034</t>
+          <t>M039</t>
         </is>
       </c>
       <c r="C1023" t="inlineStr">
@@ -63518,14 +64376,14 @@
       </c>
       <c r="E1023" t="inlineStr">
         <is>
-          <t>叽叽</t>
+          <t>咴咴</t>
         </is>
       </c>
     </row>
     <row r="1024">
       <c r="A1024" t="inlineStr">
         <is>
-          <t>M035</t>
+          <t>M040</t>
         </is>
       </c>
       <c r="C1024" t="inlineStr">
@@ -63540,14 +64398,14 @@
       </c>
       <c r="E1024" t="inlineStr">
         <is>
-          <t>으으</t>
+          <t>으르르</t>
         </is>
       </c>
     </row>
     <row r="1025">
       <c r="A1025" t="inlineStr">
         <is>
-          <t>M035</t>
+          <t>M040</t>
         </is>
       </c>
       <c r="C1025" t="inlineStr">
@@ -63562,14 +64420,14 @@
       </c>
       <c r="E1025" t="inlineStr">
         <is>
-          <t>咴咴</t>
+          <t>哼哼</t>
         </is>
       </c>
     </row>
     <row r="1026">
       <c r="A1026" t="inlineStr">
         <is>
-          <t>M036</t>
+          <t>M041</t>
         </is>
       </c>
       <c r="C1026" t="inlineStr">
@@ -63584,14 +64442,14 @@
       </c>
       <c r="E1026" t="inlineStr">
         <is>
-          <t>음음</t>
+          <t>뿌우</t>
         </is>
       </c>
     </row>
     <row r="1027">
       <c r="A1027" t="inlineStr">
         <is>
-          <t>M036</t>
+          <t>M041</t>
         </is>
       </c>
       <c r="C1027" t="inlineStr">
@@ -63606,14 +64464,14 @@
       </c>
       <c r="E1027" t="inlineStr">
         <is>
-          <t>哼哼</t>
+          <t>噗噗</t>
         </is>
       </c>
     </row>
     <row r="1028">
       <c r="A1028" t="inlineStr">
         <is>
-          <t>M037</t>
+          <t>M042</t>
         </is>
       </c>
       <c r="C1028" t="inlineStr">
@@ -63628,14 +64486,14 @@
       </c>
       <c r="E1028" t="inlineStr">
         <is>
-          <t>히이힝</t>
+          <t>뿌우</t>
         </is>
       </c>
     </row>
     <row r="1029">
       <c r="A1029" t="inlineStr">
         <is>
-          <t>M037</t>
+          <t>M042</t>
         </is>
       </c>
       <c r="C1029" t="inlineStr">
@@ -63650,14 +64508,14 @@
       </c>
       <c r="E1029" t="inlineStr">
         <is>
-          <t>咴儿咴儿</t>
+          <t>噗噗</t>
         </is>
       </c>
     </row>
     <row r="1030">
       <c r="A1030" t="inlineStr">
         <is>
-          <t>M038</t>
+          <t>M043</t>
         </is>
       </c>
       <c r="C1030" t="inlineStr">
@@ -63672,14 +64530,14 @@
       </c>
       <c r="E1030" t="inlineStr">
         <is>
-          <t>히이힝</t>
+          <t>우우</t>
         </is>
       </c>
     </row>
     <row r="1031">
       <c r="A1031" t="inlineStr">
         <is>
-          <t>M038</t>
+          <t>M043</t>
         </is>
       </c>
       <c r="C1031" t="inlineStr">
@@ -63694,14 +64552,14 @@
       </c>
       <c r="E1031" t="inlineStr">
         <is>
-          <t>咴咴</t>
+          <t>吱吱</t>
         </is>
       </c>
     </row>
     <row r="1032">
       <c r="A1032" t="inlineStr">
         <is>
-          <t>M039</t>
+          <t>M044</t>
         </is>
       </c>
       <c r="C1032" t="inlineStr">
@@ -63716,14 +64574,14 @@
       </c>
       <c r="E1032" t="inlineStr">
         <is>
-          <t>히이힝</t>
+          <t>우우</t>
         </is>
       </c>
     </row>
     <row r="1033">
       <c r="A1033" t="inlineStr">
         <is>
-          <t>M039</t>
+          <t>M044</t>
         </is>
       </c>
       <c r="C1033" t="inlineStr">
@@ -63738,14 +64596,14 @@
       </c>
       <c r="E1033" t="inlineStr">
         <is>
-          <t>咴咴</t>
+          <t>嗯嗯</t>
         </is>
       </c>
     </row>
     <row r="1034">
       <c r="A1034" t="inlineStr">
         <is>
-          <t>M040</t>
+          <t>M045</t>
         </is>
       </c>
       <c r="C1034" t="inlineStr">
@@ -63760,14 +64618,14 @@
       </c>
       <c r="E1034" t="inlineStr">
         <is>
-          <t>으르르</t>
+          <t>후우후우</t>
         </is>
       </c>
     </row>
     <row r="1035">
       <c r="A1035" t="inlineStr">
         <is>
-          <t>M040</t>
+          <t>M045</t>
         </is>
       </c>
       <c r="C1035" t="inlineStr">
@@ -63782,14 +64640,14 @@
       </c>
       <c r="E1035" t="inlineStr">
         <is>
-          <t>哼哼</t>
+          <t>呜呜</t>
         </is>
       </c>
     </row>
     <row r="1036">
       <c r="A1036" t="inlineStr">
         <is>
-          <t>M041</t>
+          <t>M047</t>
         </is>
       </c>
       <c r="C1036" t="inlineStr">
@@ -63804,14 +64662,14 @@
       </c>
       <c r="E1036" t="inlineStr">
         <is>
-          <t>뿌우</t>
+          <t>아우우</t>
         </is>
       </c>
     </row>
     <row r="1037">
       <c r="A1037" t="inlineStr">
         <is>
-          <t>M041</t>
+          <t>M047</t>
         </is>
       </c>
       <c r="C1037" t="inlineStr">
@@ -63826,14 +64684,14 @@
       </c>
       <c r="E1037" t="inlineStr">
         <is>
-          <t>噗噗</t>
+          <t>嗷嗷</t>
         </is>
       </c>
     </row>
     <row r="1038">
       <c r="A1038" t="inlineStr">
         <is>
-          <t>M042</t>
+          <t>M048</t>
         </is>
       </c>
       <c r="C1038" t="inlineStr">
@@ -63848,14 +64706,14 @@
       </c>
       <c r="E1038" t="inlineStr">
         <is>
-          <t>뿌우</t>
+          <t>꼬옥꼬옥</t>
         </is>
       </c>
     </row>
     <row r="1039">
       <c r="A1039" t="inlineStr">
         <is>
-          <t>M042</t>
+          <t>M048</t>
         </is>
       </c>
       <c r="C1039" t="inlineStr">
@@ -63870,14 +64728,14 @@
       </c>
       <c r="E1039" t="inlineStr">
         <is>
-          <t>噗噗</t>
+          <t>咕咕</t>
         </is>
       </c>
     </row>
     <row r="1040">
       <c r="A1040" t="inlineStr">
         <is>
-          <t>M043</t>
+          <t>M049</t>
         </is>
       </c>
       <c r="C1040" t="inlineStr">
@@ -63892,14 +64750,14 @@
       </c>
       <c r="E1040" t="inlineStr">
         <is>
-          <t>우우</t>
+          <t>찍찍</t>
         </is>
       </c>
     </row>
     <row r="1041">
       <c r="A1041" t="inlineStr">
         <is>
-          <t>M043</t>
+          <t>M049</t>
         </is>
       </c>
       <c r="C1041" t="inlineStr">
@@ -63921,7 +64779,7 @@
     <row r="1042">
       <c r="A1042" t="inlineStr">
         <is>
-          <t>M044</t>
+          <t>M050</t>
         </is>
       </c>
       <c r="C1042" t="inlineStr">
@@ -63936,14 +64794,14 @@
       </c>
       <c r="E1042" t="inlineStr">
         <is>
-          <t>우우</t>
+          <t>찍찍</t>
         </is>
       </c>
     </row>
     <row r="1043">
       <c r="A1043" t="inlineStr">
         <is>
-          <t>M044</t>
+          <t>M050</t>
         </is>
       </c>
       <c r="C1043" t="inlineStr">
@@ -63958,14 +64816,14 @@
       </c>
       <c r="E1043" t="inlineStr">
         <is>
-          <t>嗯嗯</t>
+          <t>吱吱</t>
         </is>
       </c>
     </row>
     <row r="1044">
       <c r="A1044" t="inlineStr">
         <is>
-          <t>M045</t>
+          <t>M051</t>
         </is>
       </c>
       <c r="C1044" t="inlineStr">
@@ -63980,14 +64838,14 @@
       </c>
       <c r="E1044" t="inlineStr">
         <is>
-          <t>후우후우</t>
+          <t>끼이끼이</t>
         </is>
       </c>
     </row>
     <row r="1045">
       <c r="A1045" t="inlineStr">
         <is>
-          <t>M045</t>
+          <t>M051</t>
         </is>
       </c>
       <c r="C1045" t="inlineStr">
@@ -64002,14 +64860,14 @@
       </c>
       <c r="E1045" t="inlineStr">
         <is>
-          <t>呜呜</t>
+          <t>吱吱</t>
         </is>
       </c>
     </row>
     <row r="1046">
       <c r="A1046" t="inlineStr">
         <is>
-          <t>M047</t>
+          <t>M052</t>
         </is>
       </c>
       <c r="C1046" t="inlineStr">
@@ -64024,14 +64882,14 @@
       </c>
       <c r="E1046" t="inlineStr">
         <is>
-          <t>아우우</t>
+          <t>끼이끼이</t>
         </is>
       </c>
     </row>
     <row r="1047">
       <c r="A1047" t="inlineStr">
         <is>
-          <t>M047</t>
+          <t>M052</t>
         </is>
       </c>
       <c r="C1047" t="inlineStr">
@@ -64046,14 +64904,14 @@
       </c>
       <c r="E1047" t="inlineStr">
         <is>
-          <t>嗷嗷</t>
+          <t>吱吱</t>
         </is>
       </c>
     </row>
     <row r="1048">
       <c r="A1048" t="inlineStr">
         <is>
-          <t>M048</t>
+          <t>M053</t>
         </is>
       </c>
       <c r="C1048" t="inlineStr">
@@ -64068,14 +64926,14 @@
       </c>
       <c r="E1048" t="inlineStr">
         <is>
-          <t>꼬옥꼬옥</t>
+          <t>끼이끼이</t>
         </is>
       </c>
     </row>
     <row r="1049">
       <c r="A1049" t="inlineStr">
         <is>
-          <t>M048</t>
+          <t>M053</t>
         </is>
       </c>
       <c r="C1049" t="inlineStr">
@@ -64090,14 +64948,14 @@
       </c>
       <c r="E1049" t="inlineStr">
         <is>
-          <t>咕咕</t>
+          <t>吱吱</t>
         </is>
       </c>
     </row>
     <row r="1050">
       <c r="A1050" t="inlineStr">
         <is>
-          <t>M049</t>
+          <t>M054</t>
         </is>
       </c>
       <c r="C1050" t="inlineStr">
@@ -64112,14 +64970,14 @@
       </c>
       <c r="E1050" t="inlineStr">
         <is>
-          <t>찍찍</t>
+          <t>끼이끼이</t>
         </is>
       </c>
     </row>
     <row r="1051">
       <c r="A1051" t="inlineStr">
         <is>
-          <t>M049</t>
+          <t>M054</t>
         </is>
       </c>
       <c r="C1051" t="inlineStr">
@@ -64141,7 +64999,7 @@
     <row r="1052">
       <c r="A1052" t="inlineStr">
         <is>
-          <t>M050</t>
+          <t>M055</t>
         </is>
       </c>
       <c r="C1052" t="inlineStr">
@@ -64156,14 +65014,14 @@
       </c>
       <c r="E1052" t="inlineStr">
         <is>
-          <t>찍찍</t>
+          <t>끼이끼이</t>
         </is>
       </c>
     </row>
     <row r="1053">
       <c r="A1053" t="inlineStr">
         <is>
-          <t>M050</t>
+          <t>M055</t>
         </is>
       </c>
       <c r="C1053" t="inlineStr">
@@ -64185,7 +65043,7 @@
     <row r="1054">
       <c r="A1054" t="inlineStr">
         <is>
-          <t>M051</t>
+          <t>M056</t>
         </is>
       </c>
       <c r="C1054" t="inlineStr">
@@ -64207,7 +65065,7 @@
     <row r="1055">
       <c r="A1055" t="inlineStr">
         <is>
-          <t>M051</t>
+          <t>M056</t>
         </is>
       </c>
       <c r="C1055" t="inlineStr">
@@ -64229,7 +65087,7 @@
     <row r="1056">
       <c r="A1056" t="inlineStr">
         <is>
-          <t>M052</t>
+          <t>M057</t>
         </is>
       </c>
       <c r="C1056" t="inlineStr">
@@ -64251,7 +65109,7 @@
     <row r="1057">
       <c r="A1057" t="inlineStr">
         <is>
-          <t>M052</t>
+          <t>M057</t>
         </is>
       </c>
       <c r="C1057" t="inlineStr">
@@ -64273,7 +65131,7 @@
     <row r="1058">
       <c r="A1058" t="inlineStr">
         <is>
-          <t>M053</t>
+          <t>M058</t>
         </is>
       </c>
       <c r="C1058" t="inlineStr">
@@ -64295,7 +65153,7 @@
     <row r="1059">
       <c r="A1059" t="inlineStr">
         <is>
-          <t>M053</t>
+          <t>M058</t>
         </is>
       </c>
       <c r="C1059" t="inlineStr">
@@ -64317,7 +65175,7 @@
     <row r="1060">
       <c r="A1060" t="inlineStr">
         <is>
-          <t>M054</t>
+          <t>M059</t>
         </is>
       </c>
       <c r="C1060" t="inlineStr">
@@ -64332,14 +65190,14 @@
       </c>
       <c r="E1060" t="inlineStr">
         <is>
-          <t>끼이끼이</t>
+          <t>삐이이</t>
         </is>
       </c>
     </row>
     <row r="1061">
       <c r="A1061" t="inlineStr">
         <is>
-          <t>M054</t>
+          <t>M059</t>
         </is>
       </c>
       <c r="C1061" t="inlineStr">
@@ -64354,14 +65212,14 @@
       </c>
       <c r="E1061" t="inlineStr">
         <is>
-          <t>吱吱</t>
+          <t>叽叽</t>
         </is>
       </c>
     </row>
     <row r="1062">
       <c r="A1062" t="inlineStr">
         <is>
-          <t>M055</t>
+          <t>M060</t>
         </is>
       </c>
       <c r="C1062" t="inlineStr">
@@ -64383,7 +65241,7 @@
     <row r="1063">
       <c r="A1063" t="inlineStr">
         <is>
-          <t>M055</t>
+          <t>M060</t>
         </is>
       </c>
       <c r="C1063" t="inlineStr">
@@ -64405,7 +65263,7 @@
     <row r="1064">
       <c r="A1064" t="inlineStr">
         <is>
-          <t>M056</t>
+          <t>M061</t>
         </is>
       </c>
       <c r="C1064" t="inlineStr">
@@ -64427,7 +65285,7 @@
     <row r="1065">
       <c r="A1065" t="inlineStr">
         <is>
-          <t>M056</t>
+          <t>M061</t>
         </is>
       </c>
       <c r="C1065" t="inlineStr">
@@ -64449,7 +65307,7 @@
     <row r="1066">
       <c r="A1066" t="inlineStr">
         <is>
-          <t>M057</t>
+          <t>M062</t>
         </is>
       </c>
       <c r="C1066" t="inlineStr">
@@ -64471,7 +65329,7 @@
     <row r="1067">
       <c r="A1067" t="inlineStr">
         <is>
-          <t>M057</t>
+          <t>M062</t>
         </is>
       </c>
       <c r="C1067" t="inlineStr">
@@ -64493,7 +65351,7 @@
     <row r="1068">
       <c r="A1068" t="inlineStr">
         <is>
-          <t>M058</t>
+          <t>M063</t>
         </is>
       </c>
       <c r="C1068" t="inlineStr">
@@ -64508,14 +65366,14 @@
       </c>
       <c r="E1068" t="inlineStr">
         <is>
-          <t>끼이끼이</t>
+          <t>으으</t>
         </is>
       </c>
     </row>
     <row r="1069">
       <c r="A1069" t="inlineStr">
         <is>
-          <t>M058</t>
+          <t>M063</t>
         </is>
       </c>
       <c r="C1069" t="inlineStr">
@@ -64530,14 +65388,14 @@
       </c>
       <c r="E1069" t="inlineStr">
         <is>
-          <t>吱吱</t>
+          <t>哼哼</t>
         </is>
       </c>
     </row>
     <row r="1070">
       <c r="A1070" t="inlineStr">
         <is>
-          <t>M059</t>
+          <t>M064</t>
         </is>
       </c>
       <c r="C1070" t="inlineStr">
@@ -64552,14 +65410,14 @@
       </c>
       <c r="E1070" t="inlineStr">
         <is>
-          <t>삐이이</t>
+          <t>끼이끼이</t>
         </is>
       </c>
     </row>
     <row r="1071">
       <c r="A1071" t="inlineStr">
         <is>
-          <t>M059</t>
+          <t>M064</t>
         </is>
       </c>
       <c r="C1071" t="inlineStr">
@@ -64574,14 +65432,14 @@
       </c>
       <c r="E1071" t="inlineStr">
         <is>
-          <t>叽叽</t>
+          <t>吱吱</t>
         </is>
       </c>
     </row>
     <row r="1072">
       <c r="A1072" t="inlineStr">
         <is>
-          <t>M060</t>
+          <t>M065</t>
         </is>
       </c>
       <c r="C1072" t="inlineStr">
@@ -64596,14 +65454,14 @@
       </c>
       <c r="E1072" t="inlineStr">
         <is>
-          <t>끼이끼이</t>
+          <t>끼이끼이야</t>
         </is>
       </c>
     </row>
     <row r="1073">
       <c r="A1073" t="inlineStr">
         <is>
-          <t>M060</t>
+          <t>M065</t>
         </is>
       </c>
       <c r="C1073" t="inlineStr">
@@ -64618,14 +65476,14 @@
       </c>
       <c r="E1073" t="inlineStr">
         <is>
-          <t>吱吱</t>
+          <t>嘎嘎</t>
         </is>
       </c>
     </row>
     <row r="1074">
       <c r="A1074" t="inlineStr">
         <is>
-          <t>M061</t>
+          <t>M066</t>
         </is>
       </c>
       <c r="C1074" t="inlineStr">
@@ -64640,14 +65498,14 @@
       </c>
       <c r="E1074" t="inlineStr">
         <is>
-          <t>끼이끼이</t>
+          <t>으으</t>
         </is>
       </c>
     </row>
     <row r="1075">
       <c r="A1075" t="inlineStr">
         <is>
-          <t>M061</t>
+          <t>M066</t>
         </is>
       </c>
       <c r="C1075" t="inlineStr">
@@ -64662,14 +65520,14 @@
       </c>
       <c r="E1075" t="inlineStr">
         <is>
-          <t>吱吱</t>
+          <t>哼哼</t>
         </is>
       </c>
     </row>
     <row r="1076">
       <c r="A1076" t="inlineStr">
         <is>
-          <t>M062</t>
+          <t>M067</t>
         </is>
       </c>
       <c r="C1076" t="inlineStr">
@@ -64691,7 +65549,7 @@
     <row r="1077">
       <c r="A1077" t="inlineStr">
         <is>
-          <t>M062</t>
+          <t>M067</t>
         </is>
       </c>
       <c r="C1077" t="inlineStr">
@@ -64713,7 +65571,7 @@
     <row r="1078">
       <c r="A1078" t="inlineStr">
         <is>
-          <t>M063</t>
+          <t>M068</t>
         </is>
       </c>
       <c r="C1078" t="inlineStr">
@@ -64728,14 +65586,14 @@
       </c>
       <c r="E1078" t="inlineStr">
         <is>
-          <t>으으</t>
+          <t>씩씩</t>
         </is>
       </c>
     </row>
     <row r="1079">
       <c r="A1079" t="inlineStr">
         <is>
-          <t>M063</t>
+          <t>M068</t>
         </is>
       </c>
       <c r="C1079" t="inlineStr">
@@ -64750,14 +65608,14 @@
       </c>
       <c r="E1079" t="inlineStr">
         <is>
-          <t>哼哼</t>
+          <t>嘶嘶</t>
         </is>
       </c>
     </row>
     <row r="1080">
       <c r="A1080" t="inlineStr">
         <is>
-          <t>M064</t>
+          <t>M069</t>
         </is>
       </c>
       <c r="C1080" t="inlineStr">
@@ -64772,14 +65630,14 @@
       </c>
       <c r="E1080" t="inlineStr">
         <is>
-          <t>끼이끼이</t>
+          <t>으르르</t>
         </is>
       </c>
     </row>
     <row r="1081">
       <c r="A1081" t="inlineStr">
         <is>
-          <t>M064</t>
+          <t>M069</t>
         </is>
       </c>
       <c r="C1081" t="inlineStr">
@@ -64794,14 +65652,14 @@
       </c>
       <c r="E1081" t="inlineStr">
         <is>
-          <t>吱吱</t>
+          <t>吼吼</t>
         </is>
       </c>
     </row>
     <row r="1082">
       <c r="A1082" t="inlineStr">
         <is>
-          <t>M065</t>
+          <t>M070</t>
         </is>
       </c>
       <c r="C1082" t="inlineStr">
@@ -64816,14 +65674,14 @@
       </c>
       <c r="E1082" t="inlineStr">
         <is>
-          <t>끼이끼이야</t>
+          <t>으르르</t>
         </is>
       </c>
     </row>
     <row r="1083">
       <c r="A1083" t="inlineStr">
         <is>
-          <t>M065</t>
+          <t>M070</t>
         </is>
       </c>
       <c r="C1083" t="inlineStr">
@@ -64838,14 +65696,14 @@
       </c>
       <c r="E1083" t="inlineStr">
         <is>
-          <t>嘎嘎</t>
+          <t>吼吼</t>
         </is>
       </c>
     </row>
     <row r="1084">
       <c r="A1084" t="inlineStr">
         <is>
-          <t>M066</t>
+          <t>M071</t>
         </is>
       </c>
       <c r="C1084" t="inlineStr">
@@ -64860,14 +65718,14 @@
       </c>
       <c r="E1084" t="inlineStr">
         <is>
-          <t>으으</t>
+          <t>끼이끼이</t>
         </is>
       </c>
     </row>
     <row r="1085">
       <c r="A1085" t="inlineStr">
         <is>
-          <t>M066</t>
+          <t>M071</t>
         </is>
       </c>
       <c r="C1085" t="inlineStr">
@@ -64882,14 +65740,14 @@
       </c>
       <c r="E1085" t="inlineStr">
         <is>
-          <t>哼哼</t>
+          <t>吱吱</t>
         </is>
       </c>
     </row>
     <row r="1086">
       <c r="A1086" t="inlineStr">
         <is>
-          <t>M067</t>
+          <t>M073</t>
         </is>
       </c>
       <c r="C1086" t="inlineStr">
@@ -64911,7 +65769,7 @@
     <row r="1087">
       <c r="A1087" t="inlineStr">
         <is>
-          <t>M067</t>
+          <t>M073</t>
         </is>
       </c>
       <c r="C1087" t="inlineStr">
@@ -64926,14 +65784,14 @@
       </c>
       <c r="E1087" t="inlineStr">
         <is>
-          <t>吱吱</t>
+          <t>叽叽</t>
         </is>
       </c>
     </row>
     <row r="1088">
       <c r="A1088" t="inlineStr">
         <is>
-          <t>M068</t>
+          <t>M074</t>
         </is>
       </c>
       <c r="C1088" t="inlineStr">
@@ -64948,14 +65806,14 @@
       </c>
       <c r="E1088" t="inlineStr">
         <is>
-          <t>씩씩</t>
+          <t>으으</t>
         </is>
       </c>
     </row>
     <row r="1089">
       <c r="A1089" t="inlineStr">
         <is>
-          <t>M068</t>
+          <t>M074</t>
         </is>
       </c>
       <c r="C1089" t="inlineStr">
@@ -64970,14 +65828,14 @@
       </c>
       <c r="E1089" t="inlineStr">
         <is>
-          <t>嘶嘶</t>
+          <t>哼哼</t>
         </is>
       </c>
     </row>
     <row r="1090">
       <c r="A1090" t="inlineStr">
         <is>
-          <t>M069</t>
+          <t>M075</t>
         </is>
       </c>
       <c r="C1090" t="inlineStr">
@@ -64992,14 +65850,14 @@
       </c>
       <c r="E1090" t="inlineStr">
         <is>
-          <t>으르르</t>
+          <t>깽깽</t>
         </is>
       </c>
     </row>
     <row r="1091">
       <c r="A1091" t="inlineStr">
         <is>
-          <t>M069</t>
+          <t>M075</t>
         </is>
       </c>
       <c r="C1091" t="inlineStr">
@@ -65014,14 +65872,14 @@
       </c>
       <c r="E1091" t="inlineStr">
         <is>
-          <t>吼吼</t>
+          <t>嗷嗷</t>
         </is>
       </c>
     </row>
     <row r="1092">
       <c r="A1092" t="inlineStr">
         <is>
-          <t>M070</t>
+          <t>M076</t>
         </is>
       </c>
       <c r="C1092" t="inlineStr">
@@ -65036,14 +65894,14 @@
       </c>
       <c r="E1092" t="inlineStr">
         <is>
-          <t>으르르</t>
+          <t>씩씩</t>
         </is>
       </c>
     </row>
     <row r="1093">
       <c r="A1093" t="inlineStr">
         <is>
-          <t>M070</t>
+          <t>M076</t>
         </is>
       </c>
       <c r="C1093" t="inlineStr">
@@ -65058,14 +65916,14 @@
       </c>
       <c r="E1093" t="inlineStr">
         <is>
-          <t>吼吼</t>
+          <t>嘶嘶</t>
         </is>
       </c>
     </row>
     <row r="1094">
       <c r="A1094" t="inlineStr">
         <is>
-          <t>M071</t>
+          <t>M077</t>
         </is>
       </c>
       <c r="C1094" t="inlineStr">
@@ -65080,14 +65938,14 @@
       </c>
       <c r="E1094" t="inlineStr">
         <is>
-          <t>끼이끼이</t>
+          <t>으으</t>
         </is>
       </c>
     </row>
     <row r="1095">
       <c r="A1095" t="inlineStr">
         <is>
-          <t>M071</t>
+          <t>M077</t>
         </is>
       </c>
       <c r="C1095" t="inlineStr">
@@ -65102,14 +65960,14 @@
       </c>
       <c r="E1095" t="inlineStr">
         <is>
-          <t>吱吱</t>
+          <t>嗯嗯</t>
         </is>
       </c>
     </row>
     <row r="1096">
       <c r="A1096" t="inlineStr">
         <is>
-          <t>M073</t>
+          <t>M079</t>
         </is>
       </c>
       <c r="C1096" t="inlineStr">
@@ -65124,14 +65982,14 @@
       </c>
       <c r="E1096" t="inlineStr">
         <is>
-          <t>끼이끼이</t>
+          <t>야우우</t>
         </is>
       </c>
     </row>
     <row r="1097">
       <c r="A1097" t="inlineStr">
         <is>
-          <t>M073</t>
+          <t>M079</t>
         </is>
       </c>
       <c r="C1097" t="inlineStr">
@@ -65146,14 +66004,14 @@
       </c>
       <c r="E1097" t="inlineStr">
         <is>
-          <t>叽叽</t>
+          <t>嗷嗷</t>
         </is>
       </c>
     </row>
     <row r="1098">
       <c r="A1098" t="inlineStr">
         <is>
-          <t>M074</t>
+          <t>M080</t>
         </is>
       </c>
       <c r="C1098" t="inlineStr">
@@ -65168,14 +66026,14 @@
       </c>
       <c r="E1098" t="inlineStr">
         <is>
-          <t>으으</t>
+          <t>끼이끼이</t>
         </is>
       </c>
     </row>
     <row r="1099">
       <c r="A1099" t="inlineStr">
         <is>
-          <t>M074</t>
+          <t>M080</t>
         </is>
       </c>
       <c r="C1099" t="inlineStr">
@@ -65190,14 +66048,14 @@
       </c>
       <c r="E1099" t="inlineStr">
         <is>
-          <t>哼哼</t>
+          <t>吱吱</t>
         </is>
       </c>
     </row>
     <row r="1100">
       <c r="A1100" t="inlineStr">
         <is>
-          <t>M075</t>
+          <t>M081</t>
         </is>
       </c>
       <c r="C1100" t="inlineStr">
@@ -65212,14 +66070,14 @@
       </c>
       <c r="E1100" t="inlineStr">
         <is>
-          <t>깽깽</t>
+          <t>우우</t>
         </is>
       </c>
     </row>
     <row r="1101">
       <c r="A1101" t="inlineStr">
         <is>
-          <t>M075</t>
+          <t>M081</t>
         </is>
       </c>
       <c r="C1101" t="inlineStr">
@@ -65234,14 +66092,14 @@
       </c>
       <c r="E1101" t="inlineStr">
         <is>
-          <t>嗷嗷</t>
+          <t>呜呜</t>
         </is>
       </c>
     </row>
     <row r="1102">
       <c r="A1102" t="inlineStr">
         <is>
-          <t>M076</t>
+          <t>R001</t>
         </is>
       </c>
       <c r="C1102" t="inlineStr">
@@ -65256,14 +66114,14 @@
       </c>
       <c r="E1102" t="inlineStr">
         <is>
-          <t>씩씩</t>
+          <t>찍찍</t>
         </is>
       </c>
     </row>
     <row r="1103">
       <c r="A1103" t="inlineStr">
         <is>
-          <t>M076</t>
+          <t>R001</t>
         </is>
       </c>
       <c r="C1103" t="inlineStr">
@@ -65278,14 +66136,14 @@
       </c>
       <c r="E1103" t="inlineStr">
         <is>
-          <t>嘶嘶</t>
+          <t>叽叽</t>
         </is>
       </c>
     </row>
     <row r="1104">
       <c r="A1104" t="inlineStr">
         <is>
-          <t>M077</t>
+          <t>R002</t>
         </is>
       </c>
       <c r="C1104" t="inlineStr">
@@ -65300,14 +66158,14 @@
       </c>
       <c r="E1104" t="inlineStr">
         <is>
-          <t>으으</t>
+          <t>또게이</t>
         </is>
       </c>
     </row>
     <row r="1105">
       <c r="A1105" t="inlineStr">
         <is>
-          <t>M077</t>
+          <t>R002</t>
         </is>
       </c>
       <c r="C1105" t="inlineStr">
@@ -65322,14 +66180,14 @@
       </c>
       <c r="E1105" t="inlineStr">
         <is>
-          <t>嗯嗯</t>
+          <t>嗒嗒</t>
         </is>
       </c>
     </row>
     <row r="1106">
       <c r="A1106" t="inlineStr">
         <is>
-          <t>M079</t>
+          <t>R003</t>
         </is>
       </c>
       <c r="C1106" t="inlineStr">
@@ -65344,14 +66202,14 @@
       </c>
       <c r="E1106" t="inlineStr">
         <is>
-          <t>야우우</t>
+          <t>씩씩</t>
         </is>
       </c>
     </row>
     <row r="1107">
       <c r="A1107" t="inlineStr">
         <is>
-          <t>M079</t>
+          <t>R003</t>
         </is>
       </c>
       <c r="C1107" t="inlineStr">
@@ -65366,14 +66224,14 @@
       </c>
       <c r="E1107" t="inlineStr">
         <is>
-          <t>嗷嗷</t>
+          <t>嘶嘶</t>
         </is>
       </c>
     </row>
     <row r="1108">
       <c r="A1108" t="inlineStr">
         <is>
-          <t>M080</t>
+          <t>R004</t>
         </is>
       </c>
       <c r="C1108" t="inlineStr">
@@ -65388,14 +66246,14 @@
       </c>
       <c r="E1108" t="inlineStr">
         <is>
-          <t>끼이끼이</t>
+          <t>씩씩</t>
         </is>
       </c>
     </row>
     <row r="1109">
       <c r="A1109" t="inlineStr">
         <is>
-          <t>M080</t>
+          <t>R004</t>
         </is>
       </c>
       <c r="C1109" t="inlineStr">
@@ -65410,14 +66268,14 @@
       </c>
       <c r="E1109" t="inlineStr">
         <is>
-          <t>吱吱</t>
+          <t>嘶嘶</t>
         </is>
       </c>
     </row>
     <row r="1110">
       <c r="A1110" t="inlineStr">
         <is>
-          <t>M081</t>
+          <t>R005</t>
         </is>
       </c>
       <c r="C1110" t="inlineStr">
@@ -65432,14 +66290,14 @@
       </c>
       <c r="E1110" t="inlineStr">
         <is>
-          <t>우우</t>
+          <t>딸랑딸랑</t>
         </is>
       </c>
     </row>
     <row r="1111">
       <c r="A1111" t="inlineStr">
         <is>
-          <t>M081</t>
+          <t>R005</t>
         </is>
       </c>
       <c r="C1111" t="inlineStr">
@@ -65454,14 +66312,14 @@
       </c>
       <c r="E1111" t="inlineStr">
         <is>
-          <t>呜呜</t>
+          <t>嘎嘎</t>
         </is>
       </c>
     </row>
     <row r="1112">
       <c r="A1112" t="inlineStr">
         <is>
-          <t>R001</t>
+          <t>R006</t>
         </is>
       </c>
       <c r="C1112" t="inlineStr">
@@ -65476,14 +66334,14 @@
       </c>
       <c r="E1112" t="inlineStr">
         <is>
-          <t>찍찍</t>
+          <t>씩씩</t>
         </is>
       </c>
     </row>
     <row r="1113">
       <c r="A1113" t="inlineStr">
         <is>
-          <t>R001</t>
+          <t>R006</t>
         </is>
       </c>
       <c r="C1113" t="inlineStr">
@@ -65498,14 +66356,14 @@
       </c>
       <c r="E1113" t="inlineStr">
         <is>
-          <t>叽叽</t>
+          <t>嘶嘶</t>
         </is>
       </c>
     </row>
     <row r="1114">
       <c r="A1114" t="inlineStr">
         <is>
-          <t>R002</t>
+          <t>R007</t>
         </is>
       </c>
       <c r="C1114" t="inlineStr">
@@ -65520,14 +66378,14 @@
       </c>
       <c r="E1114" t="inlineStr">
         <is>
-          <t>또게이</t>
+          <t>으르르</t>
         </is>
       </c>
     </row>
     <row r="1115">
       <c r="A1115" t="inlineStr">
         <is>
-          <t>R002</t>
+          <t>R007</t>
         </is>
       </c>
       <c r="C1115" t="inlineStr">
@@ -65542,14 +66400,14 @@
       </c>
       <c r="E1115" t="inlineStr">
         <is>
-          <t>嗒嗒</t>
+          <t>吼吼</t>
         </is>
       </c>
     </row>
     <row r="1116">
       <c r="A1116" t="inlineStr">
         <is>
-          <t>R003</t>
+          <t>R008</t>
         </is>
       </c>
       <c r="C1116" t="inlineStr">
@@ -65564,14 +66422,14 @@
       </c>
       <c r="E1116" t="inlineStr">
         <is>
-          <t>씩씩</t>
+          <t>으르르</t>
         </is>
       </c>
     </row>
     <row r="1117">
       <c r="A1117" t="inlineStr">
         <is>
-          <t>R003</t>
+          <t>R008</t>
         </is>
       </c>
       <c r="C1117" t="inlineStr">
@@ -65586,14 +66444,14 @@
       </c>
       <c r="E1117" t="inlineStr">
         <is>
-          <t>嘶嘶</t>
+          <t>吼吼</t>
         </is>
       </c>
     </row>
     <row r="1118">
       <c r="A1118" t="inlineStr">
         <is>
-          <t>R004</t>
+          <t>R009</t>
         </is>
       </c>
       <c r="C1118" t="inlineStr">
@@ -65615,7 +66473,7 @@
     <row r="1119">
       <c r="A1119" t="inlineStr">
         <is>
-          <t>R004</t>
+          <t>R009</t>
         </is>
       </c>
       <c r="C1119" t="inlineStr">
@@ -65637,7 +66495,7 @@
     <row r="1120">
       <c r="A1120" t="inlineStr">
         <is>
-          <t>R005</t>
+          <t>R010</t>
         </is>
       </c>
       <c r="C1120" t="inlineStr">
@@ -65652,14 +66510,14 @@
       </c>
       <c r="E1120" t="inlineStr">
         <is>
-          <t>딸랑딸랑</t>
+          <t>씩씩</t>
         </is>
       </c>
     </row>
     <row r="1121">
       <c r="A1121" t="inlineStr">
         <is>
-          <t>R005</t>
+          <t>R010</t>
         </is>
       </c>
       <c r="C1121" t="inlineStr">
@@ -65674,14 +66532,14 @@
       </c>
       <c r="E1121" t="inlineStr">
         <is>
-          <t>嘎嘎</t>
+          <t>嘶嘶</t>
         </is>
       </c>
     </row>
     <row r="1122">
       <c r="A1122" t="inlineStr">
         <is>
-          <t>R006</t>
+          <t>R011</t>
         </is>
       </c>
       <c r="C1122" t="inlineStr">
@@ -65696,14 +66554,14 @@
       </c>
       <c r="E1122" t="inlineStr">
         <is>
-          <t>씩씩</t>
+          <t>끼이</t>
         </is>
       </c>
     </row>
     <row r="1123">
       <c r="A1123" t="inlineStr">
         <is>
-          <t>R006</t>
+          <t>R011</t>
         </is>
       </c>
       <c r="C1123" t="inlineStr">
@@ -65718,14 +66576,14 @@
       </c>
       <c r="E1123" t="inlineStr">
         <is>
-          <t>嘶嘶</t>
+          <t>叽叽</t>
         </is>
       </c>
     </row>
     <row r="1124">
       <c r="A1124" t="inlineStr">
         <is>
-          <t>R007</t>
+          <t>R013</t>
         </is>
       </c>
       <c r="C1124" t="inlineStr">
@@ -65740,14 +66598,14 @@
       </c>
       <c r="E1124" t="inlineStr">
         <is>
-          <t>으르르</t>
+          <t>씩씩</t>
         </is>
       </c>
     </row>
     <row r="1125">
       <c r="A1125" t="inlineStr">
         <is>
-          <t>R007</t>
+          <t>R013</t>
         </is>
       </c>
       <c r="C1125" t="inlineStr">
@@ -65762,14 +66620,14 @@
       </c>
       <c r="E1125" t="inlineStr">
         <is>
-          <t>吼吼</t>
+          <t>嘶嘶</t>
         </is>
       </c>
     </row>
     <row r="1126">
       <c r="A1126" t="inlineStr">
         <is>
-          <t>R008</t>
+          <t>R014</t>
         </is>
       </c>
       <c r="C1126" t="inlineStr">
@@ -65784,14 +66642,14 @@
       </c>
       <c r="E1126" t="inlineStr">
         <is>
-          <t>으르르</t>
+          <t>씩씩</t>
         </is>
       </c>
     </row>
     <row r="1127">
       <c r="A1127" t="inlineStr">
         <is>
-          <t>R008</t>
+          <t>R014</t>
         </is>
       </c>
       <c r="C1127" t="inlineStr">
@@ -65806,14 +66664,14 @@
       </c>
       <c r="E1127" t="inlineStr">
         <is>
-          <t>吼吼</t>
+          <t>嘶嘶</t>
         </is>
       </c>
     </row>
     <row r="1128">
       <c r="A1128" t="inlineStr">
         <is>
-          <t>R009</t>
+          <t>R015</t>
         </is>
       </c>
       <c r="C1128" t="inlineStr">
@@ -65828,14 +66686,14 @@
       </c>
       <c r="E1128" t="inlineStr">
         <is>
-          <t>씩씩</t>
+          <t>으으</t>
         </is>
       </c>
     </row>
     <row r="1129">
       <c r="A1129" t="inlineStr">
         <is>
-          <t>R009</t>
+          <t>R015</t>
         </is>
       </c>
       <c r="C1129" t="inlineStr">
@@ -65850,14 +66708,14 @@
       </c>
       <c r="E1129" t="inlineStr">
         <is>
-          <t>嘶嘶</t>
+          <t>嗯嗯</t>
         </is>
       </c>
     </row>
     <row r="1130">
       <c r="A1130" t="inlineStr">
         <is>
-          <t>R010</t>
+          <t>R016</t>
         </is>
       </c>
       <c r="C1130" t="inlineStr">
@@ -65872,14 +66730,14 @@
       </c>
       <c r="E1130" t="inlineStr">
         <is>
-          <t>씩씩</t>
+          <t>딸랑딸랑</t>
         </is>
       </c>
     </row>
     <row r="1131">
       <c r="A1131" t="inlineStr">
         <is>
-          <t>R010</t>
+          <t>R016</t>
         </is>
       </c>
       <c r="C1131" t="inlineStr">
@@ -65894,14 +66752,14 @@
       </c>
       <c r="E1131" t="inlineStr">
         <is>
-          <t>嘶嘶</t>
+          <t>嘎嘎</t>
         </is>
       </c>
     </row>
     <row r="1132">
       <c r="A1132" t="inlineStr">
         <is>
-          <t>R011</t>
+          <t>R017</t>
         </is>
       </c>
       <c r="C1132" t="inlineStr">
@@ -65916,14 +66774,14 @@
       </c>
       <c r="E1132" t="inlineStr">
         <is>
-          <t>끼이</t>
+          <t>씩씩</t>
         </is>
       </c>
     </row>
     <row r="1133">
       <c r="A1133" t="inlineStr">
         <is>
-          <t>R011</t>
+          <t>R017</t>
         </is>
       </c>
       <c r="C1133" t="inlineStr">
@@ -65938,14 +66796,14 @@
       </c>
       <c r="E1133" t="inlineStr">
         <is>
-          <t>叽叽</t>
+          <t>嘶嘶</t>
         </is>
       </c>
     </row>
     <row r="1134">
       <c r="A1134" t="inlineStr">
         <is>
-          <t>R012</t>
+          <t>R018</t>
         </is>
       </c>
       <c r="C1134" t="inlineStr">
@@ -65960,14 +66818,14 @@
       </c>
       <c r="E1134" t="inlineStr">
         <is>
-          <t>사각사각</t>
+          <t>찍찍</t>
         </is>
       </c>
     </row>
     <row r="1135">
       <c r="A1135" t="inlineStr">
         <is>
-          <t>R012</t>
+          <t>R018</t>
         </is>
       </c>
       <c r="C1135" t="inlineStr">
@@ -65982,14 +66840,14 @@
       </c>
       <c r="E1135" t="inlineStr">
         <is>
-          <t>沙沙</t>
+          <t>叽叽</t>
         </is>
       </c>
     </row>
     <row r="1136">
       <c r="A1136" t="inlineStr">
         <is>
-          <t>R013</t>
+          <t>R019</t>
         </is>
       </c>
       <c r="C1136" t="inlineStr">
@@ -66004,14 +66862,14 @@
       </c>
       <c r="E1136" t="inlineStr">
         <is>
-          <t>씩씩</t>
+          <t>으르르</t>
         </is>
       </c>
     </row>
     <row r="1137">
       <c r="A1137" t="inlineStr">
         <is>
-          <t>R013</t>
+          <t>R019</t>
         </is>
       </c>
       <c r="C1137" t="inlineStr">
@@ -66026,14 +66884,14 @@
       </c>
       <c r="E1137" t="inlineStr">
         <is>
-          <t>嘶嘶</t>
+          <t>吼吼</t>
         </is>
       </c>
     </row>
     <row r="1138">
       <c r="A1138" t="inlineStr">
         <is>
-          <t>R014</t>
+          <t>R020</t>
         </is>
       </c>
       <c r="C1138" t="inlineStr">
@@ -66055,7 +66913,7 @@
     <row r="1139">
       <c r="A1139" t="inlineStr">
         <is>
-          <t>R014</t>
+          <t>R020</t>
         </is>
       </c>
       <c r="C1139" t="inlineStr">
@@ -66077,7 +66935,7 @@
     <row r="1140">
       <c r="A1140" t="inlineStr">
         <is>
-          <t>R015</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="C1140" t="inlineStr">
@@ -66092,14 +66950,14 @@
       </c>
       <c r="E1140" t="inlineStr">
         <is>
-          <t>으으</t>
+          <t>꾸우꾸우</t>
         </is>
       </c>
     </row>
     <row r="1141">
       <c r="A1141" t="inlineStr">
         <is>
-          <t>R015</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="C1141" t="inlineStr">
@@ -66114,14 +66972,14 @@
       </c>
       <c r="E1141" t="inlineStr">
         <is>
-          <t>嗯嗯</t>
+          <t>咕咕</t>
         </is>
       </c>
     </row>
     <row r="1142">
       <c r="A1142" t="inlineStr">
         <is>
-          <t>R016</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="C1142" t="inlineStr">
@@ -66136,14 +66994,14 @@
       </c>
       <c r="E1142" t="inlineStr">
         <is>
-          <t>딸랑딸랑</t>
+          <t>뻐억뻐억</t>
         </is>
       </c>
     </row>
     <row r="1143">
       <c r="A1143" t="inlineStr">
         <is>
-          <t>R016</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="C1143" t="inlineStr">
@@ -66158,14 +67016,14 @@
       </c>
       <c r="E1143" t="inlineStr">
         <is>
-          <t>嘎嘎</t>
+          <t>噗噗</t>
         </is>
       </c>
     </row>
     <row r="1144">
       <c r="A1144" t="inlineStr">
         <is>
-          <t>R017</t>
+          <t>S003</t>
         </is>
       </c>
       <c r="C1144" t="inlineStr">
@@ -66180,14 +67038,14 @@
       </c>
       <c r="E1144" t="inlineStr">
         <is>
-          <t>씩씩</t>
+          <t>끼이끼이</t>
         </is>
       </c>
     </row>
     <row r="1145">
       <c r="A1145" t="inlineStr">
         <is>
-          <t>R017</t>
+          <t>S003</t>
         </is>
       </c>
       <c r="C1145" t="inlineStr">
@@ -66202,14 +67060,14 @@
       </c>
       <c r="E1145" t="inlineStr">
         <is>
-          <t>嘶嘶</t>
+          <t>叽叽</t>
         </is>
       </c>
     </row>
     <row r="1146">
       <c r="A1146" t="inlineStr">
         <is>
-          <t>R018</t>
+          <t>S004</t>
         </is>
       </c>
       <c r="C1146" t="inlineStr">
@@ -66224,14 +67082,14 @@
       </c>
       <c r="E1146" t="inlineStr">
         <is>
-          <t>찍찍</t>
+          <t>끼이끼이</t>
         </is>
       </c>
     </row>
     <row r="1147">
       <c r="A1147" t="inlineStr">
         <is>
-          <t>R018</t>
+          <t>S004</t>
         </is>
       </c>
       <c r="C1147" t="inlineStr">
@@ -66253,7 +67111,7 @@
     <row r="1148">
       <c r="A1148" t="inlineStr">
         <is>
-          <t>R019</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="C1148" t="inlineStr">
@@ -66268,14 +67126,14 @@
       </c>
       <c r="E1148" t="inlineStr">
         <is>
-          <t>으르르</t>
+          <t>딱딱딱</t>
         </is>
       </c>
     </row>
     <row r="1149">
       <c r="A1149" t="inlineStr">
         <is>
-          <t>R019</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="C1149" t="inlineStr">
@@ -66290,14 +67148,14 @@
       </c>
       <c r="E1149" t="inlineStr">
         <is>
-          <t>吼吼</t>
+          <t>嗒嗒</t>
         </is>
       </c>
     </row>
     <row r="1150">
       <c r="A1150" t="inlineStr">
         <is>
-          <t>R020</t>
+          <t>S006</t>
         </is>
       </c>
       <c r="C1150" t="inlineStr">
@@ -66312,14 +67170,14 @@
       </c>
       <c r="E1150" t="inlineStr">
         <is>
-          <t>씩씩</t>
+          <t>우우우</t>
         </is>
       </c>
     </row>
     <row r="1151">
       <c r="A1151" t="inlineStr">
         <is>
-          <t>R020</t>
+          <t>S006</t>
         </is>
       </c>
       <c r="C1151" t="inlineStr">
@@ -66334,14 +67192,14 @@
       </c>
       <c r="E1151" t="inlineStr">
         <is>
-          <t>嘶嘶</t>
+          <t>嗡嗡</t>
         </is>
       </c>
     </row>
     <row r="1152">
       <c r="A1152" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S007</t>
         </is>
       </c>
       <c r="C1152" t="inlineStr">
@@ -66356,14 +67214,14 @@
       </c>
       <c r="E1152" t="inlineStr">
         <is>
-          <t>꾸우꾸우</t>
+          <t>두두두</t>
         </is>
       </c>
     </row>
     <row r="1153">
       <c r="A1153" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S007</t>
         </is>
       </c>
       <c r="C1153" t="inlineStr">
@@ -66378,14 +67236,14 @@
       </c>
       <c r="E1153" t="inlineStr">
         <is>
-          <t>咕咕</t>
+          <t>咚咚</t>
         </is>
       </c>
     </row>
     <row r="1154">
       <c r="A1154" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S008</t>
         </is>
       </c>
       <c r="C1154" t="inlineStr">
@@ -66400,14 +67258,14 @@
       </c>
       <c r="E1154" t="inlineStr">
         <is>
-          <t>뻐억뻐억</t>
+          <t>끼이끼이</t>
         </is>
       </c>
     </row>
     <row r="1155">
       <c r="A1155" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S008</t>
         </is>
       </c>
       <c r="C1155" t="inlineStr">
@@ -66422,14 +67280,14 @@
       </c>
       <c r="E1155" t="inlineStr">
         <is>
-          <t>噗噗</t>
+          <t>叽叽</t>
         </is>
       </c>
     </row>
     <row r="1156">
       <c r="A1156" t="inlineStr">
         <is>
-          <t>S003</t>
+          <t>S009</t>
         </is>
       </c>
       <c r="C1156" t="inlineStr">
@@ -66444,14 +67302,14 @@
       </c>
       <c r="E1156" t="inlineStr">
         <is>
-          <t>끼이끼이</t>
+          <t>우우우</t>
         </is>
       </c>
     </row>
     <row r="1157">
       <c r="A1157" t="inlineStr">
         <is>
-          <t>S003</t>
+          <t>S009</t>
         </is>
       </c>
       <c r="C1157" t="inlineStr">
@@ -66466,14 +67324,14 @@
       </c>
       <c r="E1157" t="inlineStr">
         <is>
-          <t>叽叽</t>
+          <t>呜呜</t>
         </is>
       </c>
     </row>
     <row r="1158">
       <c r="A1158" t="inlineStr">
         <is>
-          <t>S004</t>
+          <t>S010</t>
         </is>
       </c>
       <c r="C1158" t="inlineStr">
@@ -66488,14 +67346,14 @@
       </c>
       <c r="E1158" t="inlineStr">
         <is>
-          <t>끼이끼이</t>
+          <t>꾸욱꾸욱</t>
         </is>
       </c>
     </row>
     <row r="1159">
       <c r="A1159" t="inlineStr">
         <is>
-          <t>S004</t>
+          <t>S010</t>
         </is>
       </c>
       <c r="C1159" t="inlineStr">
@@ -66510,14 +67368,14 @@
       </c>
       <c r="E1159" t="inlineStr">
         <is>
-          <t>叽叽</t>
+          <t>咕咕</t>
         </is>
       </c>
     </row>
     <row r="1160">
       <c r="A1160" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>S011</t>
         </is>
       </c>
       <c r="C1160" t="inlineStr">
@@ -66532,14 +67390,14 @@
       </c>
       <c r="E1160" t="inlineStr">
         <is>
-          <t>딱딱딱</t>
+          <t>끼이끼이</t>
         </is>
       </c>
     </row>
     <row r="1161">
       <c r="A1161" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>S011</t>
         </is>
       </c>
       <c r="C1161" t="inlineStr">
@@ -66554,14 +67412,14 @@
       </c>
       <c r="E1161" t="inlineStr">
         <is>
-          <t>嗒嗒</t>
+          <t>叽叽</t>
         </is>
       </c>
     </row>
     <row r="1162">
       <c r="A1162" t="inlineStr">
         <is>
-          <t>S006</t>
+          <t>S012</t>
         </is>
       </c>
       <c r="C1162" t="inlineStr">
@@ -66576,14 +67434,14 @@
       </c>
       <c r="E1162" t="inlineStr">
         <is>
-          <t>우우우</t>
+          <t>끼이끼이</t>
         </is>
       </c>
     </row>
     <row r="1163">
       <c r="A1163" t="inlineStr">
         <is>
-          <t>S006</t>
+          <t>S012</t>
         </is>
       </c>
       <c r="C1163" t="inlineStr">
@@ -66598,14 +67456,14 @@
       </c>
       <c r="E1163" t="inlineStr">
         <is>
-          <t>嗡嗡</t>
+          <t>叽叽</t>
         </is>
       </c>
     </row>
     <row r="1164">
       <c r="A1164" t="inlineStr">
         <is>
-          <t>S007</t>
+          <t>S013</t>
         </is>
       </c>
       <c r="C1164" t="inlineStr">
@@ -66620,14 +67478,14 @@
       </c>
       <c r="E1164" t="inlineStr">
         <is>
-          <t>두두두</t>
+          <t>끼이끼이</t>
         </is>
       </c>
     </row>
     <row r="1165">
       <c r="A1165" t="inlineStr">
         <is>
-          <t>S007</t>
+          <t>S013</t>
         </is>
       </c>
       <c r="C1165" t="inlineStr">
@@ -66642,14 +67500,14 @@
       </c>
       <c r="E1165" t="inlineStr">
         <is>
-          <t>咚咚</t>
+          <t>叽叽</t>
         </is>
       </c>
     </row>
     <row r="1166">
       <c r="A1166" t="inlineStr">
         <is>
-          <t>S008</t>
+          <t>S014</t>
         </is>
       </c>
       <c r="C1166" t="inlineStr">
@@ -66664,14 +67522,14 @@
       </c>
       <c r="E1166" t="inlineStr">
         <is>
-          <t>끼이끼이</t>
+          <t>두두두</t>
         </is>
       </c>
     </row>
     <row r="1167">
       <c r="A1167" t="inlineStr">
         <is>
-          <t>S008</t>
+          <t>S014</t>
         </is>
       </c>
       <c r="C1167" t="inlineStr">
@@ -66686,14 +67544,14 @@
       </c>
       <c r="E1167" t="inlineStr">
         <is>
-          <t>叽叽</t>
+          <t>咚咚</t>
         </is>
       </c>
     </row>
     <row r="1168">
       <c r="A1168" t="inlineStr">
         <is>
-          <t>S009</t>
+          <t>S016</t>
         </is>
       </c>
       <c r="C1168" t="inlineStr">
@@ -66708,14 +67566,14 @@
       </c>
       <c r="E1168" t="inlineStr">
         <is>
-          <t>우우우</t>
+          <t>끼이끼이</t>
         </is>
       </c>
     </row>
     <row r="1169">
       <c r="A1169" t="inlineStr">
         <is>
-          <t>S009</t>
+          <t>S016</t>
         </is>
       </c>
       <c r="C1169" t="inlineStr">
@@ -66730,14 +67588,14 @@
       </c>
       <c r="E1169" t="inlineStr">
         <is>
-          <t>呜呜</t>
+          <t>叽叽</t>
         </is>
       </c>
     </row>
     <row r="1170">
       <c r="A1170" t="inlineStr">
         <is>
-          <t>S010</t>
+          <t>S017</t>
         </is>
       </c>
       <c r="C1170" t="inlineStr">
@@ -66752,14 +67610,14 @@
       </c>
       <c r="E1170" t="inlineStr">
         <is>
-          <t>꾸욱꾸욱</t>
+          <t>끼이끼이</t>
         </is>
       </c>
     </row>
     <row r="1171">
       <c r="A1171" t="inlineStr">
         <is>
-          <t>S010</t>
+          <t>S017</t>
         </is>
       </c>
       <c r="C1171" t="inlineStr">
@@ -66774,14 +67632,14 @@
       </c>
       <c r="E1171" t="inlineStr">
         <is>
-          <t>咕咕</t>
+          <t>叽叽</t>
         </is>
       </c>
     </row>
     <row r="1172">
       <c r="A1172" t="inlineStr">
         <is>
-          <t>S011</t>
+          <t>S018</t>
         </is>
       </c>
       <c r="C1172" t="inlineStr">
@@ -66803,7 +67661,7 @@
     <row r="1173">
       <c r="A1173" t="inlineStr">
         <is>
-          <t>S011</t>
+          <t>S018</t>
         </is>
       </c>
       <c r="C1173" t="inlineStr">
@@ -66825,7 +67683,7 @@
     <row r="1174">
       <c r="A1174" t="inlineStr">
         <is>
-          <t>S012</t>
+          <t>V001</t>
         </is>
       </c>
       <c r="C1174" t="inlineStr">
@@ -66840,14 +67698,14 @@
       </c>
       <c r="E1174" t="inlineStr">
         <is>
-          <t>끼이끼이</t>
+          <t>딱딱</t>
         </is>
       </c>
     </row>
     <row r="1175">
       <c r="A1175" t="inlineStr">
         <is>
-          <t>S012</t>
+          <t>V001</t>
         </is>
       </c>
       <c r="C1175" t="inlineStr">
@@ -66862,14 +67720,14 @@
       </c>
       <c r="E1175" t="inlineStr">
         <is>
-          <t>叽叽</t>
+          <t>嗒嗒</t>
         </is>
       </c>
     </row>
     <row r="1176">
       <c r="A1176" t="inlineStr">
         <is>
-          <t>S013</t>
+          <t>V002</t>
         </is>
       </c>
       <c r="C1176" t="inlineStr">
@@ -66891,7 +67749,7 @@
     <row r="1177">
       <c r="A1177" t="inlineStr">
         <is>
-          <t>S013</t>
+          <t>V002</t>
         </is>
       </c>
       <c r="C1177" t="inlineStr">
@@ -66913,7 +67771,7 @@
     <row r="1178">
       <c r="A1178" t="inlineStr">
         <is>
-          <t>S014</t>
+          <t>V003</t>
         </is>
       </c>
       <c r="C1178" t="inlineStr">
@@ -66928,14 +67786,14 @@
       </c>
       <c r="E1178" t="inlineStr">
         <is>
-          <t>두두두</t>
+          <t>딱딱</t>
         </is>
       </c>
     </row>
     <row r="1179">
       <c r="A1179" t="inlineStr">
         <is>
-          <t>S014</t>
+          <t>V003</t>
         </is>
       </c>
       <c r="C1179" t="inlineStr">
@@ -66950,14 +67808,14 @@
       </c>
       <c r="E1179" t="inlineStr">
         <is>
-          <t>咚咚</t>
+          <t>嗒嗒</t>
         </is>
       </c>
     </row>
     <row r="1180">
       <c r="A1180" t="inlineStr">
         <is>
-          <t>S016</t>
+          <t>V004</t>
         </is>
       </c>
       <c r="C1180" t="inlineStr">
@@ -66972,14 +67830,14 @@
       </c>
       <c r="E1180" t="inlineStr">
         <is>
-          <t>끼이끼이</t>
+          <t>바사바사</t>
         </is>
       </c>
     </row>
     <row r="1181">
       <c r="A1181" t="inlineStr">
         <is>
-          <t>S016</t>
+          <t>V004</t>
         </is>
       </c>
       <c r="C1181" t="inlineStr">
@@ -66994,14 +67852,14 @@
       </c>
       <c r="E1181" t="inlineStr">
         <is>
-          <t>叽叽</t>
+          <t>沙沙</t>
         </is>
       </c>
     </row>
     <row r="1182">
       <c r="A1182" t="inlineStr">
         <is>
-          <t>S017</t>
+          <t>V005</t>
         </is>
       </c>
       <c r="C1182" t="inlineStr">
@@ -67023,7 +67881,7 @@
     <row r="1183">
       <c r="A1183" t="inlineStr">
         <is>
-          <t>S017</t>
+          <t>V005</t>
         </is>
       </c>
       <c r="C1183" t="inlineStr">
@@ -67045,7 +67903,7 @@
     <row r="1184">
       <c r="A1184" t="inlineStr">
         <is>
-          <t>S018</t>
+          <t>V006</t>
         </is>
       </c>
       <c r="C1184" t="inlineStr">
@@ -67060,14 +67918,14 @@
       </c>
       <c r="E1184" t="inlineStr">
         <is>
-          <t>끼이끼이</t>
+          <t>딱딱</t>
         </is>
       </c>
     </row>
     <row r="1185">
       <c r="A1185" t="inlineStr">
         <is>
-          <t>S018</t>
+          <t>V006</t>
         </is>
       </c>
       <c r="C1185" t="inlineStr">
@@ -67082,14 +67940,14 @@
       </c>
       <c r="E1185" t="inlineStr">
         <is>
-          <t>叽叽</t>
+          <t>啪啪</t>
         </is>
       </c>
     </row>
     <row r="1186">
       <c r="A1186" t="inlineStr">
         <is>
-          <t>V001</t>
+          <t>V008</t>
         </is>
       </c>
       <c r="C1186" t="inlineStr">
@@ -67104,14 +67962,14 @@
       </c>
       <c r="E1186" t="inlineStr">
         <is>
-          <t>딱딱</t>
+          <t>끼이끼이</t>
         </is>
       </c>
     </row>
     <row r="1187">
       <c r="A1187" t="inlineStr">
         <is>
-          <t>V001</t>
+          <t>V008</t>
         </is>
       </c>
       <c r="C1187" t="inlineStr">
@@ -67126,14 +67984,14 @@
       </c>
       <c r="E1187" t="inlineStr">
         <is>
-          <t>嗒嗒</t>
+          <t>叽叽</t>
         </is>
       </c>
     </row>
     <row r="1188">
       <c r="A1188" t="inlineStr">
         <is>
-          <t>V002</t>
+          <t>V009</t>
         </is>
       </c>
       <c r="C1188" t="inlineStr">
@@ -67148,14 +68006,14 @@
       </c>
       <c r="E1188" t="inlineStr">
         <is>
-          <t>끼이끼이</t>
+          <t>사각사각</t>
         </is>
       </c>
     </row>
     <row r="1189">
       <c r="A1189" t="inlineStr">
         <is>
-          <t>V002</t>
+          <t>V009</t>
         </is>
       </c>
       <c r="C1189" t="inlineStr">
@@ -67170,14 +68028,14 @@
       </c>
       <c r="E1189" t="inlineStr">
         <is>
-          <t>叽叽</t>
+          <t>沙沙</t>
         </is>
       </c>
     </row>
     <row r="1190">
       <c r="A1190" t="inlineStr">
         <is>
-          <t>V003</t>
+          <t>V010</t>
         </is>
       </c>
       <c r="C1190" t="inlineStr">
@@ -67192,14 +68050,14 @@
       </c>
       <c r="E1190" t="inlineStr">
         <is>
-          <t>딱딱</t>
+          <t>끼이끼이</t>
         </is>
       </c>
     </row>
     <row r="1191">
       <c r="A1191" t="inlineStr">
         <is>
-          <t>V003</t>
+          <t>V010</t>
         </is>
       </c>
       <c r="C1191" t="inlineStr">
@@ -67214,14 +68072,14 @@
       </c>
       <c r="E1191" t="inlineStr">
         <is>
-          <t>嗒嗒</t>
+          <t>叽叽</t>
         </is>
       </c>
     </row>
     <row r="1192">
       <c r="A1192" t="inlineStr">
         <is>
-          <t>V004</t>
+          <t>V012</t>
         </is>
       </c>
       <c r="C1192" t="inlineStr">
@@ -67236,14 +68094,14 @@
       </c>
       <c r="E1192" t="inlineStr">
         <is>
-          <t>바사바사</t>
+          <t>으으으</t>
         </is>
       </c>
     </row>
     <row r="1193">
       <c r="A1193" t="inlineStr">
         <is>
-          <t>V004</t>
+          <t>V012</t>
         </is>
       </c>
       <c r="C1193" t="inlineStr">
@@ -67258,411 +68116,103 @@
       </c>
       <c r="E1193" t="inlineStr">
         <is>
-          <t>沙沙</t>
+          <t>呜呜</t>
         </is>
       </c>
     </row>
     <row r="1194">
       <c r="A1194" t="inlineStr">
         <is>
-          <t>V005</t>
+          <t>A002</t>
+        </is>
+      </c>
+      <c r="B1194" t="inlineStr">
+        <is>
+          <t>ハシブトガラス</t>
         </is>
       </c>
       <c r="C1194" t="inlineStr">
         <is>
-          <t>ko</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="D1194" t="inlineStr">
         <is>
-          <t>한국어</t>
+          <t>日本語</t>
         </is>
       </c>
       <c r="E1194" t="inlineStr">
         <is>
-          <t>끼이끼이</t>
+          <t>カーカー</t>
         </is>
       </c>
     </row>
     <row r="1195">
       <c r="A1195" t="inlineStr">
         <is>
-          <t>V005</t>
+          <t>A002</t>
+        </is>
+      </c>
+      <c r="B1195" t="inlineStr">
+        <is>
+          <t>ハシブトガラス</t>
         </is>
       </c>
       <c r="C1195" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D1195" t="inlineStr">
         <is>
-          <t>中文</t>
+          <t>英語</t>
         </is>
       </c>
       <c r="E1195" t="inlineStr">
         <is>
-          <t>叽叽</t>
+          <t>Caw caw</t>
         </is>
       </c>
     </row>
     <row r="1196">
       <c r="A1196" t="inlineStr">
         <is>
-          <t>V006</t>
+          <t>B022</t>
         </is>
       </c>
       <c r="C1196" t="inlineStr">
         <is>
-          <t>ko</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D1196" t="inlineStr">
         <is>
-          <t>한국어</t>
+          <t>English</t>
         </is>
       </c>
       <c r="E1196" t="inlineStr">
         <is>
-          <t>딱딱</t>
+          <t>Teet</t>
         </is>
       </c>
     </row>
     <row r="1197">
       <c r="A1197" t="inlineStr">
         <is>
-          <t>V006</t>
+          <t>B069</t>
         </is>
       </c>
       <c r="C1197" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D1197" t="inlineStr">
         <is>
-          <t>中文</t>
+          <t>English</t>
         </is>
       </c>
       <c r="E1197" t="inlineStr">
-        <is>
-          <t>啪啪</t>
-        </is>
-      </c>
-    </row>
-    <row r="1198">
-      <c r="A1198" t="inlineStr">
-        <is>
-          <t>V008</t>
-        </is>
-      </c>
-      <c r="C1198" t="inlineStr">
-        <is>
-          <t>ko</t>
-        </is>
-      </c>
-      <c r="D1198" t="inlineStr">
-        <is>
-          <t>한국어</t>
-        </is>
-      </c>
-      <c r="E1198" t="inlineStr">
-        <is>
-          <t>끼이끼이</t>
-        </is>
-      </c>
-    </row>
-    <row r="1199">
-      <c r="A1199" t="inlineStr">
-        <is>
-          <t>V008</t>
-        </is>
-      </c>
-      <c r="C1199" t="inlineStr">
-        <is>
-          <t>zh</t>
-        </is>
-      </c>
-      <c r="D1199" t="inlineStr">
-        <is>
-          <t>中文</t>
-        </is>
-      </c>
-      <c r="E1199" t="inlineStr">
-        <is>
-          <t>叽叽</t>
-        </is>
-      </c>
-    </row>
-    <row r="1200">
-      <c r="A1200" t="inlineStr">
-        <is>
-          <t>V009</t>
-        </is>
-      </c>
-      <c r="C1200" t="inlineStr">
-        <is>
-          <t>ko</t>
-        </is>
-      </c>
-      <c r="D1200" t="inlineStr">
-        <is>
-          <t>한국어</t>
-        </is>
-      </c>
-      <c r="E1200" t="inlineStr">
-        <is>
-          <t>사각사각</t>
-        </is>
-      </c>
-    </row>
-    <row r="1201">
-      <c r="A1201" t="inlineStr">
-        <is>
-          <t>V009</t>
-        </is>
-      </c>
-      <c r="C1201" t="inlineStr">
-        <is>
-          <t>zh</t>
-        </is>
-      </c>
-      <c r="D1201" t="inlineStr">
-        <is>
-          <t>中文</t>
-        </is>
-      </c>
-      <c r="E1201" t="inlineStr">
-        <is>
-          <t>沙沙</t>
-        </is>
-      </c>
-    </row>
-    <row r="1202">
-      <c r="A1202" t="inlineStr">
-        <is>
-          <t>V010</t>
-        </is>
-      </c>
-      <c r="C1202" t="inlineStr">
-        <is>
-          <t>ko</t>
-        </is>
-      </c>
-      <c r="D1202" t="inlineStr">
-        <is>
-          <t>한국어</t>
-        </is>
-      </c>
-      <c r="E1202" t="inlineStr">
-        <is>
-          <t>끼이끼이</t>
-        </is>
-      </c>
-    </row>
-    <row r="1203">
-      <c r="A1203" t="inlineStr">
-        <is>
-          <t>V010</t>
-        </is>
-      </c>
-      <c r="C1203" t="inlineStr">
-        <is>
-          <t>zh</t>
-        </is>
-      </c>
-      <c r="D1203" t="inlineStr">
-        <is>
-          <t>中文</t>
-        </is>
-      </c>
-      <c r="E1203" t="inlineStr">
-        <is>
-          <t>叽叽</t>
-        </is>
-      </c>
-    </row>
-    <row r="1204">
-      <c r="A1204" t="inlineStr">
-        <is>
-          <t>V011</t>
-        </is>
-      </c>
-      <c r="C1204" t="inlineStr">
-        <is>
-          <t>ko</t>
-        </is>
-      </c>
-      <c r="D1204" t="inlineStr">
-        <is>
-          <t>한국어</t>
-        </is>
-      </c>
-      <c r="E1204" t="inlineStr">
-        <is>
-          <t>사각사각</t>
-        </is>
-      </c>
-    </row>
-    <row r="1205">
-      <c r="A1205" t="inlineStr">
-        <is>
-          <t>V011</t>
-        </is>
-      </c>
-      <c r="C1205" t="inlineStr">
-        <is>
-          <t>zh</t>
-        </is>
-      </c>
-      <c r="D1205" t="inlineStr">
-        <is>
-          <t>中文</t>
-        </is>
-      </c>
-      <c r="E1205" t="inlineStr">
-        <is>
-          <t>沙沙</t>
-        </is>
-      </c>
-    </row>
-    <row r="1206">
-      <c r="A1206" t="inlineStr">
-        <is>
-          <t>V012</t>
-        </is>
-      </c>
-      <c r="C1206" t="inlineStr">
-        <is>
-          <t>ko</t>
-        </is>
-      </c>
-      <c r="D1206" t="inlineStr">
-        <is>
-          <t>한국어</t>
-        </is>
-      </c>
-      <c r="E1206" t="inlineStr">
-        <is>
-          <t>으으으</t>
-        </is>
-      </c>
-    </row>
-    <row r="1207">
-      <c r="A1207" t="inlineStr">
-        <is>
-          <t>V012</t>
-        </is>
-      </c>
-      <c r="C1207" t="inlineStr">
-        <is>
-          <t>zh</t>
-        </is>
-      </c>
-      <c r="D1207" t="inlineStr">
-        <is>
-          <t>中文</t>
-        </is>
-      </c>
-      <c r="E1207" t="inlineStr">
-        <is>
-          <t>呜呜</t>
-        </is>
-      </c>
-    </row>
-    <row r="1208">
-      <c r="A1208" t="inlineStr">
-        <is>
-          <t>A002</t>
-        </is>
-      </c>
-      <c r="B1208" t="inlineStr">
-        <is>
-          <t>ハシブトガラス</t>
-        </is>
-      </c>
-      <c r="C1208" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="D1208" t="inlineStr">
-        <is>
-          <t>日本語</t>
-        </is>
-      </c>
-      <c r="E1208" t="inlineStr">
-        <is>
-          <t>カーカー</t>
-        </is>
-      </c>
-    </row>
-    <row r="1209">
-      <c r="A1209" t="inlineStr">
-        <is>
-          <t>A002</t>
-        </is>
-      </c>
-      <c r="B1209" t="inlineStr">
-        <is>
-          <t>ハシブトガラス</t>
-        </is>
-      </c>
-      <c r="C1209" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="D1209" t="inlineStr">
-        <is>
-          <t>英語</t>
-        </is>
-      </c>
-      <c r="E1209" t="inlineStr">
-        <is>
-          <t>Caw caw</t>
-        </is>
-      </c>
-    </row>
-    <row r="1210">
-      <c r="A1210" t="inlineStr">
-        <is>
-          <t>B022</t>
-        </is>
-      </c>
-      <c r="C1210" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="D1210" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="E1210" t="inlineStr">
-        <is>
-          <t>Teet</t>
-        </is>
-      </c>
-    </row>
-    <row r="1211">
-      <c r="A1211" t="inlineStr">
-        <is>
-          <t>B069</t>
-        </is>
-      </c>
-      <c r="C1211" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="D1211" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="E1211" t="inlineStr">
         <is>
           <t>Aah-aah</t>
         </is>
